--- a/analytics-mvp/exports/orders_analytics_2026-08.xlsx
+++ b/analytics-mvp/exports/orders_analytics_2026-08.xlsx
@@ -8125,11 +8125,7 @@
           <t>95681217-0075-1</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>FBS</t>
-        </is>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
           <t>в пути</t>
@@ -10845,11 +10841,7 @@
           <t>0252722211-0075-1</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>FBS</t>
-        </is>
-      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
           <t>ожидает отправки</t>
@@ -12745,11 +12737,7 @@
           <t>29007646-0486-1</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>FBS</t>
-        </is>
-      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
           <t>в пути</t>
@@ -12909,11 +12897,7 @@
           <t>90760158-0108-1</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>FBS</t>
-        </is>
-      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
           <t>в пути</t>
@@ -14463,11 +14447,7 @@
           <t>10428193-0946-4</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>FBS</t>
-        </is>
-      </c>
+      <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
           <t>в пути</t>
@@ -20512,11 +20492,7 @@
           <t>26239914-0165-2</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>FBS</t>
-        </is>
-      </c>
+      <c r="B253" t="inlineStr"/>
       <c r="C253" t="inlineStr">
         <is>
           <t>в пути</t>

--- a/analytics-mvp/exports/orders_analytics_2026-08.xlsx
+++ b/analytics-mvp/exports/orders_analytics_2026-08.xlsx
@@ -662,16 +662,16 @@
         <v>1885</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>66843</v>
+        <v>66851</v>
       </c>
       <c r="O3" t="n">
-        <v>56632</v>
+        <v>56624</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -683,16 +683,16 @@
         <v>13231</v>
       </c>
       <c r="S3" t="n">
-        <v>43401</v>
+        <v>43393</v>
       </c>
       <c r="T3" t="n">
-        <v>16990</v>
+        <v>16987</v>
       </c>
       <c r="U3" t="n">
-        <v>8495</v>
+        <v>8494</v>
       </c>
       <c r="V3" t="n">
-        <v>17917</v>
+        <v>17912</v>
       </c>
       <c r="W3" t="n">
         <v>31.6</v>
@@ -746,10 +746,10 @@
         <v>5706</v>
       </c>
       <c r="N4" t="n">
-        <v>68423</v>
+        <v>68403</v>
       </c>
       <c r="O4" t="n">
-        <v>45691</v>
+        <v>45711</v>
       </c>
       <c r="P4" t="n">
         <v>1028</v>
@@ -761,16 +761,16 @@
         <v>11827</v>
       </c>
       <c r="S4" t="n">
-        <v>35036</v>
+        <v>35056</v>
       </c>
       <c r="T4" t="n">
-        <v>13707</v>
+        <v>13713</v>
       </c>
       <c r="U4" t="n">
-        <v>6854</v>
+        <v>6857</v>
       </c>
       <c r="V4" t="n">
-        <v>14475</v>
+        <v>14486</v>
       </c>
       <c r="W4" t="n">
         <v>31.7</v>
@@ -984,10 +984,10 @@
         <v>5045</v>
       </c>
       <c r="N7" t="n">
-        <v>60306</v>
+        <v>60286</v>
       </c>
       <c r="O7" t="n">
-        <v>40594</v>
+        <v>40614</v>
       </c>
       <c r="P7" t="n">
         <v>4056</v>
@@ -999,19 +999,19 @@
         <v>13231</v>
       </c>
       <c r="S7" t="n">
-        <v>28557</v>
+        <v>28577</v>
       </c>
       <c r="T7" t="n">
-        <v>12178</v>
+        <v>12184</v>
       </c>
       <c r="U7" t="n">
-        <v>6089</v>
+        <v>6092</v>
       </c>
       <c r="V7" t="n">
-        <v>10290</v>
+        <v>10301</v>
       </c>
       <c r="W7" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
         <v>4395</v>
       </c>
       <c r="N9" t="n">
-        <v>51999</v>
+        <v>51979</v>
       </c>
       <c r="O9" t="n">
-        <v>35901</v>
+        <v>35921</v>
       </c>
       <c r="P9" t="n">
         <v>28</v>
@@ -1159,16 +1159,16 @@
         <v>11827</v>
       </c>
       <c r="S9" t="n">
-        <v>26446</v>
+        <v>26466</v>
       </c>
       <c r="T9" t="n">
-        <v>10770</v>
+        <v>10776</v>
       </c>
       <c r="U9" t="n">
-        <v>5385</v>
+        <v>5388</v>
       </c>
       <c r="V9" t="n">
-        <v>10291</v>
+        <v>10302</v>
       </c>
       <c r="W9" t="n">
         <v>28.7</v>
@@ -1226,10 +1226,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>47604</v>
+        <v>47584</v>
       </c>
       <c r="O10" t="n">
-        <v>40296</v>
+        <v>40316</v>
       </c>
       <c r="P10" t="n">
         <v>3195</v>
@@ -1241,16 +1241,16 @@
         <v>11827</v>
       </c>
       <c r="S10" t="n">
-        <v>27774</v>
+        <v>27794</v>
       </c>
       <c r="T10" t="n">
-        <v>12089</v>
+        <v>12095</v>
       </c>
       <c r="U10" t="n">
-        <v>6044</v>
+        <v>6047</v>
       </c>
       <c r="V10" t="n">
-        <v>9641</v>
+        <v>9652</v>
       </c>
       <c r="W10" t="n">
         <v>23.9</v>
@@ -1302,16 +1302,16 @@
         <v>1046</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
         <v>4022</v>
       </c>
       <c r="N11" t="n">
-        <v>49514</v>
+        <v>49524</v>
       </c>
       <c r="O11" t="n">
-        <v>30917</v>
+        <v>30907</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1323,16 +1323,16 @@
         <v>8528</v>
       </c>
       <c r="S11" t="n">
-        <v>22389</v>
+        <v>22379</v>
       </c>
       <c r="T11" t="n">
-        <v>9275</v>
+        <v>9272</v>
       </c>
       <c r="U11" t="n">
-        <v>4638</v>
+        <v>4636</v>
       </c>
       <c r="V11" t="n">
-        <v>8476</v>
+        <v>8471</v>
       </c>
       <c r="W11" t="n">
         <v>27.4</v>
@@ -1380,16 +1380,16 @@
         <v>1677</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
         <v>6561</v>
       </c>
       <c r="N12" t="n">
-        <v>47863</v>
+        <v>47871</v>
       </c>
       <c r="O12" t="n">
-        <v>25037</v>
+        <v>25029</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1401,16 +1401,16 @@
         <v>6945</v>
       </c>
       <c r="S12" t="n">
-        <v>18092</v>
+        <v>18084</v>
       </c>
       <c r="T12" t="n">
-        <v>7511</v>
+        <v>7509</v>
       </c>
       <c r="U12" t="n">
-        <v>3756</v>
+        <v>3754</v>
       </c>
       <c r="V12" t="n">
-        <v>6825</v>
+        <v>6821</v>
       </c>
       <c r="W12" t="n">
         <v>27.3</v>
@@ -1698,10 +1698,10 @@
         <v>6492</v>
       </c>
       <c r="N16" t="n">
-        <v>50139</v>
+        <v>50119</v>
       </c>
       <c r="O16" t="n">
-        <v>21989</v>
+        <v>22009</v>
       </c>
       <c r="P16" t="n">
         <v>3099</v>
@@ -1713,16 +1713,16 @@
         <v>11827</v>
       </c>
       <c r="S16" t="n">
-        <v>9762</v>
+        <v>9782</v>
       </c>
       <c r="T16" t="n">
-        <v>6597</v>
+        <v>6603</v>
       </c>
       <c r="U16" t="n">
-        <v>3298</v>
+        <v>3301</v>
       </c>
       <c r="V16" t="n">
-        <v>-133</v>
+        <v>-122</v>
       </c>
       <c r="W16" t="n">
         <v>-0.6</v>
@@ -1858,10 +1858,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>39278</v>
+        <v>39258</v>
       </c>
       <c r="O18" t="n">
-        <v>31961</v>
+        <v>31981</v>
       </c>
       <c r="P18" t="n">
         <v>1000</v>
@@ -1873,16 +1873,16 @@
         <v>9687</v>
       </c>
       <c r="S18" t="n">
-        <v>23774</v>
+        <v>23794</v>
       </c>
       <c r="T18" t="n">
-        <v>9588</v>
+        <v>9594</v>
       </c>
       <c r="U18" t="n">
-        <v>4794</v>
+        <v>4797</v>
       </c>
       <c r="V18" t="n">
-        <v>9392</v>
+        <v>9403</v>
       </c>
       <c r="W18" t="n">
         <v>29.4</v>
@@ -2172,16 +2172,16 @@
         <v>805</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>33535</v>
+        <v>33544</v>
       </c>
       <c r="O22" t="n">
-        <v>28365</v>
+        <v>28356</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2193,16 +2193,16 @@
         <v>8528</v>
       </c>
       <c r="S22" t="n">
-        <v>19837</v>
+        <v>19828</v>
       </c>
       <c r="T22" t="n">
-        <v>8510</v>
+        <v>8507</v>
       </c>
       <c r="U22" t="n">
-        <v>4255</v>
+        <v>4253</v>
       </c>
       <c r="V22" t="n">
-        <v>7073</v>
+        <v>7068</v>
       </c>
       <c r="W22" t="n">
         <v>24.9</v>
@@ -2406,16 +2406,16 @@
         <v>797</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M25" t="n">
         <v>10008</v>
       </c>
       <c r="N25" t="n">
-        <v>45745</v>
+        <v>45752</v>
       </c>
       <c r="O25" t="n">
-        <v>15569</v>
+        <v>15562</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2427,16 +2427,16 @@
         <v>7673</v>
       </c>
       <c r="S25" t="n">
-        <v>7896</v>
+        <v>7889</v>
       </c>
       <c r="T25" t="n">
-        <v>4671</v>
+        <v>4669</v>
       </c>
       <c r="U25" t="n">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="V25" t="n">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="W25" t="n">
         <v>5.7</v>
@@ -2484,16 +2484,16 @@
         <v>797</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M26" t="n">
         <v>8782</v>
       </c>
       <c r="N26" t="n">
-        <v>45088</v>
+        <v>45097</v>
       </c>
       <c r="O26" t="n">
-        <v>16226</v>
+        <v>16217</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2505,16 +2505,16 @@
         <v>7673</v>
       </c>
       <c r="S26" t="n">
-        <v>8553</v>
+        <v>8544</v>
       </c>
       <c r="T26" t="n">
-        <v>4868</v>
+        <v>4865</v>
       </c>
       <c r="U26" t="n">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="V26" t="n">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="W26" t="n">
         <v>7.7</v>
@@ -2640,16 +2640,16 @@
         <v>797</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M28" t="n">
         <v>10008</v>
       </c>
       <c r="N28" t="n">
-        <v>44470</v>
+        <v>44477</v>
       </c>
       <c r="O28" t="n">
-        <v>16844</v>
+        <v>16837</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2661,16 +2661,16 @@
         <v>7673</v>
       </c>
       <c r="S28" t="n">
-        <v>9171</v>
+        <v>9164</v>
       </c>
       <c r="T28" t="n">
-        <v>5053</v>
+        <v>5051</v>
       </c>
       <c r="U28" t="n">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="V28" t="n">
-        <v>1591</v>
+        <v>1587</v>
       </c>
       <c r="W28" t="n">
         <v>9.4</v>
@@ -2880,10 +2880,10 @@
         <v>2944</v>
       </c>
       <c r="N31" t="n">
-        <v>35451</v>
+        <v>35431</v>
       </c>
       <c r="O31" t="n">
-        <v>23421</v>
+        <v>23441</v>
       </c>
       <c r="P31" t="n">
         <v>769</v>
@@ -2895,16 +2895,16 @@
         <v>8295</v>
       </c>
       <c r="S31" t="n">
-        <v>19656</v>
+        <v>19676</v>
       </c>
       <c r="T31" t="n">
-        <v>7026</v>
+        <v>7032</v>
       </c>
       <c r="U31" t="n">
-        <v>3513</v>
+        <v>3516</v>
       </c>
       <c r="V31" t="n">
-        <v>9117</v>
+        <v>9128</v>
       </c>
       <c r="W31" t="n">
         <v>38.9</v>
@@ -2962,10 +2962,10 @@
         <v>2944</v>
       </c>
       <c r="N32" t="n">
-        <v>35449</v>
+        <v>35429</v>
       </c>
       <c r="O32" t="n">
-        <v>23423</v>
+        <v>23443</v>
       </c>
       <c r="P32" t="n">
         <v>1769</v>
@@ -2977,19 +2977,19 @@
         <v>8295</v>
       </c>
       <c r="S32" t="n">
-        <v>15959</v>
+        <v>15979</v>
       </c>
       <c r="T32" t="n">
-        <v>7027</v>
+        <v>7033</v>
       </c>
       <c r="U32" t="n">
-        <v>3513</v>
+        <v>3516</v>
       </c>
       <c r="V32" t="n">
-        <v>5419</v>
+        <v>5430</v>
       </c>
       <c r="W32" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3200,10 +3200,10 @@
         <v>4053</v>
       </c>
       <c r="N35" t="n">
-        <v>35986</v>
+        <v>35966</v>
       </c>
       <c r="O35" t="n">
-        <v>21914</v>
+        <v>21934</v>
       </c>
       <c r="P35" t="n">
         <v>7352</v>
@@ -3215,19 +3215,19 @@
         <v>6691</v>
       </c>
       <c r="S35" t="n">
-        <v>12370</v>
+        <v>12390</v>
       </c>
       <c r="T35" t="n">
-        <v>6574</v>
+        <v>6580</v>
       </c>
       <c r="U35" t="n">
-        <v>3287</v>
+        <v>3290</v>
       </c>
       <c r="V35" t="n">
-        <v>2509</v>
+        <v>2520</v>
       </c>
       <c r="W35" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -3276,16 +3276,16 @@
         <v>1329</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2939</v>
       </c>
       <c r="M36" t="n">
         <v>4046</v>
       </c>
       <c r="N36" t="n">
-        <v>39488</v>
+        <v>39468</v>
       </c>
       <c r="O36" t="n">
-        <v>18312</v>
+        <v>18332</v>
       </c>
       <c r="P36" t="n">
         <v>769</v>
@@ -3297,19 +3297,19 @@
         <v>8295</v>
       </c>
       <c r="S36" t="n">
-        <v>9657</v>
+        <v>9677</v>
       </c>
       <c r="T36" t="n">
-        <v>5494</v>
+        <v>5500</v>
       </c>
       <c r="U36" t="n">
-        <v>2747</v>
+        <v>2750</v>
       </c>
       <c r="V36" t="n">
-        <v>1417</v>
+        <v>1428</v>
       </c>
       <c r="W36" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -3358,16 +3358,16 @@
         <v>1329</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2538</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>35041</v>
+        <v>35021</v>
       </c>
       <c r="O37" t="n">
-        <v>22759</v>
+        <v>22779</v>
       </c>
       <c r="P37" t="n">
         <v>769</v>
@@ -3379,19 +3379,19 @@
         <v>8295</v>
       </c>
       <c r="S37" t="n">
-        <v>14208</v>
+        <v>14228</v>
       </c>
       <c r="T37" t="n">
-        <v>6828</v>
+        <v>6834</v>
       </c>
       <c r="U37" t="n">
-        <v>3414</v>
+        <v>3417</v>
       </c>
       <c r="V37" t="n">
-        <v>3966</v>
+        <v>3977</v>
       </c>
       <c r="W37" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -3440,16 +3440,16 @@
         <v>740</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>28385</v>
+        <v>28396</v>
       </c>
       <c r="O38" t="n">
-        <v>28555</v>
+        <v>28544</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3461,19 +3461,19 @@
         <v>3497</v>
       </c>
       <c r="S38" t="n">
-        <v>25058</v>
+        <v>25047</v>
       </c>
       <c r="T38" t="n">
-        <v>8566</v>
+        <v>8563</v>
       </c>
       <c r="U38" t="n">
-        <v>4283</v>
+        <v>4282</v>
       </c>
       <c r="V38" t="n">
-        <v>12208</v>
+        <v>12202</v>
       </c>
       <c r="W38" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="X38" t="inlineStr"/>
     </row>
@@ -3518,16 +3518,16 @@
         <v>721</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>11136</v>
       </c>
       <c r="M39" t="n">
         <v>3893</v>
       </c>
       <c r="N39" t="n">
-        <v>45605</v>
+        <v>45585</v>
       </c>
       <c r="O39" t="n">
-        <v>9870</v>
+        <v>9890</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -3539,16 +3539,16 @@
         <v>8414</v>
       </c>
       <c r="S39" t="n">
-        <v>8302</v>
+        <v>8322</v>
       </c>
       <c r="T39" t="n">
-        <v>2961</v>
+        <v>2967</v>
       </c>
       <c r="U39" t="n">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="V39" t="n">
-        <v>3860</v>
+        <v>3872</v>
       </c>
       <c r="W39" t="n">
         <v>39.1</v>
@@ -3752,16 +3752,16 @@
         <v>1217</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M42" t="n">
         <v>4761</v>
       </c>
       <c r="N42" t="n">
-        <v>33690</v>
+        <v>33700</v>
       </c>
       <c r="O42" t="n">
-        <v>19210</v>
+        <v>19200</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -3773,16 +3773,16 @@
         <v>6448</v>
       </c>
       <c r="S42" t="n">
-        <v>12762</v>
+        <v>12752</v>
       </c>
       <c r="T42" t="n">
-        <v>5763</v>
+        <v>5760</v>
       </c>
       <c r="U42" t="n">
-        <v>2882</v>
+        <v>2880</v>
       </c>
       <c r="V42" t="n">
-        <v>4118</v>
+        <v>4112</v>
       </c>
       <c r="W42" t="n">
         <v>21.4</v>
@@ -3908,16 +3908,16 @@
         <v>687</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M44" t="n">
         <v>2643</v>
       </c>
       <c r="N44" t="n">
-        <v>30908</v>
+        <v>30915</v>
       </c>
       <c r="O44" t="n">
-        <v>21950</v>
+        <v>21943</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -3929,16 +3929,16 @@
         <v>6380</v>
       </c>
       <c r="S44" t="n">
-        <v>15570</v>
+        <v>15563</v>
       </c>
       <c r="T44" t="n">
-        <v>6585</v>
+        <v>6583</v>
       </c>
       <c r="U44" t="n">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="V44" t="n">
-        <v>5692</v>
+        <v>5689</v>
       </c>
       <c r="W44" t="n">
         <v>25.9</v>
@@ -4220,16 +4220,16 @@
         <v>662</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M48" t="n">
         <v>2659</v>
       </c>
       <c r="N48" t="n">
-        <v>38561</v>
+        <v>38582</v>
       </c>
       <c r="O48" t="n">
-        <v>12339</v>
+        <v>12318</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -4241,19 +4241,19 @@
         <v>10434</v>
       </c>
       <c r="S48" t="n">
-        <v>1905</v>
+        <v>1884</v>
       </c>
       <c r="T48" t="n">
-        <v>3702</v>
+        <v>3695</v>
       </c>
       <c r="U48" t="n">
-        <v>1851</v>
+        <v>1848</v>
       </c>
       <c r="V48" t="n">
-        <v>-3648</v>
+        <v>-3659</v>
       </c>
       <c r="W48" t="n">
-        <v>-29.6</v>
+        <v>-29.7</v>
       </c>
       <c r="X48" t="inlineStr"/>
     </row>
@@ -4298,16 +4298,16 @@
         <v>659</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M49" t="n">
         <v>3549</v>
       </c>
       <c r="N49" t="n">
-        <v>30942</v>
+        <v>30953</v>
       </c>
       <c r="O49" t="n">
-        <v>19761</v>
+        <v>19750</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -4319,16 +4319,16 @@
         <v>6380</v>
       </c>
       <c r="S49" t="n">
-        <v>13381</v>
+        <v>13370</v>
       </c>
       <c r="T49" t="n">
-        <v>5928</v>
+        <v>5925</v>
       </c>
       <c r="U49" t="n">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="V49" t="n">
-        <v>4489</v>
+        <v>4482</v>
       </c>
       <c r="W49" t="n">
         <v>22.7</v>
@@ -4454,16 +4454,16 @@
         <v>652</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M51" t="n">
         <v>2622</v>
       </c>
       <c r="N51" t="n">
-        <v>35872</v>
+        <v>35881</v>
       </c>
       <c r="O51" t="n">
-        <v>14295</v>
+        <v>14286</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -4475,16 +4475,16 @@
         <v>10434</v>
       </c>
       <c r="S51" t="n">
-        <v>3861</v>
+        <v>3852</v>
       </c>
       <c r="T51" t="n">
-        <v>4288</v>
+        <v>4286</v>
       </c>
       <c r="U51" t="n">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="V51" t="n">
-        <v>-2572</v>
+        <v>-2577</v>
       </c>
       <c r="W51" t="n">
         <v>-18</v>
@@ -4532,16 +4532,16 @@
         <v>647</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M52" t="n">
         <v>2490</v>
       </c>
       <c r="N52" t="n">
-        <v>29489</v>
+        <v>29503</v>
       </c>
       <c r="O52" t="n">
-        <v>20311</v>
+        <v>20297</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -4553,16 +4553,16 @@
         <v>6034</v>
       </c>
       <c r="S52" t="n">
-        <v>14277</v>
+        <v>14263</v>
       </c>
       <c r="T52" t="n">
-        <v>6093</v>
+        <v>6089</v>
       </c>
       <c r="U52" t="n">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="V52" t="n">
-        <v>5137</v>
+        <v>5129</v>
       </c>
       <c r="W52" t="n">
         <v>25.3</v>
@@ -4616,10 +4616,10 @@
         <v>356</v>
       </c>
       <c r="N53" t="n">
-        <v>26968</v>
+        <v>26948</v>
       </c>
       <c r="O53" t="n">
-        <v>22005</v>
+        <v>22025</v>
       </c>
       <c r="P53" t="n">
         <v>4824</v>
@@ -4631,16 +4631,16 @@
         <v>9352</v>
       </c>
       <c r="S53" t="n">
-        <v>11729</v>
+        <v>11749</v>
       </c>
       <c r="T53" t="n">
-        <v>6602</v>
+        <v>6608</v>
       </c>
       <c r="U53" t="n">
-        <v>3301</v>
+        <v>3304</v>
       </c>
       <c r="V53" t="n">
-        <v>1827</v>
+        <v>1838</v>
       </c>
       <c r="W53" t="n">
         <v>8.300000000000001</v>
@@ -4692,16 +4692,16 @@
         <v>631</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M54" t="n">
         <v>6458</v>
       </c>
       <c r="N54" t="n">
-        <v>31872</v>
+        <v>31893</v>
       </c>
       <c r="O54" t="n">
-        <v>16700</v>
+        <v>16679</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -4713,19 +4713,19 @@
         <v>6448</v>
       </c>
       <c r="S54" t="n">
-        <v>10252</v>
+        <v>10231</v>
       </c>
       <c r="T54" t="n">
-        <v>5010</v>
+        <v>5004</v>
       </c>
       <c r="U54" t="n">
-        <v>2505</v>
+        <v>2502</v>
       </c>
       <c r="V54" t="n">
-        <v>2737</v>
+        <v>2725</v>
       </c>
       <c r="W54" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="X54" t="inlineStr"/>
     </row>
@@ -4926,16 +4926,16 @@
         <v>623</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>25723</v>
+        <v>25734</v>
       </c>
       <c r="O57" t="n">
-        <v>22177</v>
+        <v>22166</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4947,16 +4947,16 @@
         <v>5882</v>
       </c>
       <c r="S57" t="n">
-        <v>16295</v>
+        <v>16284</v>
       </c>
       <c r="T57" t="n">
-        <v>6653</v>
+        <v>6650</v>
       </c>
       <c r="U57" t="n">
-        <v>3327</v>
+        <v>3325</v>
       </c>
       <c r="V57" t="n">
-        <v>6315</v>
+        <v>6309</v>
       </c>
       <c r="W57" t="n">
         <v>28.5</v>
@@ -5004,16 +5004,16 @@
         <v>621</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>26163</v>
+        <v>26173</v>
       </c>
       <c r="O58" t="n">
-        <v>21637</v>
+        <v>21627</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -5025,16 +5025,16 @@
         <v>5662</v>
       </c>
       <c r="S58" t="n">
-        <v>15975</v>
+        <v>15965</v>
       </c>
       <c r="T58" t="n">
-        <v>6491</v>
+        <v>6488</v>
       </c>
       <c r="U58" t="n">
-        <v>3246</v>
+        <v>3244</v>
       </c>
       <c r="V58" t="n">
-        <v>6238</v>
+        <v>6233</v>
       </c>
       <c r="W58" t="n">
         <v>28.8</v>
@@ -5082,16 +5082,16 @@
         <v>614</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M59" t="n">
         <v>2363</v>
       </c>
       <c r="N59" t="n">
-        <v>27828</v>
+        <v>27843</v>
       </c>
       <c r="O59" t="n">
-        <v>19433</v>
+        <v>19418</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -5103,19 +5103,19 @@
         <v>5662</v>
       </c>
       <c r="S59" t="n">
-        <v>13771</v>
+        <v>13756</v>
       </c>
       <c r="T59" t="n">
-        <v>5830</v>
+        <v>5825</v>
       </c>
       <c r="U59" t="n">
-        <v>2915</v>
+        <v>2913</v>
       </c>
       <c r="V59" t="n">
-        <v>5026</v>
+        <v>5018</v>
       </c>
       <c r="W59" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="X59" t="inlineStr"/>
     </row>
@@ -5800,16 +5800,16 @@
         <v>851</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M68" t="n">
         <v>3951</v>
       </c>
       <c r="N68" t="n">
-        <v>31496</v>
+        <v>31504</v>
       </c>
       <c r="O68" t="n">
-        <v>12404</v>
+        <v>12396</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>4971</v>
       </c>
       <c r="S68" t="n">
-        <v>7433</v>
+        <v>7425</v>
       </c>
       <c r="T68" t="n">
-        <v>3721</v>
+        <v>3719</v>
       </c>
       <c r="U68" t="n">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="V68" t="n">
-        <v>1851</v>
+        <v>1847</v>
       </c>
       <c r="W68" t="n">
         <v>14.9</v>
@@ -6124,16 +6124,16 @@
         <v>569</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M72" t="n">
         <v>2190</v>
       </c>
       <c r="N72" t="n">
-        <v>29408</v>
+        <v>29416</v>
       </c>
       <c r="O72" t="n">
-        <v>14392</v>
+        <v>14384</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -6145,16 +6145,16 @@
         <v>4565</v>
       </c>
       <c r="S72" t="n">
-        <v>9827</v>
+        <v>9819</v>
       </c>
       <c r="T72" t="n">
-        <v>4318</v>
+        <v>4315</v>
       </c>
       <c r="U72" t="n">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="V72" t="n">
-        <v>3351</v>
+        <v>3346</v>
       </c>
       <c r="W72" t="n">
         <v>23.3</v>
@@ -6202,16 +6202,16 @@
         <v>569</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M73" t="n">
         <v>1758</v>
       </c>
       <c r="N73" t="n">
-        <v>28963</v>
+        <v>28971</v>
       </c>
       <c r="O73" t="n">
-        <v>14837</v>
+        <v>14829</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -6223,16 +6223,16 @@
         <v>4971</v>
       </c>
       <c r="S73" t="n">
-        <v>9866</v>
+        <v>9858</v>
       </c>
       <c r="T73" t="n">
-        <v>4451</v>
+        <v>4449</v>
       </c>
       <c r="U73" t="n">
-        <v>2226</v>
+        <v>2224</v>
       </c>
       <c r="V73" t="n">
-        <v>3189</v>
+        <v>3185</v>
       </c>
       <c r="W73" t="n">
         <v>21.5</v>
@@ -6362,16 +6362,16 @@
         <v>569</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M75" t="n">
         <v>7110</v>
       </c>
       <c r="N75" t="n">
-        <v>31911</v>
+        <v>31918</v>
       </c>
       <c r="O75" t="n">
-        <v>11867</v>
+        <v>11860</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
@@ -6383,16 +6383,16 @@
         <v>4565</v>
       </c>
       <c r="S75" t="n">
-        <v>7302</v>
+        <v>7295</v>
       </c>
       <c r="T75" t="n">
-        <v>3560</v>
+        <v>3558</v>
       </c>
       <c r="U75" t="n">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="V75" t="n">
-        <v>1962</v>
+        <v>1958</v>
       </c>
       <c r="W75" t="n">
         <v>16.5</v>
@@ -6518,16 +6518,16 @@
         <v>569</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M77" t="n">
         <v>7110</v>
       </c>
       <c r="N77" t="n">
-        <v>31912</v>
+        <v>31920</v>
       </c>
       <c r="O77" t="n">
-        <v>11866</v>
+        <v>11858</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -6539,16 +6539,16 @@
         <v>4565</v>
       </c>
       <c r="S77" t="n">
-        <v>7301</v>
+        <v>7293</v>
       </c>
       <c r="T77" t="n">
-        <v>3560</v>
+        <v>3557</v>
       </c>
       <c r="U77" t="n">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="V77" t="n">
-        <v>1961</v>
+        <v>1957</v>
       </c>
       <c r="W77" t="n">
         <v>16.5</v>
@@ -6674,16 +6674,16 @@
         <v>569</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M79" t="n">
         <v>7111</v>
       </c>
       <c r="N79" t="n">
-        <v>32351</v>
+        <v>32359</v>
       </c>
       <c r="O79" t="n">
-        <v>11427</v>
+        <v>11419</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -6695,19 +6695,19 @@
         <v>4565</v>
       </c>
       <c r="S79" t="n">
-        <v>6862</v>
+        <v>6854</v>
       </c>
       <c r="T79" t="n">
-        <v>3428</v>
+        <v>3426</v>
       </c>
       <c r="U79" t="n">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="V79" t="n">
-        <v>1720</v>
+        <v>1715</v>
       </c>
       <c r="W79" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="X79" t="inlineStr"/>
     </row>
@@ -6830,16 +6830,16 @@
         <v>541</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M81" t="n">
         <v>2079</v>
       </c>
       <c r="N81" t="n">
-        <v>24258</v>
+        <v>24267</v>
       </c>
       <c r="O81" t="n">
-        <v>17322</v>
+        <v>17313</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -6851,16 +6851,16 @@
         <v>4768</v>
       </c>
       <c r="S81" t="n">
-        <v>12554</v>
+        <v>12545</v>
       </c>
       <c r="T81" t="n">
-        <v>5197</v>
+        <v>5194</v>
       </c>
       <c r="U81" t="n">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="V81" t="n">
-        <v>4759</v>
+        <v>4754</v>
       </c>
       <c r="W81" t="n">
         <v>27.5</v>
@@ -6908,16 +6908,16 @@
         <v>519</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M82" t="n">
         <v>3591</v>
       </c>
       <c r="N82" t="n">
-        <v>26370</v>
+        <v>26378</v>
       </c>
       <c r="O82" t="n">
-        <v>13530</v>
+        <v>13522</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
@@ -6929,16 +6929,16 @@
         <v>4196</v>
       </c>
       <c r="S82" t="n">
-        <v>9334</v>
+        <v>9326</v>
       </c>
       <c r="T82" t="n">
-        <v>4059</v>
+        <v>4057</v>
       </c>
       <c r="U82" t="n">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="V82" t="n">
-        <v>3246</v>
+        <v>3241</v>
       </c>
       <c r="W82" t="n">
         <v>24</v>
@@ -6986,16 +6986,16 @@
         <v>510</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M83" t="n">
         <v>2432</v>
       </c>
       <c r="N83" t="n">
-        <v>23425</v>
+        <v>23437</v>
       </c>
       <c r="O83" t="n">
-        <v>15836</v>
+        <v>15824</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -7007,19 +7007,19 @@
         <v>6815</v>
       </c>
       <c r="S83" t="n">
-        <v>9021</v>
+        <v>9009</v>
       </c>
       <c r="T83" t="n">
-        <v>4751</v>
+        <v>4747</v>
       </c>
       <c r="U83" t="n">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="V83" t="n">
-        <v>1895</v>
+        <v>1888</v>
       </c>
       <c r="W83" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="X83" t="inlineStr"/>
     </row>
@@ -7142,16 +7142,16 @@
         <v>786</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M85" t="n">
         <v>234</v>
       </c>
       <c r="N85" t="n">
-        <v>22975</v>
+        <v>22990</v>
       </c>
       <c r="O85" t="n">
-        <v>15925</v>
+        <v>15910</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
@@ -7163,16 +7163,16 @@
         <v>4971</v>
       </c>
       <c r="S85" t="n">
-        <v>10954</v>
+        <v>10939</v>
       </c>
       <c r="T85" t="n">
-        <v>4778</v>
+        <v>4773</v>
       </c>
       <c r="U85" t="n">
-        <v>2389</v>
+        <v>2386</v>
       </c>
       <c r="V85" t="n">
-        <v>3788</v>
+        <v>3780</v>
       </c>
       <c r="W85" t="n">
         <v>23.8</v>
@@ -7298,16 +7298,16 @@
         <v>467</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M87" t="n">
         <v>3235</v>
       </c>
       <c r="N87" t="n">
-        <v>23059</v>
+        <v>23067</v>
       </c>
       <c r="O87" t="n">
-        <v>12869</v>
+        <v>12861</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
@@ -7319,16 +7319,16 @@
         <v>6422</v>
       </c>
       <c r="S87" t="n">
-        <v>6447</v>
+        <v>6439</v>
       </c>
       <c r="T87" t="n">
-        <v>3861</v>
+        <v>3858</v>
       </c>
       <c r="U87" t="n">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="V87" t="n">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="W87" t="n">
         <v>5.1</v>
@@ -7454,16 +7454,16 @@
         <v>467</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M89" t="n">
         <v>3231</v>
       </c>
       <c r="N89" t="n">
-        <v>22824</v>
+        <v>22835</v>
       </c>
       <c r="O89" t="n">
-        <v>13076</v>
+        <v>13065</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
@@ -7475,16 +7475,16 @@
         <v>3737</v>
       </c>
       <c r="S89" t="n">
-        <v>9339</v>
+        <v>9328</v>
       </c>
       <c r="T89" t="n">
-        <v>3923</v>
+        <v>3920</v>
       </c>
       <c r="U89" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="V89" t="n">
-        <v>3455</v>
+        <v>3449</v>
       </c>
       <c r="W89" t="n">
         <v>26.4</v>
@@ -7532,16 +7532,16 @@
         <v>467</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M90" t="n">
         <v>1795</v>
       </c>
       <c r="N90" t="n">
-        <v>21367</v>
+        <v>21377</v>
       </c>
       <c r="O90" t="n">
-        <v>14533</v>
+        <v>14523</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -7553,16 +7553,16 @@
         <v>3737</v>
       </c>
       <c r="S90" t="n">
-        <v>10796</v>
+        <v>10786</v>
       </c>
       <c r="T90" t="n">
-        <v>4360</v>
+        <v>4357</v>
       </c>
       <c r="U90" t="n">
-        <v>2180</v>
+        <v>2178</v>
       </c>
       <c r="V90" t="n">
-        <v>4256</v>
+        <v>4251</v>
       </c>
       <c r="W90" t="n">
         <v>29.3</v>
@@ -8468,16 +8468,16 @@
         <v>778</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M102" t="n">
         <v>3046</v>
       </c>
       <c r="N102" t="n">
-        <v>21645</v>
+        <v>21655</v>
       </c>
       <c r="O102" t="n">
-        <v>12197</v>
+        <v>12187</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
@@ -8489,19 +8489,19 @@
         <v>3419</v>
       </c>
       <c r="S102" t="n">
-        <v>8778</v>
+        <v>8768</v>
       </c>
       <c r="T102" t="n">
-        <v>3659</v>
+        <v>3656</v>
       </c>
       <c r="U102" t="n">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="V102" t="n">
-        <v>3289</v>
+        <v>3284</v>
       </c>
       <c r="W102" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="X102" t="inlineStr"/>
     </row>
@@ -8546,16 +8546,16 @@
         <v>424</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M103" t="n">
         <v>2938</v>
       </c>
       <c r="N103" t="n">
-        <v>20565</v>
+        <v>20572</v>
       </c>
       <c r="O103" t="n">
-        <v>12078</v>
+        <v>12071</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
@@ -8567,16 +8567,16 @@
         <v>3419</v>
       </c>
       <c r="S103" t="n">
-        <v>8659</v>
+        <v>8652</v>
       </c>
       <c r="T103" t="n">
-        <v>3623</v>
+        <v>3621</v>
       </c>
       <c r="U103" t="n">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="V103" t="n">
-        <v>3224</v>
+        <v>3220</v>
       </c>
       <c r="W103" t="n">
         <v>26.7</v>
@@ -8624,16 +8624,16 @@
         <v>424</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M104" t="n">
         <v>1632</v>
       </c>
       <c r="N104" t="n">
-        <v>18976</v>
+        <v>18985</v>
       </c>
       <c r="O104" t="n">
-        <v>13667</v>
+        <v>13658</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
@@ -8645,16 +8645,16 @@
         <v>3419</v>
       </c>
       <c r="S104" t="n">
-        <v>10248</v>
+        <v>10239</v>
       </c>
       <c r="T104" t="n">
-        <v>4100</v>
+        <v>4097</v>
       </c>
       <c r="U104" t="n">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="V104" t="n">
-        <v>4098</v>
+        <v>4093</v>
       </c>
       <c r="W104" t="n">
         <v>30</v>
@@ -8780,16 +8780,16 @@
         <v>550</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M106" t="n">
         <v>2151</v>
       </c>
       <c r="N106" t="n">
-        <v>15756</v>
+        <v>15764</v>
       </c>
       <c r="O106" t="n">
-        <v>8144</v>
+        <v>8136</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
@@ -8801,16 +8801,16 @@
         <v>3233</v>
       </c>
       <c r="S106" t="n">
-        <v>4911</v>
+        <v>4903</v>
       </c>
       <c r="T106" t="n">
-        <v>2443</v>
+        <v>2441</v>
       </c>
       <c r="U106" t="n">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="V106" t="n">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="W106" t="n">
         <v>15.3</v>
@@ -8858,16 +8858,16 @@
         <v>535</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M107" t="n">
         <v>2094</v>
       </c>
       <c r="N107" t="n">
-        <v>15366</v>
+        <v>15381</v>
       </c>
       <c r="O107" t="n">
-        <v>7897</v>
+        <v>7882</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -8879,19 +8879,19 @@
         <v>3233</v>
       </c>
       <c r="S107" t="n">
-        <v>4664</v>
+        <v>4649</v>
       </c>
       <c r="T107" t="n">
-        <v>2369</v>
+        <v>2365</v>
       </c>
       <c r="U107" t="n">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="V107" t="n">
-        <v>1110</v>
+        <v>1102</v>
       </c>
       <c r="W107" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="X107" t="inlineStr"/>
     </row>
@@ -8936,16 +8936,16 @@
         <v>298</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M108" t="n">
         <v>1861</v>
       </c>
       <c r="N108" t="n">
-        <v>14194</v>
+        <v>14205</v>
       </c>
       <c r="O108" t="n">
-        <v>8706</v>
+        <v>8695</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
@@ -8957,16 +8957,16 @@
         <v>3419</v>
       </c>
       <c r="S108" t="n">
-        <v>5287</v>
+        <v>5276</v>
       </c>
       <c r="T108" t="n">
-        <v>2612</v>
+        <v>2608</v>
       </c>
       <c r="U108" t="n">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="V108" t="n">
-        <v>1369</v>
+        <v>1363</v>
       </c>
       <c r="W108" t="n">
         <v>15.7</v>
@@ -9014,16 +9014,16 @@
         <v>233</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M109" t="n">
         <v>895</v>
       </c>
       <c r="N109" t="n">
-        <v>10125</v>
+        <v>10136</v>
       </c>
       <c r="O109" t="n">
-        <v>7775</v>
+        <v>7764</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
@@ -9035,16 +9035,16 @@
         <v>2889</v>
       </c>
       <c r="S109" t="n">
-        <v>4886</v>
+        <v>4875</v>
       </c>
       <c r="T109" t="n">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="U109" t="n">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="V109" t="n">
-        <v>1387</v>
+        <v>1381</v>
       </c>
       <c r="W109" t="n">
         <v>17.8</v>
@@ -9092,16 +9092,16 @@
         <v>751</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M110" t="n">
         <v>2938</v>
       </c>
       <c r="N110" t="n">
-        <v>4336</v>
+        <v>4345</v>
       </c>
       <c r="O110" t="n">
-        <v>-4336</v>
+        <v>-4345</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
@@ -9113,16 +9113,16 @@
         <v>3419</v>
       </c>
       <c r="S110" t="n">
-        <v>-7755</v>
+        <v>-7764</v>
       </c>
       <c r="T110" t="n">
-        <v>-1301</v>
+        <v>-1304</v>
       </c>
       <c r="U110" t="n">
-        <v>-650</v>
+        <v>-652</v>
       </c>
       <c r="V110" t="n">
-        <v>-5804</v>
+        <v>-5809</v>
       </c>
       <c r="X110" t="inlineStr"/>
     </row>
@@ -9242,16 +9242,16 @@
         <v>874</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M112" t="n">
         <v>3362</v>
       </c>
       <c r="N112" t="n">
-        <v>5959</v>
+        <v>5969</v>
       </c>
       <c r="O112" t="n">
-        <v>-5959</v>
+        <v>-5969</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
@@ -9263,16 +9263,16 @@
         <v>7453</v>
       </c>
       <c r="S112" t="n">
-        <v>-13412</v>
+        <v>-13422</v>
       </c>
       <c r="T112" t="n">
-        <v>-1788</v>
+        <v>-1791</v>
       </c>
       <c r="U112" t="n">
-        <v>-894</v>
+        <v>-895</v>
       </c>
       <c r="V112" t="n">
-        <v>-10730</v>
+        <v>-10736</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
@@ -9357,10 +9357,10 @@
         <v>3795</v>
       </c>
       <c r="N114" t="n">
-        <v>44163</v>
+        <v>44143</v>
       </c>
       <c r="O114" t="n">
-        <v>31737</v>
+        <v>31757</v>
       </c>
       <c r="P114" t="n">
         <v>3245</v>
@@ -9372,19 +9372,19 @@
         <v>11477</v>
       </c>
       <c r="S114" t="n">
-        <v>19814</v>
+        <v>19834</v>
       </c>
       <c r="T114" t="n">
-        <v>9521</v>
+        <v>9527</v>
       </c>
       <c r="U114" t="n">
-        <v>4761</v>
+        <v>4764</v>
       </c>
       <c r="V114" t="n">
-        <v>5532</v>
+        <v>5543</v>
       </c>
       <c r="W114" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
@@ -9433,16 +9433,16 @@
         <v>994</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M115" t="n">
         <v>2745</v>
       </c>
       <c r="N115" t="n">
-        <v>32470</v>
+        <v>32479</v>
       </c>
       <c r="O115" t="n">
-        <v>22430</v>
+        <v>22421</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
@@ -9454,16 +9454,16 @@
         <v>10263</v>
       </c>
       <c r="S115" t="n">
-        <v>12167</v>
+        <v>12158</v>
       </c>
       <c r="T115" t="n">
-        <v>6729</v>
+        <v>6726</v>
       </c>
       <c r="U115" t="n">
-        <v>3364</v>
+        <v>3363</v>
       </c>
       <c r="V115" t="n">
-        <v>2074</v>
+        <v>2069</v>
       </c>
       <c r="W115" t="n">
         <v>9.199999999999999</v>
@@ -9515,16 +9515,16 @@
         <v>994</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>29027</v>
+        <v>29038</v>
       </c>
       <c r="O116" t="n">
-        <v>25873</v>
+        <v>25862</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
@@ -9536,16 +9536,16 @@
         <v>10263</v>
       </c>
       <c r="S116" t="n">
-        <v>15610</v>
+        <v>15599</v>
       </c>
       <c r="T116" t="n">
-        <v>7762</v>
+        <v>7759</v>
       </c>
       <c r="U116" t="n">
-        <v>3881</v>
+        <v>3879</v>
       </c>
       <c r="V116" t="n">
-        <v>3967</v>
+        <v>3961</v>
       </c>
       <c r="W116" t="n">
         <v>15.3</v>
@@ -9679,16 +9679,16 @@
         <v>531</v>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>25045</v>
+        <v>25061</v>
       </c>
       <c r="O118" t="n">
-        <v>15835</v>
+        <v>15819</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -9700,16 +9700,16 @@
         <v>7962</v>
       </c>
       <c r="S118" t="n">
-        <v>7873</v>
+        <v>7857</v>
       </c>
       <c r="T118" t="n">
-        <v>4750</v>
+        <v>4746</v>
       </c>
       <c r="U118" t="n">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="V118" t="n">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="W118" t="n">
         <v>4.7</v>
@@ -10007,16 +10007,16 @@
         <v>772</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M122" t="n">
         <v>6818</v>
       </c>
       <c r="N122" t="n">
-        <v>27488</v>
+        <v>27507</v>
       </c>
       <c r="O122" t="n">
-        <v>10392</v>
+        <v>10373</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -10028,19 +10028,19 @@
         <v>6061</v>
       </c>
       <c r="S122" t="n">
-        <v>4331</v>
+        <v>4312</v>
       </c>
       <c r="T122" t="n">
-        <v>3118</v>
+        <v>3112</v>
       </c>
       <c r="U122" t="n">
-        <v>1559</v>
+        <v>1556</v>
       </c>
       <c r="V122" t="n">
-        <v>-345</v>
+        <v>-356</v>
       </c>
       <c r="W122" t="n">
-        <v>-3.3</v>
+        <v>-3.4</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
@@ -10405,16 +10405,16 @@
         <v>310</v>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M127" t="n">
         <v>2149</v>
       </c>
       <c r="N127" t="n">
-        <v>16122</v>
+        <v>16129</v>
       </c>
       <c r="O127" t="n">
-        <v>7758</v>
+        <v>7751</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
@@ -10426,16 +10426,16 @@
         <v>4287</v>
       </c>
       <c r="S127" t="n">
-        <v>3471</v>
+        <v>3464</v>
       </c>
       <c r="T127" t="n">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="U127" t="n">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="V127" t="n">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="W127" t="n">
         <v>-0.3</v>
@@ -10513,16 +10513,16 @@
         <v>1059</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>27492</v>
+        <v>27500</v>
       </c>
       <c r="O129" t="n">
-        <v>32408</v>
+        <v>32400</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -10534,19 +10534,19 @@
         <v>7340</v>
       </c>
       <c r="S129" t="n">
-        <v>25068</v>
+        <v>25060</v>
       </c>
       <c r="T129" t="n">
-        <v>9722</v>
+        <v>9720</v>
       </c>
       <c r="U129" t="n">
-        <v>4861</v>
+        <v>4860</v>
       </c>
       <c r="V129" t="n">
-        <v>10484</v>
+        <v>10480</v>
       </c>
       <c r="W129" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="X129" t="inlineStr"/>
     </row>
@@ -10679,10 +10679,10 @@
         <v>2595</v>
       </c>
       <c r="N131" t="n">
-        <v>27659</v>
+        <v>27639</v>
       </c>
       <c r="O131" t="n">
-        <v>24241</v>
+        <v>24261</v>
       </c>
       <c r="P131" t="n">
         <v>1854</v>
@@ -10694,16 +10694,16 @@
         <v>8494</v>
       </c>
       <c r="S131" t="n">
-        <v>17593</v>
+        <v>17613</v>
       </c>
       <c r="T131" t="n">
-        <v>7272</v>
+        <v>7278</v>
       </c>
       <c r="U131" t="n">
-        <v>3636</v>
+        <v>3639</v>
       </c>
       <c r="V131" t="n">
-        <v>6685</v>
+        <v>6696</v>
       </c>
       <c r="W131" t="n">
         <v>27.6</v>
@@ -10761,10 +10761,10 @@
         <v>3073</v>
       </c>
       <c r="N132" t="n">
-        <v>23858</v>
+        <v>23838</v>
       </c>
       <c r="O132" t="n">
-        <v>20042</v>
+        <v>20062</v>
       </c>
       <c r="P132" t="n">
         <v>3987</v>
@@ -10776,19 +10776,19 @@
         <v>9446</v>
       </c>
       <c r="S132" t="n">
-        <v>10809</v>
+        <v>10829</v>
       </c>
       <c r="T132" t="n">
-        <v>6013</v>
+        <v>6019</v>
       </c>
       <c r="U132" t="n">
-        <v>3006</v>
+        <v>3009</v>
       </c>
       <c r="V132" t="n">
-        <v>1790</v>
+        <v>1801</v>
       </c>
       <c r="W132" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
@@ -10947,10 +10947,10 @@
         <v>9163</v>
       </c>
       <c r="N135" t="n">
-        <v>78737</v>
+        <v>78717</v>
       </c>
       <c r="O135" t="n">
-        <v>52163</v>
+        <v>52183</v>
       </c>
       <c r="P135" t="n">
         <v>6317</v>
@@ -10962,16 +10962,16 @@
         <v>22283</v>
       </c>
       <c r="S135" t="n">
-        <v>28863</v>
+        <v>28883</v>
       </c>
       <c r="T135" t="n">
-        <v>15649</v>
+        <v>15655</v>
       </c>
       <c r="U135" t="n">
-        <v>7824</v>
+        <v>7827</v>
       </c>
       <c r="V135" t="n">
-        <v>5390</v>
+        <v>5401</v>
       </c>
       <c r="W135" t="n">
         <v>10.3</v>
@@ -11019,16 +11019,16 @@
         <v>1546</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>3628</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>66843</v>
+        <v>66823</v>
       </c>
       <c r="O136" t="n">
-        <v>52057</v>
+        <v>52077</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -11040,16 +11040,16 @@
         <v>18384</v>
       </c>
       <c r="S136" t="n">
-        <v>35031</v>
+        <v>35051</v>
       </c>
       <c r="T136" t="n">
-        <v>15617</v>
+        <v>15623</v>
       </c>
       <c r="U136" t="n">
-        <v>7809</v>
+        <v>7812</v>
       </c>
       <c r="V136" t="n">
-        <v>11605</v>
+        <v>11616</v>
       </c>
       <c r="W136" t="n">
         <v>22.3</v>
@@ -11107,10 +11107,10 @@
         <v>7833</v>
       </c>
       <c r="N137" t="n">
-        <v>67351</v>
+        <v>67331</v>
       </c>
       <c r="O137" t="n">
-        <v>44549</v>
+        <v>44569</v>
       </c>
       <c r="P137" t="n">
         <v>1000</v>
@@ -11122,16 +11122,16 @@
         <v>20508</v>
       </c>
       <c r="S137" t="n">
-        <v>26640</v>
+        <v>26660</v>
       </c>
       <c r="T137" t="n">
-        <v>13365</v>
+        <v>13371</v>
       </c>
       <c r="U137" t="n">
-        <v>6682</v>
+        <v>6685</v>
       </c>
       <c r="V137" t="n">
-        <v>6593</v>
+        <v>6604</v>
       </c>
       <c r="W137" t="n">
         <v>14.8</v>
@@ -11185,10 +11185,10 @@
         <v>25470</v>
       </c>
       <c r="N138" t="n">
-        <v>83720</v>
+        <v>83700</v>
       </c>
       <c r="O138" t="n">
-        <v>26180</v>
+        <v>26200</v>
       </c>
       <c r="P138" t="n">
         <v>5275</v>
@@ -11200,16 +11200,16 @@
         <v>16996</v>
       </c>
       <c r="S138" t="n">
-        <v>8109</v>
+        <v>8129</v>
       </c>
       <c r="T138" t="n">
-        <v>7854</v>
+        <v>7860</v>
       </c>
       <c r="U138" t="n">
-        <v>3927</v>
+        <v>3930</v>
       </c>
       <c r="V138" t="n">
-        <v>-3672</v>
+        <v>-3661</v>
       </c>
       <c r="W138" t="n">
         <v>-14</v>
@@ -11297,10 +11297,10 @@
         <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>87270</v>
+        <v>87250</v>
       </c>
       <c r="O140" t="n">
-        <v>94773</v>
+        <v>94793</v>
       </c>
       <c r="P140" t="n">
         <v>3666</v>
@@ -11312,16 +11312,16 @@
         <v>37395</v>
       </c>
       <c r="S140" t="n">
-        <v>56511</v>
+        <v>56531</v>
       </c>
       <c r="T140" t="n">
-        <v>28432</v>
+        <v>28438</v>
       </c>
       <c r="U140" t="n">
-        <v>14216</v>
+        <v>14219</v>
       </c>
       <c r="V140" t="n">
-        <v>13863</v>
+        <v>13874</v>
       </c>
       <c r="W140" t="n">
         <v>14.6</v>
@@ -11375,10 +11375,10 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>76547</v>
+        <v>76527</v>
       </c>
       <c r="O141" t="n">
-        <v>85244</v>
+        <v>85264</v>
       </c>
       <c r="P141" t="n">
         <v>1000</v>
@@ -11390,16 +11390,16 @@
         <v>16435</v>
       </c>
       <c r="S141" t="n">
-        <v>70309</v>
+        <v>70329</v>
       </c>
       <c r="T141" t="n">
-        <v>25573</v>
+        <v>25579</v>
       </c>
       <c r="U141" t="n">
-        <v>12787</v>
+        <v>12790</v>
       </c>
       <c r="V141" t="n">
-        <v>31949</v>
+        <v>31960</v>
       </c>
       <c r="W141" t="n">
         <v>37.5</v>
@@ -11457,10 +11457,10 @@
         <v>23350</v>
       </c>
       <c r="N142" t="n">
-        <v>81824</v>
+        <v>81804</v>
       </c>
       <c r="O142" t="n">
-        <v>40076</v>
+        <v>40096</v>
       </c>
       <c r="P142" t="n">
         <v>6539</v>
@@ -11472,16 +11472,16 @@
         <v>16933</v>
       </c>
       <c r="S142" t="n">
-        <v>21804</v>
+        <v>21824</v>
       </c>
       <c r="T142" t="n">
-        <v>12023</v>
+        <v>12029</v>
       </c>
       <c r="U142" t="n">
-        <v>6011</v>
+        <v>6014</v>
       </c>
       <c r="V142" t="n">
-        <v>3770</v>
+        <v>3781</v>
       </c>
       <c r="W142" t="n">
         <v>9.4</v>
@@ -11539,10 +11539,10 @@
         <v>14676</v>
       </c>
       <c r="N143" t="n">
-        <v>73209</v>
+        <v>73189</v>
       </c>
       <c r="O143" t="n">
-        <v>48691</v>
+        <v>48711</v>
       </c>
       <c r="P143" t="n">
         <v>5929</v>
@@ -11554,16 +11554,16 @@
         <v>16933</v>
       </c>
       <c r="S143" t="n">
-        <v>29729</v>
+        <v>29749</v>
       </c>
       <c r="T143" t="n">
-        <v>14607</v>
+        <v>14613</v>
       </c>
       <c r="U143" t="n">
-        <v>7304</v>
+        <v>7307</v>
       </c>
       <c r="V143" t="n">
-        <v>7818</v>
+        <v>7829</v>
       </c>
       <c r="W143" t="n">
         <v>16.1</v>
@@ -11621,10 +11621,10 @@
         <v>24001</v>
       </c>
       <c r="N144" t="n">
-        <v>82509</v>
+        <v>82489</v>
       </c>
       <c r="O144" t="n">
-        <v>39391</v>
+        <v>39411</v>
       </c>
       <c r="P144" t="n">
         <v>5398</v>
@@ -11636,16 +11636,16 @@
         <v>16933</v>
       </c>
       <c r="S144" t="n">
-        <v>21059</v>
+        <v>21079</v>
       </c>
       <c r="T144" t="n">
-        <v>11817</v>
+        <v>11823</v>
       </c>
       <c r="U144" t="n">
-        <v>5909</v>
+        <v>5912</v>
       </c>
       <c r="V144" t="n">
-        <v>3333</v>
+        <v>3344</v>
       </c>
       <c r="W144" t="n">
         <v>8.5</v>
@@ -11703,10 +11703,10 @@
         <v>17253</v>
       </c>
       <c r="N145" t="n">
-        <v>75725</v>
+        <v>75705</v>
       </c>
       <c r="O145" t="n">
-        <v>46175</v>
+        <v>46195</v>
       </c>
       <c r="P145" t="n">
         <v>6539</v>
@@ -11718,16 +11718,16 @@
         <v>16933</v>
       </c>
       <c r="S145" t="n">
-        <v>28252</v>
+        <v>28272</v>
       </c>
       <c r="T145" t="n">
-        <v>13852</v>
+        <v>13858</v>
       </c>
       <c r="U145" t="n">
-        <v>6926</v>
+        <v>6929</v>
       </c>
       <c r="V145" t="n">
-        <v>7473</v>
+        <v>7484</v>
       </c>
       <c r="W145" t="n">
         <v>16.2</v>
@@ -11785,10 +11785,10 @@
         <v>6095</v>
       </c>
       <c r="N146" t="n">
-        <v>70140</v>
+        <v>70120</v>
       </c>
       <c r="O146" t="n">
-        <v>51760</v>
+        <v>51780</v>
       </c>
       <c r="P146" t="n">
         <v>3099</v>
@@ -11800,16 +11800,16 @@
         <v>16933</v>
       </c>
       <c r="S146" t="n">
-        <v>34227</v>
+        <v>34247</v>
       </c>
       <c r="T146" t="n">
-        <v>15528</v>
+        <v>15534</v>
       </c>
       <c r="U146" t="n">
-        <v>7764</v>
+        <v>7767</v>
       </c>
       <c r="V146" t="n">
-        <v>10935</v>
+        <v>10946</v>
       </c>
       <c r="W146" t="n">
         <v>21.1</v>
@@ -11867,10 +11867,10 @@
         <v>10969</v>
       </c>
       <c r="N147" t="n">
-        <v>68909</v>
+        <v>68889</v>
       </c>
       <c r="O147" t="n">
-        <v>52971</v>
+        <v>52991</v>
       </c>
       <c r="P147" t="n">
         <v>3099</v>
@@ -11882,16 +11882,16 @@
         <v>16933</v>
       </c>
       <c r="S147" t="n">
-        <v>35239</v>
+        <v>35259</v>
       </c>
       <c r="T147" t="n">
-        <v>15891</v>
+        <v>15897</v>
       </c>
       <c r="U147" t="n">
-        <v>7946</v>
+        <v>7949</v>
       </c>
       <c r="V147" t="n">
-        <v>11402</v>
+        <v>11413</v>
       </c>
       <c r="W147" t="n">
         <v>21.5</v>
@@ -11949,10 +11949,10 @@
         <v>17255</v>
       </c>
       <c r="N148" t="n">
-        <v>75719</v>
+        <v>75699</v>
       </c>
       <c r="O148" t="n">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="P148" t="n">
         <v>3099</v>
@@ -11964,16 +11964,16 @@
         <v>16933</v>
       </c>
       <c r="S148" t="n">
-        <v>29028</v>
+        <v>29048</v>
       </c>
       <c r="T148" t="n">
-        <v>13848</v>
+        <v>13854</v>
       </c>
       <c r="U148" t="n">
-        <v>6924</v>
+        <v>6927</v>
       </c>
       <c r="V148" t="n">
-        <v>8256</v>
+        <v>8267</v>
       </c>
       <c r="W148" t="n">
         <v>17.9</v>
@@ -12031,10 +12031,10 @@
         <v>23349</v>
       </c>
       <c r="N149" t="n">
-        <v>81813</v>
+        <v>81793</v>
       </c>
       <c r="O149" t="n">
-        <v>40067</v>
+        <v>40087</v>
       </c>
       <c r="P149" t="n">
         <v>3099</v>
@@ -12046,19 +12046,19 @@
         <v>16933</v>
       </c>
       <c r="S149" t="n">
-        <v>22734</v>
+        <v>22754</v>
       </c>
       <c r="T149" t="n">
-        <v>12020</v>
+        <v>12026</v>
       </c>
       <c r="U149" t="n">
-        <v>6010</v>
+        <v>6013</v>
       </c>
       <c r="V149" t="n">
-        <v>4704</v>
+        <v>4715</v>
       </c>
       <c r="W149" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
@@ -12113,10 +12113,10 @@
         <v>8532</v>
       </c>
       <c r="N150" t="n">
-        <v>67388</v>
+        <v>67368</v>
       </c>
       <c r="O150" t="n">
-        <v>54492</v>
+        <v>54512</v>
       </c>
       <c r="P150" t="n">
         <v>9369</v>
@@ -12128,19 +12128,19 @@
         <v>16933</v>
       </c>
       <c r="S150" t="n">
-        <v>30590</v>
+        <v>30610</v>
       </c>
       <c r="T150" t="n">
-        <v>16348</v>
+        <v>16354</v>
       </c>
       <c r="U150" t="n">
-        <v>8174</v>
+        <v>8177</v>
       </c>
       <c r="V150" t="n">
-        <v>6069</v>
+        <v>6080</v>
       </c>
       <c r="W150" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
@@ -12195,10 +12195,10 @@
         <v>12206</v>
       </c>
       <c r="N151" t="n">
-        <v>70433</v>
+        <v>70413</v>
       </c>
       <c r="O151" t="n">
-        <v>50821</v>
+        <v>50841</v>
       </c>
       <c r="P151" t="n">
         <v>4575</v>
@@ -12210,16 +12210,16 @@
         <v>16933</v>
       </c>
       <c r="S151" t="n">
-        <v>33713</v>
+        <v>33733</v>
       </c>
       <c r="T151" t="n">
-        <v>15246</v>
+        <v>15252</v>
       </c>
       <c r="U151" t="n">
-        <v>7623</v>
+        <v>7626</v>
       </c>
       <c r="V151" t="n">
-        <v>10844</v>
+        <v>10855</v>
       </c>
       <c r="W151" t="n">
         <v>21.3</v>
@@ -12277,10 +12277,10 @@
         <v>17907</v>
       </c>
       <c r="N152" t="n">
-        <v>74049</v>
+        <v>74029</v>
       </c>
       <c r="O152" t="n">
-        <v>42851</v>
+        <v>42871</v>
       </c>
       <c r="P152" t="n">
         <v>4282</v>
@@ -12292,16 +12292,16 @@
         <v>16933</v>
       </c>
       <c r="S152" t="n">
-        <v>24236</v>
+        <v>24256</v>
       </c>
       <c r="T152" t="n">
-        <v>12855</v>
+        <v>12861</v>
       </c>
       <c r="U152" t="n">
-        <v>6428</v>
+        <v>6431</v>
       </c>
       <c r="V152" t="n">
-        <v>4953</v>
+        <v>4964</v>
       </c>
       <c r="W152" t="n">
         <v>11.6</v>
@@ -12359,10 +12359,10 @@
         <v>28428</v>
       </c>
       <c r="N153" t="n">
-        <v>84570</v>
+        <v>84550</v>
       </c>
       <c r="O153" t="n">
-        <v>32330</v>
+        <v>32350</v>
       </c>
       <c r="P153" t="n">
         <v>4282</v>
@@ -12374,19 +12374,19 @@
         <v>16933</v>
       </c>
       <c r="S153" t="n">
-        <v>14015</v>
+        <v>14035</v>
       </c>
       <c r="T153" t="n">
-        <v>9699</v>
+        <v>9705</v>
       </c>
       <c r="U153" t="n">
-        <v>4850</v>
+        <v>4852</v>
       </c>
       <c r="V153" t="n">
-        <v>-534</v>
+        <v>-522</v>
       </c>
       <c r="W153" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         <v>26090</v>
       </c>
       <c r="N154" t="n">
-        <v>82232</v>
+        <v>82212</v>
       </c>
       <c r="O154" t="n">
-        <v>34668</v>
+        <v>34688</v>
       </c>
       <c r="P154" t="n">
         <v>7722</v>
@@ -12456,19 +12456,19 @@
         <v>16933</v>
       </c>
       <c r="S154" t="n">
-        <v>15263</v>
+        <v>15283</v>
       </c>
       <c r="T154" t="n">
-        <v>10400</v>
+        <v>10406</v>
       </c>
       <c r="U154" t="n">
-        <v>5200</v>
+        <v>5203</v>
       </c>
       <c r="V154" t="n">
-        <v>-338</v>
+        <v>-327</v>
       </c>
       <c r="W154" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
@@ -12523,10 +12523,10 @@
         <v>468</v>
       </c>
       <c r="N155" t="n">
-        <v>56795</v>
+        <v>56775</v>
       </c>
       <c r="O155" t="n">
-        <v>59381</v>
+        <v>59401</v>
       </c>
       <c r="P155" t="n">
         <v>23377</v>
@@ -12538,16 +12538,16 @@
         <v>17660</v>
       </c>
       <c r="S155" t="n">
-        <v>23643</v>
+        <v>23663</v>
       </c>
       <c r="T155" t="n">
-        <v>17814</v>
+        <v>17820</v>
       </c>
       <c r="U155" t="n">
-        <v>8907</v>
+        <v>8910</v>
       </c>
       <c r="V155" t="n">
-        <v>-3078</v>
+        <v>-3067</v>
       </c>
       <c r="W155" t="n">
         <v>-5.2</v>
@@ -12605,10 +12605,10 @@
         <v>23044</v>
       </c>
       <c r="N156" t="n">
-        <v>83923</v>
+        <v>83903</v>
       </c>
       <c r="O156" t="n">
-        <v>31863</v>
+        <v>31883</v>
       </c>
       <c r="P156" t="n">
         <v>5530</v>
@@ -12620,16 +12620,16 @@
         <v>16933</v>
       </c>
       <c r="S156" t="n">
-        <v>14900</v>
+        <v>14920</v>
       </c>
       <c r="T156" t="n">
-        <v>9559</v>
+        <v>9565</v>
       </c>
       <c r="U156" t="n">
-        <v>4779</v>
+        <v>4782</v>
       </c>
       <c r="V156" t="n">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="W156" t="n">
         <v>1.8</v>
@@ -12687,10 +12687,10 @@
         <v>11872</v>
       </c>
       <c r="N157" t="n">
-        <v>72674</v>
+        <v>72654</v>
       </c>
       <c r="O157" t="n">
-        <v>41912</v>
+        <v>41932</v>
       </c>
       <c r="P157" t="n">
         <v>1000</v>
@@ -12702,16 +12702,16 @@
         <v>16933</v>
       </c>
       <c r="S157" t="n">
-        <v>26279</v>
+        <v>26299</v>
       </c>
       <c r="T157" t="n">
-        <v>12574</v>
+        <v>12580</v>
       </c>
       <c r="U157" t="n">
-        <v>6287</v>
+        <v>6290</v>
       </c>
       <c r="V157" t="n">
-        <v>7419</v>
+        <v>7430</v>
       </c>
       <c r="W157" t="n">
         <v>17.7</v>
@@ -12847,10 +12847,10 @@
         <v>27902</v>
       </c>
       <c r="N159" t="n">
-        <v>81279</v>
+        <v>81259</v>
       </c>
       <c r="O159" t="n">
-        <v>29776</v>
+        <v>29796</v>
       </c>
       <c r="P159" t="n">
         <v>6374</v>
@@ -12862,16 +12862,16 @@
         <v>16933</v>
       </c>
       <c r="S159" t="n">
-        <v>11368</v>
+        <v>11388</v>
       </c>
       <c r="T159" t="n">
-        <v>8933</v>
+        <v>8939</v>
       </c>
       <c r="U159" t="n">
-        <v>4466</v>
+        <v>4469</v>
       </c>
       <c r="V159" t="n">
-        <v>-2031</v>
+        <v>-2020</v>
       </c>
       <c r="W159" t="n">
         <v>-6.8</v>
@@ -13003,10 +13003,10 @@
         <v>6143</v>
       </c>
       <c r="N161" t="n">
-        <v>63949</v>
+        <v>63929</v>
       </c>
       <c r="O161" t="n">
-        <v>44908</v>
+        <v>44928</v>
       </c>
       <c r="P161" t="n">
         <v>1000</v>
@@ -13018,16 +13018,16 @@
         <v>16933</v>
       </c>
       <c r="S161" t="n">
-        <v>29475</v>
+        <v>29495</v>
       </c>
       <c r="T161" t="n">
-        <v>13472</v>
+        <v>13478</v>
       </c>
       <c r="U161" t="n">
-        <v>6736</v>
+        <v>6739</v>
       </c>
       <c r="V161" t="n">
-        <v>9266</v>
+        <v>9277</v>
       </c>
       <c r="W161" t="n">
         <v>20.6</v>
@@ -13085,10 +13085,10 @@
         <v>11586</v>
       </c>
       <c r="N162" t="n">
-        <v>69392</v>
+        <v>69372</v>
       </c>
       <c r="O162" t="n">
-        <v>39465</v>
+        <v>39485</v>
       </c>
       <c r="P162" t="n">
         <v>1000</v>
@@ -13100,19 +13100,19 @@
         <v>16933</v>
       </c>
       <c r="S162" t="n">
-        <v>24131</v>
+        <v>24151</v>
       </c>
       <c r="T162" t="n">
-        <v>11840</v>
+        <v>11846</v>
       </c>
       <c r="U162" t="n">
-        <v>5920</v>
+        <v>5923</v>
       </c>
       <c r="V162" t="n">
-        <v>6372</v>
+        <v>6383</v>
       </c>
       <c r="W162" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
@@ -13167,10 +13167,10 @@
         <v>11548</v>
       </c>
       <c r="N163" t="n">
-        <v>68998</v>
+        <v>68978</v>
       </c>
       <c r="O163" t="n">
-        <v>39176</v>
+        <v>39196</v>
       </c>
       <c r="P163" t="n">
         <v>3041</v>
@@ -13182,16 +13182,16 @@
         <v>16933</v>
       </c>
       <c r="S163" t="n">
-        <v>23701</v>
+        <v>23721</v>
       </c>
       <c r="T163" t="n">
-        <v>11753</v>
+        <v>11759</v>
       </c>
       <c r="U163" t="n">
-        <v>5876</v>
+        <v>5879</v>
       </c>
       <c r="V163" t="n">
-        <v>6072</v>
+        <v>6083</v>
       </c>
       <c r="W163" t="n">
         <v>15.5</v>
@@ -13249,10 +13249,10 @@
         <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>50997</v>
+        <v>50977</v>
       </c>
       <c r="O164" t="n">
-        <v>56776</v>
+        <v>56796</v>
       </c>
       <c r="P164" t="n">
         <v>1000</v>
@@ -13264,16 +13264,16 @@
         <v>17660</v>
       </c>
       <c r="S164" t="n">
-        <v>40416</v>
+        <v>40436</v>
       </c>
       <c r="T164" t="n">
-        <v>17033</v>
+        <v>17039</v>
       </c>
       <c r="U164" t="n">
-        <v>8516</v>
+        <v>8519</v>
       </c>
       <c r="V164" t="n">
-        <v>14867</v>
+        <v>14878</v>
       </c>
       <c r="W164" t="n">
         <v>26.2</v>
@@ -13331,10 +13331,10 @@
         <v>5389</v>
       </c>
       <c r="N165" t="n">
-        <v>57394</v>
+        <v>57374</v>
       </c>
       <c r="O165" t="n">
-        <v>50379</v>
+        <v>50399</v>
       </c>
       <c r="P165" t="n">
         <v>3099</v>
@@ -13346,16 +13346,16 @@
         <v>17660</v>
       </c>
       <c r="S165" t="n">
-        <v>32220</v>
+        <v>32240</v>
       </c>
       <c r="T165" t="n">
-        <v>15114</v>
+        <v>15120</v>
       </c>
       <c r="U165" t="n">
-        <v>7557</v>
+        <v>7560</v>
       </c>
       <c r="V165" t="n">
-        <v>9549</v>
+        <v>9560</v>
       </c>
       <c r="W165" t="n">
         <v>19</v>
@@ -13413,10 +13413,10 @@
         <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>57358</v>
+        <v>57338</v>
       </c>
       <c r="O166" t="n">
-        <v>50415</v>
+        <v>50435</v>
       </c>
       <c r="P166" t="n">
         <v>4136</v>
@@ -13428,16 +13428,16 @@
         <v>17660</v>
       </c>
       <c r="S166" t="n">
-        <v>32919</v>
+        <v>32939</v>
       </c>
       <c r="T166" t="n">
-        <v>15124</v>
+        <v>15130</v>
       </c>
       <c r="U166" t="n">
-        <v>7562</v>
+        <v>7565</v>
       </c>
       <c r="V166" t="n">
-        <v>10232</v>
+        <v>10243</v>
       </c>
       <c r="W166" t="n">
         <v>20.3</v>
@@ -13495,10 +13495,10 @@
         <v>554</v>
       </c>
       <c r="N167" t="n">
-        <v>51556</v>
+        <v>51536</v>
       </c>
       <c r="O167" t="n">
-        <v>54344</v>
+        <v>54364</v>
       </c>
       <c r="P167" t="n">
         <v>3154</v>
@@ -13510,19 +13510,19 @@
         <v>17189</v>
       </c>
       <c r="S167" t="n">
-        <v>36600</v>
+        <v>36620</v>
       </c>
       <c r="T167" t="n">
-        <v>16303</v>
+        <v>16309</v>
       </c>
       <c r="U167" t="n">
-        <v>8152</v>
+        <v>8155</v>
       </c>
       <c r="V167" t="n">
-        <v>12145</v>
+        <v>12156</v>
       </c>
       <c r="W167" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
@@ -13577,10 +13577,10 @@
         <v>6265</v>
       </c>
       <c r="N168" t="n">
-        <v>57264</v>
+        <v>57244</v>
       </c>
       <c r="O168" t="n">
-        <v>48636</v>
+        <v>48656</v>
       </c>
       <c r="P168" t="n">
         <v>3813</v>
@@ -13592,19 +13592,19 @@
         <v>17660</v>
       </c>
       <c r="S168" t="n">
-        <v>30563</v>
+        <v>30583</v>
       </c>
       <c r="T168" t="n">
-        <v>14591</v>
+        <v>14597</v>
       </c>
       <c r="U168" t="n">
-        <v>7295</v>
+        <v>7298</v>
       </c>
       <c r="V168" t="n">
-        <v>8677</v>
+        <v>8688</v>
       </c>
       <c r="W168" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
@@ -13659,10 +13659,10 @@
         <v>6266</v>
       </c>
       <c r="N169" t="n">
-        <v>69303</v>
+        <v>57245</v>
       </c>
       <c r="O169" t="n">
-        <v>36597</v>
+        <v>48655</v>
       </c>
       <c r="P169" t="n">
         <v>0</v>
@@ -13674,19 +13674,19 @@
         <v>17660</v>
       </c>
       <c r="S169" t="n">
-        <v>28875</v>
+        <v>40933</v>
       </c>
       <c r="T169" t="n">
-        <v>10979</v>
+        <v>14596</v>
       </c>
       <c r="U169" t="n">
-        <v>5490</v>
+        <v>7298</v>
       </c>
       <c r="V169" t="n">
-        <v>12406</v>
+        <v>19038</v>
       </c>
       <c r="W169" t="n">
-        <v>33.9</v>
+        <v>39.1</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
@@ -13741,10 +13741,10 @@
         <v>29625</v>
       </c>
       <c r="N170" t="n">
-        <v>80726</v>
+        <v>80706</v>
       </c>
       <c r="O170" t="n">
-        <v>25174</v>
+        <v>25194</v>
       </c>
       <c r="P170" t="n">
         <v>3099</v>
@@ -13756,19 +13756,19 @@
         <v>17189</v>
       </c>
       <c r="S170" t="n">
-        <v>7886</v>
+        <v>7906</v>
       </c>
       <c r="T170" t="n">
-        <v>7552</v>
+        <v>7558</v>
       </c>
       <c r="U170" t="n">
-        <v>3776</v>
+        <v>3779</v>
       </c>
       <c r="V170" t="n">
-        <v>-3442</v>
+        <v>-3431</v>
       </c>
       <c r="W170" t="n">
-        <v>-13.7</v>
+        <v>-13.6</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
@@ -13823,10 +13823,10 @@
         <v>553</v>
       </c>
       <c r="N171" t="n">
-        <v>61566</v>
+        <v>61546</v>
       </c>
       <c r="O171" t="n">
-        <v>44334</v>
+        <v>44354</v>
       </c>
       <c r="P171" t="n">
         <v>3099</v>
@@ -13838,16 +13838,16 @@
         <v>17189</v>
       </c>
       <c r="S171" t="n">
-        <v>26545</v>
+        <v>26565</v>
       </c>
       <c r="T171" t="n">
-        <v>13300</v>
+        <v>13306</v>
       </c>
       <c r="U171" t="n">
-        <v>6650</v>
+        <v>6653</v>
       </c>
       <c r="V171" t="n">
-        <v>6595</v>
+        <v>6606</v>
       </c>
       <c r="W171" t="n">
         <v>14.9</v>
@@ -13905,10 +13905,10 @@
         <v>7265</v>
       </c>
       <c r="N172" t="n">
-        <v>57022</v>
+        <v>57002</v>
       </c>
       <c r="O172" t="n">
-        <v>46759</v>
+        <v>46779</v>
       </c>
       <c r="P172" t="n">
         <v>6009</v>
@@ -13920,16 +13920,16 @@
         <v>17189</v>
       </c>
       <c r="S172" t="n">
-        <v>29910</v>
+        <v>29930</v>
       </c>
       <c r="T172" t="n">
-        <v>14028</v>
+        <v>14034</v>
       </c>
       <c r="U172" t="n">
-        <v>7014</v>
+        <v>7017</v>
       </c>
       <c r="V172" t="n">
-        <v>8868</v>
+        <v>8879</v>
       </c>
       <c r="W172" t="n">
         <v>19</v>
@@ -13987,10 +13987,10 @@
         <v>11314</v>
       </c>
       <c r="N173" t="n">
-        <v>66275</v>
+        <v>66255</v>
       </c>
       <c r="O173" t="n">
-        <v>37141</v>
+        <v>37161</v>
       </c>
       <c r="P173" t="n">
         <v>0</v>
@@ -14002,16 +14002,16 @@
         <v>16933</v>
       </c>
       <c r="S173" t="n">
-        <v>24508</v>
+        <v>24528</v>
       </c>
       <c r="T173" t="n">
-        <v>11142</v>
+        <v>11148</v>
       </c>
       <c r="U173" t="n">
-        <v>5571</v>
+        <v>5574</v>
       </c>
       <c r="V173" t="n">
-        <v>7795</v>
+        <v>7806</v>
       </c>
       <c r="W173" t="n">
         <v>21</v>
@@ -14069,10 +14069,10 @@
         <v>20110</v>
       </c>
       <c r="N174" t="n">
-        <v>70296</v>
+        <v>70276</v>
       </c>
       <c r="O174" t="n">
-        <v>32604</v>
+        <v>32624</v>
       </c>
       <c r="P174" t="n">
         <v>3477</v>
@@ -14084,16 +14084,16 @@
         <v>14537</v>
       </c>
       <c r="S174" t="n">
-        <v>17890</v>
+        <v>17910</v>
       </c>
       <c r="T174" t="n">
-        <v>9781</v>
+        <v>9787</v>
       </c>
       <c r="U174" t="n">
-        <v>4891</v>
+        <v>4894</v>
       </c>
       <c r="V174" t="n">
-        <v>3218</v>
+        <v>3229</v>
       </c>
       <c r="W174" t="n">
         <v>9.9</v>
@@ -14151,10 +14151,10 @@
         <v>12907</v>
       </c>
       <c r="N175" t="n">
-        <v>62064</v>
+        <v>62044</v>
       </c>
       <c r="O175" t="n">
-        <v>40836</v>
+        <v>40856</v>
       </c>
       <c r="P175" t="n">
         <v>5117</v>
@@ -14166,16 +14166,16 @@
         <v>14537</v>
       </c>
       <c r="S175" t="n">
-        <v>26332</v>
+        <v>26352</v>
       </c>
       <c r="T175" t="n">
-        <v>12251</v>
+        <v>12257</v>
       </c>
       <c r="U175" t="n">
-        <v>6125</v>
+        <v>6128</v>
       </c>
       <c r="V175" t="n">
-        <v>7956</v>
+        <v>7967</v>
       </c>
       <c r="W175" t="n">
         <v>19.5</v>
@@ -14233,10 +14233,10 @@
         <v>12907</v>
       </c>
       <c r="N176" t="n">
-        <v>62054</v>
+        <v>62034</v>
       </c>
       <c r="O176" t="n">
-        <v>40826</v>
+        <v>40846</v>
       </c>
       <c r="P176" t="n">
         <v>5354</v>
@@ -14248,16 +14248,16 @@
         <v>14537</v>
       </c>
       <c r="S176" t="n">
-        <v>26234</v>
+        <v>26254</v>
       </c>
       <c r="T176" t="n">
-        <v>12248</v>
+        <v>12254</v>
       </c>
       <c r="U176" t="n">
-        <v>6124</v>
+        <v>6127</v>
       </c>
       <c r="V176" t="n">
-        <v>7862</v>
+        <v>7873</v>
       </c>
       <c r="W176" t="n">
         <v>19.3</v>
@@ -14315,10 +14315,10 @@
         <v>12907</v>
       </c>
       <c r="N177" t="n">
-        <v>62054</v>
+        <v>62034</v>
       </c>
       <c r="O177" t="n">
-        <v>40826</v>
+        <v>40846</v>
       </c>
       <c r="P177" t="n">
         <v>3652</v>
@@ -14330,16 +14330,16 @@
         <v>14537</v>
       </c>
       <c r="S177" t="n">
-        <v>25037</v>
+        <v>25057</v>
       </c>
       <c r="T177" t="n">
-        <v>12248</v>
+        <v>12254</v>
       </c>
       <c r="U177" t="n">
-        <v>6124</v>
+        <v>6127</v>
       </c>
       <c r="V177" t="n">
-        <v>6665</v>
+        <v>6676</v>
       </c>
       <c r="W177" t="n">
         <v>16.3</v>
@@ -14397,10 +14397,10 @@
         <v>12907</v>
       </c>
       <c r="N178" t="n">
-        <v>62743</v>
+        <v>62723</v>
       </c>
       <c r="O178" t="n">
-        <v>39433</v>
+        <v>39453</v>
       </c>
       <c r="P178" t="n">
         <v>4430</v>
@@ -14412,16 +14412,16 @@
         <v>14537</v>
       </c>
       <c r="S178" t="n">
-        <v>24666</v>
+        <v>24686</v>
       </c>
       <c r="T178" t="n">
-        <v>11830</v>
+        <v>11836</v>
       </c>
       <c r="U178" t="n">
-        <v>5915</v>
+        <v>5918</v>
       </c>
       <c r="V178" t="n">
-        <v>6921</v>
+        <v>6932</v>
       </c>
       <c r="W178" t="n">
         <v>17.6</v>
@@ -14557,10 +14557,10 @@
         <v>7027</v>
       </c>
       <c r="N180" t="n">
-        <v>55461</v>
+        <v>55441</v>
       </c>
       <c r="O180" t="n">
-        <v>44925</v>
+        <v>44945</v>
       </c>
       <c r="P180" t="n">
         <v>5929</v>
@@ -14572,16 +14572,16 @@
         <v>20103</v>
       </c>
       <c r="S180" t="n">
-        <v>23092</v>
+        <v>23112</v>
       </c>
       <c r="T180" t="n">
-        <v>13478</v>
+        <v>13484</v>
       </c>
       <c r="U180" t="n">
-        <v>6739</v>
+        <v>6742</v>
       </c>
       <c r="V180" t="n">
-        <v>2876</v>
+        <v>2887</v>
       </c>
       <c r="W180" t="n">
         <v>6.4</v>
@@ -14639,10 +14639,10 @@
         <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>46780</v>
+        <v>46760</v>
       </c>
       <c r="O181" t="n">
-        <v>50120</v>
+        <v>50140</v>
       </c>
       <c r="P181" t="n">
         <v>3099</v>
@@ -14654,16 +14654,16 @@
         <v>14537</v>
       </c>
       <c r="S181" t="n">
-        <v>35083</v>
+        <v>35103</v>
       </c>
       <c r="T181" t="n">
-        <v>15036</v>
+        <v>15042</v>
       </c>
       <c r="U181" t="n">
-        <v>7518</v>
+        <v>7521</v>
       </c>
       <c r="V181" t="n">
-        <v>12529</v>
+        <v>12540</v>
       </c>
       <c r="W181" t="n">
         <v>25</v>
@@ -14721,10 +14721,10 @@
         <v>12907</v>
       </c>
       <c r="N182" t="n">
-        <v>63192</v>
+        <v>63172</v>
       </c>
       <c r="O182" t="n">
-        <v>32031</v>
+        <v>32051</v>
       </c>
       <c r="P182" t="n">
         <v>5451</v>
@@ -14736,16 +14736,16 @@
         <v>14537</v>
       </c>
       <c r="S182" t="n">
-        <v>15943</v>
+        <v>15963</v>
       </c>
       <c r="T182" t="n">
-        <v>9609</v>
+        <v>9615</v>
       </c>
       <c r="U182" t="n">
-        <v>4805</v>
+        <v>4808</v>
       </c>
       <c r="V182" t="n">
-        <v>1529</v>
+        <v>1540</v>
       </c>
       <c r="W182" t="n">
         <v>4.8</v>
@@ -14803,10 +14803,10 @@
         <v>7448</v>
       </c>
       <c r="N183" t="n">
-        <v>53239</v>
+        <v>53219</v>
       </c>
       <c r="O183" t="n">
-        <v>39661</v>
+        <v>39681</v>
       </c>
       <c r="P183" t="n">
         <v>5137</v>
@@ -14818,16 +14818,16 @@
         <v>17660</v>
       </c>
       <c r="S183" t="n">
-        <v>22114</v>
+        <v>22134</v>
       </c>
       <c r="T183" t="n">
-        <v>11898</v>
+        <v>11904</v>
       </c>
       <c r="U183" t="n">
-        <v>5949</v>
+        <v>5952</v>
       </c>
       <c r="V183" t="n">
-        <v>4267</v>
+        <v>4278</v>
       </c>
       <c r="W183" t="n">
         <v>10.8</v>
@@ -14885,10 +14885,10 @@
         <v>27597</v>
       </c>
       <c r="N184" t="n">
-        <v>73186</v>
+        <v>73166</v>
       </c>
       <c r="O184" t="n">
-        <v>19714</v>
+        <v>19734</v>
       </c>
       <c r="P184" t="n">
         <v>3559</v>
@@ -14900,19 +14900,19 @@
         <v>17660</v>
       </c>
       <c r="S184" t="n">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="T184" t="n">
-        <v>5914</v>
+        <v>5920</v>
       </c>
       <c r="U184" t="n">
-        <v>2957</v>
+        <v>2960</v>
       </c>
       <c r="V184" t="n">
-        <v>-7977</v>
+        <v>-7966</v>
       </c>
       <c r="W184" t="n">
-        <v>-40.5</v>
+        <v>-40.4</v>
       </c>
       <c r="X184" t="inlineStr">
         <is>
@@ -14967,10 +14967,10 @@
         <v>7473</v>
       </c>
       <c r="N185" t="n">
-        <v>52323</v>
+        <v>52303</v>
       </c>
       <c r="O185" t="n">
-        <v>40577</v>
+        <v>40597</v>
       </c>
       <c r="P185" t="n">
         <v>3932</v>
@@ -14982,16 +14982,16 @@
         <v>17660</v>
       </c>
       <c r="S185" t="n">
-        <v>23285</v>
+        <v>23305</v>
       </c>
       <c r="T185" t="n">
-        <v>12173</v>
+        <v>12179</v>
       </c>
       <c r="U185" t="n">
-        <v>6087</v>
+        <v>6090</v>
       </c>
       <c r="V185" t="n">
-        <v>5025</v>
+        <v>5036</v>
       </c>
       <c r="W185" t="n">
         <v>12.4</v>
@@ -15049,10 +15049,10 @@
         <v>8361</v>
       </c>
       <c r="N186" t="n">
-        <v>53297</v>
+        <v>53277</v>
       </c>
       <c r="O186" t="n">
-        <v>39603</v>
+        <v>39623</v>
       </c>
       <c r="P186" t="n">
         <v>3139</v>
@@ -15064,16 +15064,16 @@
         <v>17660</v>
       </c>
       <c r="S186" t="n">
-        <v>22303</v>
+        <v>22323</v>
       </c>
       <c r="T186" t="n">
-        <v>11881</v>
+        <v>11887</v>
       </c>
       <c r="U186" t="n">
-        <v>5940</v>
+        <v>5943</v>
       </c>
       <c r="V186" t="n">
-        <v>4482</v>
+        <v>4493</v>
       </c>
       <c r="W186" t="n">
         <v>11.3</v>
@@ -15131,10 +15131,10 @@
         <v>27597</v>
       </c>
       <c r="N187" t="n">
-        <v>76503</v>
+        <v>76483</v>
       </c>
       <c r="O187" t="n">
-        <v>16397</v>
+        <v>16417</v>
       </c>
       <c r="P187" t="n">
         <v>3559</v>
@@ -15146,19 +15146,19 @@
         <v>17660</v>
       </c>
       <c r="S187" t="n">
-        <v>-1722</v>
+        <v>-1702</v>
       </c>
       <c r="T187" t="n">
-        <v>4919</v>
+        <v>4925</v>
       </c>
       <c r="U187" t="n">
-        <v>2460</v>
+        <v>2463</v>
       </c>
       <c r="V187" t="n">
-        <v>-9101</v>
+        <v>-9090</v>
       </c>
       <c r="W187" t="n">
-        <v>-55.5</v>
+        <v>-55.4</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
@@ -15213,10 +15213,10 @@
         <v>8361</v>
       </c>
       <c r="N188" t="n">
-        <v>53297</v>
+        <v>53277</v>
       </c>
       <c r="O188" t="n">
-        <v>39603</v>
+        <v>39623</v>
       </c>
       <c r="P188" t="n">
         <v>2948</v>
@@ -15228,19 +15228,19 @@
         <v>17660</v>
       </c>
       <c r="S188" t="n">
-        <v>22394</v>
+        <v>22414</v>
       </c>
       <c r="T188" t="n">
-        <v>11881</v>
+        <v>11887</v>
       </c>
       <c r="U188" t="n">
-        <v>5940</v>
+        <v>5943</v>
       </c>
       <c r="V188" t="n">
-        <v>4573</v>
+        <v>4584</v>
       </c>
       <c r="W188" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
@@ -15295,10 +15295,10 @@
         <v>7448</v>
       </c>
       <c r="N189" t="n">
-        <v>52310</v>
+        <v>52290</v>
       </c>
       <c r="O189" t="n">
-        <v>40590</v>
+        <v>40610</v>
       </c>
       <c r="P189" t="n">
         <v>7335</v>
@@ -15310,16 +15310,16 @@
         <v>17660</v>
       </c>
       <c r="S189" t="n">
-        <v>20645</v>
+        <v>20665</v>
       </c>
       <c r="T189" t="n">
-        <v>12177</v>
+        <v>12183</v>
       </c>
       <c r="U189" t="n">
-        <v>6088</v>
+        <v>6092</v>
       </c>
       <c r="V189" t="n">
-        <v>2380</v>
+        <v>2390</v>
       </c>
       <c r="W189" t="n">
         <v>5.9</v>
@@ -15377,10 +15377,10 @@
         <v>7449</v>
       </c>
       <c r="N190" t="n">
-        <v>52312</v>
+        <v>52292</v>
       </c>
       <c r="O190" t="n">
-        <v>40588</v>
+        <v>40608</v>
       </c>
       <c r="P190" t="n">
         <v>6538</v>
@@ -15392,16 +15392,16 @@
         <v>17660</v>
       </c>
       <c r="S190" t="n">
-        <v>19590</v>
+        <v>19610</v>
       </c>
       <c r="T190" t="n">
-        <v>12176</v>
+        <v>12182</v>
       </c>
       <c r="U190" t="n">
-        <v>6088</v>
+        <v>6091</v>
       </c>
       <c r="V190" t="n">
-        <v>1325</v>
+        <v>1336</v>
       </c>
       <c r="W190" t="n">
         <v>3.3</v>
@@ -15459,10 +15459,10 @@
         <v>27597</v>
       </c>
       <c r="N191" t="n">
-        <v>72257</v>
+        <v>72237</v>
       </c>
       <c r="O191" t="n">
-        <v>20643</v>
+        <v>20663</v>
       </c>
       <c r="P191" t="n">
         <v>3559</v>
@@ -15474,19 +15474,19 @@
         <v>17660</v>
       </c>
       <c r="S191" t="n">
-        <v>2123</v>
+        <v>2143</v>
       </c>
       <c r="T191" t="n">
-        <v>6193</v>
+        <v>6199</v>
       </c>
       <c r="U191" t="n">
-        <v>3096</v>
+        <v>3099</v>
       </c>
       <c r="V191" t="n">
-        <v>-7166</v>
+        <v>-7155</v>
       </c>
       <c r="W191" t="n">
-        <v>-34.7</v>
+        <v>-34.6</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
@@ -15541,10 +15541,10 @@
         <v>27597</v>
       </c>
       <c r="N192" t="n">
-        <v>72257</v>
+        <v>72237</v>
       </c>
       <c r="O192" t="n">
-        <v>20643</v>
+        <v>20663</v>
       </c>
       <c r="P192" t="n">
         <v>611</v>
@@ -15556,19 +15556,19 @@
         <v>17660</v>
       </c>
       <c r="S192" t="n">
-        <v>7371</v>
+        <v>7391</v>
       </c>
       <c r="T192" t="n">
-        <v>6193</v>
+        <v>6199</v>
       </c>
       <c r="U192" t="n">
-        <v>3096</v>
+        <v>3099</v>
       </c>
       <c r="V192" t="n">
-        <v>-1918</v>
+        <v>-1907</v>
       </c>
       <c r="W192" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
@@ -15623,10 +15623,10 @@
         <v>8361</v>
       </c>
       <c r="N193" t="n">
-        <v>52323</v>
+        <v>52303</v>
       </c>
       <c r="O193" t="n">
-        <v>40577</v>
+        <v>40597</v>
       </c>
       <c r="P193" t="n">
         <v>0</v>
@@ -15638,16 +15638,16 @@
         <v>17660</v>
       </c>
       <c r="S193" t="n">
-        <v>29567</v>
+        <v>29587</v>
       </c>
       <c r="T193" t="n">
-        <v>12173</v>
+        <v>12179</v>
       </c>
       <c r="U193" t="n">
-        <v>6087</v>
+        <v>6090</v>
       </c>
       <c r="V193" t="n">
-        <v>11307</v>
+        <v>11318</v>
       </c>
       <c r="W193" t="n">
         <v>27.9</v>
@@ -15705,10 +15705,10 @@
         <v>23882</v>
       </c>
       <c r="N194" t="n">
-        <v>68542</v>
+        <v>68522</v>
       </c>
       <c r="O194" t="n">
-        <v>24358</v>
+        <v>24378</v>
       </c>
       <c r="P194" t="n">
         <v>611</v>
@@ -15720,19 +15720,19 @@
         <v>17660</v>
       </c>
       <c r="S194" t="n">
-        <v>11137</v>
+        <v>11157</v>
       </c>
       <c r="T194" t="n">
-        <v>7307</v>
+        <v>7313</v>
       </c>
       <c r="U194" t="n">
-        <v>3654</v>
+        <v>3657</v>
       </c>
       <c r="V194" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="W194" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
@@ -15787,10 +15787,10 @@
         <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>49557</v>
+        <v>49537</v>
       </c>
       <c r="O195" t="n">
-        <v>43343</v>
+        <v>43363</v>
       </c>
       <c r="P195" t="n">
         <v>0</v>
@@ -15802,16 +15802,16 @@
         <v>13664</v>
       </c>
       <c r="S195" t="n">
-        <v>32979</v>
+        <v>32999</v>
       </c>
       <c r="T195" t="n">
-        <v>13003</v>
+        <v>13009</v>
       </c>
       <c r="U195" t="n">
-        <v>6501</v>
+        <v>6504</v>
       </c>
       <c r="V195" t="n">
-        <v>13475</v>
+        <v>13486</v>
       </c>
       <c r="W195" t="n">
         <v>31.1</v>
@@ -15869,10 +15869,10 @@
         <v>4644</v>
       </c>
       <c r="N196" t="n">
-        <v>49182</v>
+        <v>49162</v>
       </c>
       <c r="O196" t="n">
-        <v>43698</v>
+        <v>43718</v>
       </c>
       <c r="P196" t="n">
         <v>0</v>
@@ -15884,19 +15884,19 @@
         <v>17660</v>
       </c>
       <c r="S196" t="n">
-        <v>28338</v>
+        <v>28358</v>
       </c>
       <c r="T196" t="n">
-        <v>13109</v>
+        <v>13115</v>
       </c>
       <c r="U196" t="n">
-        <v>6555</v>
+        <v>6558</v>
       </c>
       <c r="V196" t="n">
-        <v>8674</v>
+        <v>8685</v>
       </c>
       <c r="W196" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="X196" t="inlineStr"/>
     </row>
@@ -15947,10 +15947,10 @@
         <v>945</v>
       </c>
       <c r="N197" t="n">
-        <v>51607</v>
+        <v>51587</v>
       </c>
       <c r="O197" t="n">
-        <v>40753</v>
+        <v>40773</v>
       </c>
       <c r="P197" t="n">
         <v>4720</v>
@@ -15962,16 +15962,16 @@
         <v>17660</v>
       </c>
       <c r="S197" t="n">
-        <v>23223</v>
+        <v>23243</v>
       </c>
       <c r="T197" t="n">
-        <v>12226</v>
+        <v>12232</v>
       </c>
       <c r="U197" t="n">
-        <v>6113</v>
+        <v>6116</v>
       </c>
       <c r="V197" t="n">
-        <v>4884</v>
+        <v>4895</v>
       </c>
       <c r="W197" t="n">
         <v>12</v>
@@ -16029,10 +16029,10 @@
         <v>25694</v>
       </c>
       <c r="N198" t="n">
-        <v>70049</v>
+        <v>70029</v>
       </c>
       <c r="O198" t="n">
-        <v>22207</v>
+        <v>22227</v>
       </c>
       <c r="P198" t="n">
         <v>9546</v>
@@ -16044,19 +16044,19 @@
         <v>17660</v>
       </c>
       <c r="S198" t="n">
-        <v>1001</v>
+        <v>1021</v>
       </c>
       <c r="T198" t="n">
-        <v>6662</v>
+        <v>6668</v>
       </c>
       <c r="U198" t="n">
-        <v>3331</v>
+        <v>3334</v>
       </c>
       <c r="V198" t="n">
-        <v>-8992</v>
+        <v>-8981</v>
       </c>
       <c r="W198" t="n">
-        <v>-40.5</v>
+        <v>-40.4</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
@@ -16111,10 +16111,10 @@
         <v>23038</v>
       </c>
       <c r="N199" t="n">
-        <v>66688</v>
+        <v>66668</v>
       </c>
       <c r="O199" t="n">
-        <v>25212</v>
+        <v>25232</v>
       </c>
       <c r="P199" t="n">
         <v>2500</v>
@@ -16126,19 +16126,19 @@
         <v>11759</v>
       </c>
       <c r="S199" t="n">
-        <v>14053</v>
+        <v>14073</v>
       </c>
       <c r="T199" t="n">
-        <v>7564</v>
+        <v>7570</v>
       </c>
       <c r="U199" t="n">
-        <v>3782</v>
+        <v>3785</v>
       </c>
       <c r="V199" t="n">
-        <v>2708</v>
+        <v>2719</v>
       </c>
       <c r="W199" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="X199" t="inlineStr"/>
     </row>
@@ -16189,10 +16189,10 @@
         <v>13590</v>
       </c>
       <c r="N200" t="n">
-        <v>57444</v>
+        <v>57424</v>
       </c>
       <c r="O200" t="n">
-        <v>34456</v>
+        <v>34476</v>
       </c>
       <c r="P200" t="n">
         <v>1000</v>
@@ -16204,16 +16204,16 @@
         <v>11759</v>
       </c>
       <c r="S200" t="n">
-        <v>24396</v>
+        <v>24416</v>
       </c>
       <c r="T200" t="n">
-        <v>10337</v>
+        <v>10343</v>
       </c>
       <c r="U200" t="n">
-        <v>5168</v>
+        <v>5171</v>
       </c>
       <c r="V200" t="n">
-        <v>8891</v>
+        <v>8902</v>
       </c>
       <c r="W200" t="n">
         <v>25.8</v>
@@ -16267,10 +16267,10 @@
         <v>6847</v>
       </c>
       <c r="N201" t="n">
-        <v>51180</v>
+        <v>51160</v>
       </c>
       <c r="O201" t="n">
-        <v>38720</v>
+        <v>38740</v>
       </c>
       <c r="P201" t="n">
         <v>4992</v>
@@ -16282,16 +16282,16 @@
         <v>17189</v>
       </c>
       <c r="S201" t="n">
-        <v>21139</v>
+        <v>21159</v>
       </c>
       <c r="T201" t="n">
-        <v>11616</v>
+        <v>11622</v>
       </c>
       <c r="U201" t="n">
-        <v>5808</v>
+        <v>5811</v>
       </c>
       <c r="V201" t="n">
-        <v>3715</v>
+        <v>3726</v>
       </c>
       <c r="W201" t="n">
         <v>9.6</v>
@@ -16349,10 +16349,10 @@
         <v>6293</v>
       </c>
       <c r="N202" t="n">
-        <v>50595</v>
+        <v>50575</v>
       </c>
       <c r="O202" t="n">
-        <v>39305</v>
+        <v>39325</v>
       </c>
       <c r="P202" t="n">
         <v>4286</v>
@@ -16364,16 +16364,16 @@
         <v>17189</v>
       </c>
       <c r="S202" t="n">
-        <v>21729</v>
+        <v>21749</v>
       </c>
       <c r="T202" t="n">
-        <v>11792</v>
+        <v>11798</v>
       </c>
       <c r="U202" t="n">
-        <v>5896</v>
+        <v>5899</v>
       </c>
       <c r="V202" t="n">
-        <v>4042</v>
+        <v>4053</v>
       </c>
       <c r="W202" t="n">
         <v>10.3</v>
@@ -16431,10 +16431,10 @@
         <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>43397</v>
+        <v>43377</v>
       </c>
       <c r="O203" t="n">
-        <v>46503</v>
+        <v>46523</v>
       </c>
       <c r="P203" t="n">
         <v>6049</v>
@@ -16446,19 +16446,19 @@
         <v>17189</v>
       </c>
       <c r="S203" t="n">
-        <v>28715</v>
+        <v>28735</v>
       </c>
       <c r="T203" t="n">
-        <v>13951</v>
+        <v>13957</v>
       </c>
       <c r="U203" t="n">
-        <v>6975</v>
+        <v>6978</v>
       </c>
       <c r="V203" t="n">
-        <v>7789</v>
+        <v>7800</v>
       </c>
       <c r="W203" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
@@ -16513,10 +16513,10 @@
         <v>8091</v>
       </c>
       <c r="N204" t="n">
-        <v>51495</v>
+        <v>51475</v>
       </c>
       <c r="O204" t="n">
-        <v>38405</v>
+        <v>38425</v>
       </c>
       <c r="P204" t="n">
         <v>2948</v>
@@ -16528,16 +16528,16 @@
         <v>17189</v>
       </c>
       <c r="S204" t="n">
-        <v>20767</v>
+        <v>20787</v>
       </c>
       <c r="T204" t="n">
-        <v>11522</v>
+        <v>11528</v>
       </c>
       <c r="U204" t="n">
-        <v>5761</v>
+        <v>5764</v>
       </c>
       <c r="V204" t="n">
-        <v>3485</v>
+        <v>3496</v>
       </c>
       <c r="W204" t="n">
         <v>9.1</v>
@@ -16595,10 +16595,10 @@
         <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>43193</v>
+        <v>43173</v>
       </c>
       <c r="O205" t="n">
-        <v>46707</v>
+        <v>46727</v>
       </c>
       <c r="P205" t="n">
         <v>4924</v>
@@ -16610,19 +16610,19 @@
         <v>17189</v>
       </c>
       <c r="S205" t="n">
-        <v>30144</v>
+        <v>30164</v>
       </c>
       <c r="T205" t="n">
-        <v>14012</v>
+        <v>14018</v>
       </c>
       <c r="U205" t="n">
-        <v>7006</v>
+        <v>7009</v>
       </c>
       <c r="V205" t="n">
-        <v>9126</v>
+        <v>9137</v>
       </c>
       <c r="W205" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
@@ -16677,10 +16677,10 @@
         <v>554</v>
       </c>
       <c r="N206" t="n">
-        <v>43988</v>
+        <v>43968</v>
       </c>
       <c r="O206" t="n">
-        <v>45912</v>
+        <v>45932</v>
       </c>
       <c r="P206" t="n">
         <v>6614</v>
@@ -16692,16 +16692,16 @@
         <v>17189</v>
       </c>
       <c r="S206" t="n">
-        <v>24509</v>
+        <v>24529</v>
       </c>
       <c r="T206" t="n">
-        <v>13774</v>
+        <v>13780</v>
       </c>
       <c r="U206" t="n">
-        <v>6887</v>
+        <v>6890</v>
       </c>
       <c r="V206" t="n">
-        <v>3849</v>
+        <v>3860</v>
       </c>
       <c r="W206" t="n">
         <v>8.4</v>
@@ -16759,10 +16759,10 @@
         <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>43193</v>
+        <v>43173</v>
       </c>
       <c r="O207" t="n">
-        <v>46707</v>
+        <v>46727</v>
       </c>
       <c r="P207" t="n">
         <v>2948</v>
@@ -16774,16 +16774,16 @@
         <v>17189</v>
       </c>
       <c r="S207" t="n">
-        <v>29170</v>
+        <v>29190</v>
       </c>
       <c r="T207" t="n">
-        <v>14012</v>
+        <v>14018</v>
       </c>
       <c r="U207" t="n">
-        <v>7006</v>
+        <v>7009</v>
       </c>
       <c r="V207" t="n">
-        <v>8152</v>
+        <v>8163</v>
       </c>
       <c r="W207" t="n">
         <v>17.5</v>
@@ -16841,10 +16841,10 @@
         <v>8091</v>
       </c>
       <c r="N208" t="n">
-        <v>51284</v>
+        <v>51264</v>
       </c>
       <c r="O208" t="n">
-        <v>38616</v>
+        <v>38636</v>
       </c>
       <c r="P208" t="n">
         <v>14918</v>
@@ -16856,16 +16856,16 @@
         <v>17189</v>
       </c>
       <c r="S208" t="n">
-        <v>15358</v>
+        <v>15378</v>
       </c>
       <c r="T208" t="n">
-        <v>11585</v>
+        <v>11591</v>
       </c>
       <c r="U208" t="n">
-        <v>5792</v>
+        <v>5795</v>
       </c>
       <c r="V208" t="n">
-        <v>-2019</v>
+        <v>-2008</v>
       </c>
       <c r="W208" t="n">
         <v>-5.2</v>
@@ -16923,10 +16923,10 @@
         <v>7690</v>
       </c>
       <c r="N209" t="n">
-        <v>48930</v>
+        <v>48910</v>
       </c>
       <c r="O209" t="n">
-        <v>36476</v>
+        <v>36496</v>
       </c>
       <c r="P209" t="n">
         <v>4118</v>
@@ -16938,19 +16938,19 @@
         <v>17189</v>
       </c>
       <c r="S209" t="n">
-        <v>19568</v>
+        <v>19588</v>
       </c>
       <c r="T209" t="n">
-        <v>10943</v>
+        <v>10949</v>
       </c>
       <c r="U209" t="n">
-        <v>5471</v>
+        <v>5474</v>
       </c>
       <c r="V209" t="n">
-        <v>3154</v>
+        <v>3165</v>
       </c>
       <c r="W209" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>46003</v>
+        <v>45983</v>
       </c>
       <c r="O210" t="n">
-        <v>37897</v>
+        <v>37917</v>
       </c>
       <c r="P210" t="n">
         <v>4564</v>
@@ -17020,16 +17020,16 @@
         <v>17440</v>
       </c>
       <c r="S210" t="n">
-        <v>20843</v>
+        <v>20863</v>
       </c>
       <c r="T210" t="n">
-        <v>11369</v>
+        <v>11375</v>
       </c>
       <c r="U210" t="n">
-        <v>5685</v>
+        <v>5688</v>
       </c>
       <c r="V210" t="n">
-        <v>3789</v>
+        <v>3800</v>
       </c>
       <c r="W210" t="n">
         <v>10</v>
@@ -17087,10 +17087,10 @@
         <v>5803</v>
       </c>
       <c r="N211" t="n">
-        <v>45035</v>
+        <v>45015</v>
       </c>
       <c r="O211" t="n">
-        <v>37865</v>
+        <v>37885</v>
       </c>
       <c r="P211" t="n">
         <v>6198</v>
@@ -17102,19 +17102,19 @@
         <v>14537</v>
       </c>
       <c r="S211" t="n">
-        <v>22130</v>
+        <v>22150</v>
       </c>
       <c r="T211" t="n">
-        <v>11360</v>
+        <v>11366</v>
       </c>
       <c r="U211" t="n">
-        <v>5680</v>
+        <v>5683</v>
       </c>
       <c r="V211" t="n">
-        <v>5091</v>
+        <v>5102</v>
       </c>
       <c r="W211" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="X211" t="inlineStr">
         <is>
@@ -17169,10 +17169,10 @@
         <v>4145</v>
       </c>
       <c r="N212" t="n">
-        <v>43377</v>
+        <v>43357</v>
       </c>
       <c r="O212" t="n">
-        <v>39523</v>
+        <v>39543</v>
       </c>
       <c r="P212" t="n">
         <v>10516</v>
@@ -17184,16 +17184,16 @@
         <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>33207</v>
+        <v>33227</v>
       </c>
       <c r="T212" t="n">
-        <v>11857</v>
+        <v>11863</v>
       </c>
       <c r="U212" t="n">
-        <v>5928</v>
+        <v>5931</v>
       </c>
       <c r="V212" t="n">
-        <v>15422</v>
+        <v>15433</v>
       </c>
       <c r="W212" t="n">
         <v>39</v>
@@ -17247,10 +17247,10 @@
         <v>7413</v>
       </c>
       <c r="N213" t="n">
-        <v>47136</v>
+        <v>47116</v>
       </c>
       <c r="O213" t="n">
-        <v>35232</v>
+        <v>35252</v>
       </c>
       <c r="P213" t="n">
         <v>2948</v>
@@ -17262,16 +17262,16 @@
         <v>14537</v>
       </c>
       <c r="S213" t="n">
-        <v>20247</v>
+        <v>20267</v>
       </c>
       <c r="T213" t="n">
-        <v>10570</v>
+        <v>10576</v>
       </c>
       <c r="U213" t="n">
-        <v>5285</v>
+        <v>5288</v>
       </c>
       <c r="V213" t="n">
-        <v>4393</v>
+        <v>4404</v>
       </c>
       <c r="W213" t="n">
         <v>12.5</v>
@@ -17329,10 +17329,10 @@
         <v>19320</v>
       </c>
       <c r="N214" t="n">
-        <v>58114</v>
+        <v>58094</v>
       </c>
       <c r="O214" t="n">
-        <v>24206</v>
+        <v>24226</v>
       </c>
       <c r="P214" t="n">
         <v>11584</v>
@@ -17344,19 +17344,19 @@
         <v>14537</v>
       </c>
       <c r="S214" t="n">
-        <v>2285</v>
+        <v>2305</v>
       </c>
       <c r="T214" t="n">
-        <v>7262</v>
+        <v>7268</v>
       </c>
       <c r="U214" t="n">
-        <v>3631</v>
+        <v>3634</v>
       </c>
       <c r="V214" t="n">
-        <v>-8608</v>
+        <v>-8597</v>
       </c>
       <c r="W214" t="n">
-        <v>-35.6</v>
+        <v>-35.5</v>
       </c>
       <c r="X214" t="inlineStr">
         <is>
@@ -17411,10 +17411,10 @@
         <v>951</v>
       </c>
       <c r="N215" t="n">
-        <v>40068</v>
+        <v>40048</v>
       </c>
       <c r="O215" t="n">
-        <v>41939</v>
+        <v>41959</v>
       </c>
       <c r="P215" t="n">
         <v>5415</v>
@@ -17426,16 +17426,16 @@
         <v>14537</v>
       </c>
       <c r="S215" t="n">
-        <v>27537</v>
+        <v>27557</v>
       </c>
       <c r="T215" t="n">
-        <v>12582</v>
+        <v>12588</v>
       </c>
       <c r="U215" t="n">
-        <v>6291</v>
+        <v>6294</v>
       </c>
       <c r="V215" t="n">
-        <v>8664</v>
+        <v>8675</v>
       </c>
       <c r="W215" t="n">
         <v>20.7</v>
@@ -17493,10 +17493,10 @@
         <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>39589</v>
+        <v>39569</v>
       </c>
       <c r="O216" t="n">
-        <v>42418</v>
+        <v>42438</v>
       </c>
       <c r="P216" t="n">
         <v>3099</v>
@@ -17508,16 +17508,16 @@
         <v>14537</v>
       </c>
       <c r="S216" t="n">
-        <v>27581</v>
+        <v>27601</v>
       </c>
       <c r="T216" t="n">
-        <v>12725</v>
+        <v>12731</v>
       </c>
       <c r="U216" t="n">
-        <v>6363</v>
+        <v>6366</v>
       </c>
       <c r="V216" t="n">
-        <v>8493</v>
+        <v>8504</v>
       </c>
       <c r="W216" t="n">
         <v>20</v>
@@ -17575,10 +17575,10 @@
         <v>951</v>
       </c>
       <c r="N217" t="n">
-        <v>44168</v>
+        <v>44148</v>
       </c>
       <c r="O217" t="n">
-        <v>37839</v>
+        <v>37859</v>
       </c>
       <c r="P217" t="n">
         <v>4463</v>
@@ -17590,16 +17590,16 @@
         <v>14537</v>
       </c>
       <c r="S217" t="n">
-        <v>23039</v>
+        <v>23059</v>
       </c>
       <c r="T217" t="n">
-        <v>11352</v>
+        <v>11358</v>
       </c>
       <c r="U217" t="n">
-        <v>5676</v>
+        <v>5679</v>
       </c>
       <c r="V217" t="n">
-        <v>6011</v>
+        <v>6022</v>
       </c>
       <c r="W217" t="n">
         <v>15.9</v>
@@ -17657,10 +17657,10 @@
         <v>5018</v>
       </c>
       <c r="N218" t="n">
-        <v>43817</v>
+        <v>43797</v>
       </c>
       <c r="O218" t="n">
-        <v>37518</v>
+        <v>37538</v>
       </c>
       <c r="P218" t="n">
         <v>4947</v>
@@ -17672,16 +17672,16 @@
         <v>14537</v>
       </c>
       <c r="S218" t="n">
-        <v>23034</v>
+        <v>23054</v>
       </c>
       <c r="T218" t="n">
-        <v>11255</v>
+        <v>11261</v>
       </c>
       <c r="U218" t="n">
-        <v>5628</v>
+        <v>5631</v>
       </c>
       <c r="V218" t="n">
-        <v>6151</v>
+        <v>6162</v>
       </c>
       <c r="W218" t="n">
         <v>16.4</v>
@@ -17739,10 +17739,10 @@
         <v>9134</v>
       </c>
       <c r="N219" t="n">
-        <v>47421</v>
+        <v>47401</v>
       </c>
       <c r="O219" t="n">
-        <v>32479</v>
+        <v>32499</v>
       </c>
       <c r="P219" t="n">
         <v>6882</v>
@@ -17754,16 +17754,16 @@
         <v>12464</v>
       </c>
       <c r="S219" t="n">
-        <v>18033</v>
+        <v>18053</v>
       </c>
       <c r="T219" t="n">
-        <v>9744</v>
+        <v>9750</v>
       </c>
       <c r="U219" t="n">
-        <v>4872</v>
+        <v>4875</v>
       </c>
       <c r="V219" t="n">
-        <v>3417</v>
+        <v>3428</v>
       </c>
       <c r="W219" t="n">
         <v>10.5</v>
@@ -17822,10 +17822,10 @@
         <v>9134</v>
       </c>
       <c r="N220" t="n">
-        <v>47421</v>
+        <v>47401</v>
       </c>
       <c r="O220" t="n">
-        <v>32479</v>
+        <v>32499</v>
       </c>
       <c r="P220" t="n">
         <v>7175</v>
@@ -17837,19 +17837,19 @@
         <v>12464</v>
       </c>
       <c r="S220" t="n">
-        <v>18039</v>
+        <v>18059</v>
       </c>
       <c r="T220" t="n">
-        <v>9744</v>
+        <v>9750</v>
       </c>
       <c r="U220" t="n">
-        <v>4872</v>
+        <v>4875</v>
       </c>
       <c r="V220" t="n">
-        <v>3423</v>
+        <v>3434</v>
       </c>
       <c r="W220" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="X220" t="inlineStr">
         <is>
@@ -17905,10 +17905,10 @@
         <v>7175</v>
       </c>
       <c r="N221" t="n">
-        <v>45672</v>
+        <v>45652</v>
       </c>
       <c r="O221" t="n">
-        <v>34049</v>
+        <v>34069</v>
       </c>
       <c r="P221" t="n">
         <v>0</v>
@@ -17920,16 +17920,16 @@
         <v>13664</v>
       </c>
       <c r="S221" t="n">
-        <v>25934</v>
+        <v>25954</v>
       </c>
       <c r="T221" t="n">
-        <v>10215</v>
+        <v>10221</v>
       </c>
       <c r="U221" t="n">
-        <v>5107</v>
+        <v>5110</v>
       </c>
       <c r="V221" t="n">
-        <v>10612</v>
+        <v>10623</v>
       </c>
       <c r="W221" t="n">
         <v>31.2</v>
@@ -17987,10 +17987,10 @@
         <v>10682</v>
       </c>
       <c r="N222" t="n">
-        <v>56012</v>
+        <v>55992</v>
       </c>
       <c r="O222" t="n">
-        <v>23191</v>
+        <v>23211</v>
       </c>
       <c r="P222" t="n">
         <v>5919</v>
@@ -18002,16 +18002,16 @@
         <v>12464</v>
       </c>
       <c r="S222" t="n">
-        <v>9807</v>
+        <v>9827</v>
       </c>
       <c r="T222" t="n">
-        <v>6957</v>
+        <v>6963</v>
       </c>
       <c r="U222" t="n">
-        <v>3479</v>
+        <v>3482</v>
       </c>
       <c r="V222" t="n">
-        <v>-629</v>
+        <v>-618</v>
       </c>
       <c r="W222" t="n">
         <v>-2.7</v>
@@ -18070,10 +18070,10 @@
         <v>17414</v>
       </c>
       <c r="N223" t="n">
-        <v>58804</v>
+        <v>58784</v>
       </c>
       <c r="O223" t="n">
-        <v>19952</v>
+        <v>19972</v>
       </c>
       <c r="P223" t="n">
         <v>7914</v>
@@ -18085,19 +18085,19 @@
         <v>16574</v>
       </c>
       <c r="S223" t="n">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="T223" t="n">
-        <v>5986</v>
+        <v>5992</v>
       </c>
       <c r="U223" t="n">
-        <v>2993</v>
+        <v>2996</v>
       </c>
       <c r="V223" t="n">
-        <v>-8664</v>
+        <v>-8653</v>
       </c>
       <c r="W223" t="n">
-        <v>-43.4</v>
+        <v>-43.3</v>
       </c>
       <c r="X223" t="inlineStr">
         <is>
@@ -18152,10 +18152,10 @@
         <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>37670</v>
+        <v>37650</v>
       </c>
       <c r="O224" t="n">
-        <v>40352</v>
+        <v>40372</v>
       </c>
       <c r="P224" t="n">
         <v>6040</v>
@@ -18167,16 +18167,16 @@
         <v>13664</v>
       </c>
       <c r="S224" t="n">
-        <v>23348</v>
+        <v>23368</v>
       </c>
       <c r="T224" t="n">
-        <v>12106</v>
+        <v>12112</v>
       </c>
       <c r="U224" t="n">
-        <v>6053</v>
+        <v>6056</v>
       </c>
       <c r="V224" t="n">
-        <v>5190</v>
+        <v>5201</v>
       </c>
       <c r="W224" t="n">
         <v>12.9</v>
@@ -18234,10 +18234,10 @@
         <v>11570</v>
       </c>
       <c r="N225" t="n">
-        <v>52620</v>
+        <v>52600</v>
       </c>
       <c r="O225" t="n">
-        <v>25402</v>
+        <v>25422</v>
       </c>
       <c r="P225" t="n">
         <v>4386</v>
@@ -18249,19 +18249,19 @@
         <v>13664</v>
       </c>
       <c r="S225" t="n">
-        <v>11951</v>
+        <v>11971</v>
       </c>
       <c r="T225" t="n">
-        <v>7621</v>
+        <v>7627</v>
       </c>
       <c r="U225" t="n">
-        <v>3810</v>
+        <v>3813</v>
       </c>
       <c r="V225" t="n">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="W225" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="X225" t="inlineStr">
         <is>
@@ -18316,10 +18316,10 @@
         <v>11570</v>
       </c>
       <c r="N226" t="n">
-        <v>49093</v>
+        <v>49073</v>
       </c>
       <c r="O226" t="n">
-        <v>28929</v>
+        <v>28949</v>
       </c>
       <c r="P226" t="n">
         <v>3099</v>
@@ -18331,16 +18331,16 @@
         <v>13664</v>
       </c>
       <c r="S226" t="n">
-        <v>15566</v>
+        <v>15586</v>
       </c>
       <c r="T226" t="n">
-        <v>8679</v>
+        <v>8685</v>
       </c>
       <c r="U226" t="n">
-        <v>4339</v>
+        <v>4342</v>
       </c>
       <c r="V226" t="n">
-        <v>2548</v>
+        <v>2559</v>
       </c>
       <c r="W226" t="n">
         <v>8.800000000000001</v>
@@ -18398,10 +18398,10 @@
         <v>11570</v>
       </c>
       <c r="N227" t="n">
-        <v>49093</v>
+        <v>49073</v>
       </c>
       <c r="O227" t="n">
-        <v>28929</v>
+        <v>28949</v>
       </c>
       <c r="P227" t="n">
         <v>3098</v>
@@ -18413,19 +18413,19 @@
         <v>13664</v>
       </c>
       <c r="S227" t="n">
-        <v>14966</v>
+        <v>14986</v>
       </c>
       <c r="T227" t="n">
-        <v>8679</v>
+        <v>8685</v>
       </c>
       <c r="U227" t="n">
-        <v>4339</v>
+        <v>4342</v>
       </c>
       <c r="V227" t="n">
-        <v>1948</v>
+        <v>1959</v>
       </c>
       <c r="W227" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X227" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>14691</v>
       </c>
       <c r="N228" t="n">
-        <v>52214</v>
+        <v>52194</v>
       </c>
       <c r="O228" t="n">
-        <v>25808</v>
+        <v>25828</v>
       </c>
       <c r="P228" t="n">
         <v>0</v>
@@ -18495,16 +18495,16 @@
         <v>13664</v>
       </c>
       <c r="S228" t="n">
-        <v>15644</v>
+        <v>15664</v>
       </c>
       <c r="T228" t="n">
-        <v>7742</v>
+        <v>7748</v>
       </c>
       <c r="U228" t="n">
-        <v>3871</v>
+        <v>3874</v>
       </c>
       <c r="V228" t="n">
-        <v>4030</v>
+        <v>4041</v>
       </c>
       <c r="W228" t="n">
         <v>15.6</v>
@@ -18562,10 +18562,10 @@
         <v>11570</v>
       </c>
       <c r="N229" t="n">
-        <v>49093</v>
+        <v>49073</v>
       </c>
       <c r="O229" t="n">
-        <v>28929</v>
+        <v>28949</v>
       </c>
       <c r="P229" t="n">
         <v>0</v>
@@ -18577,16 +18577,16 @@
         <v>13664</v>
       </c>
       <c r="S229" t="n">
-        <v>19664</v>
+        <v>19684</v>
       </c>
       <c r="T229" t="n">
-        <v>8679</v>
+        <v>8685</v>
       </c>
       <c r="U229" t="n">
-        <v>4339</v>
+        <v>4342</v>
       </c>
       <c r="V229" t="n">
-        <v>6646</v>
+        <v>6657</v>
       </c>
       <c r="W229" t="n">
         <v>23</v>
@@ -18644,10 +18644,10 @@
         <v>5462</v>
       </c>
       <c r="N230" t="n">
-        <v>43117</v>
+        <v>43097</v>
       </c>
       <c r="O230" t="n">
-        <v>34905</v>
+        <v>34925</v>
       </c>
       <c r="P230" t="n">
         <v>4386</v>
@@ -18659,16 +18659,16 @@
         <v>13664</v>
       </c>
       <c r="S230" t="n">
-        <v>21155</v>
+        <v>21175</v>
       </c>
       <c r="T230" t="n">
-        <v>10472</v>
+        <v>10478</v>
       </c>
       <c r="U230" t="n">
-        <v>5236</v>
+        <v>5239</v>
       </c>
       <c r="V230" t="n">
-        <v>5448</v>
+        <v>5459</v>
       </c>
       <c r="W230" t="n">
         <v>15.6</v>
@@ -18726,10 +18726,10 @@
         <v>3901</v>
       </c>
       <c r="N231" t="n">
-        <v>41357</v>
+        <v>41337</v>
       </c>
       <c r="O231" t="n">
-        <v>36665</v>
+        <v>36685</v>
       </c>
       <c r="P231" t="n">
         <v>5350</v>
@@ -18741,16 +18741,16 @@
         <v>13664</v>
       </c>
       <c r="S231" t="n">
-        <v>22801</v>
+        <v>22821</v>
       </c>
       <c r="T231" t="n">
-        <v>11000</v>
+        <v>11006</v>
       </c>
       <c r="U231" t="n">
-        <v>5500</v>
+        <v>5503</v>
       </c>
       <c r="V231" t="n">
-        <v>6302</v>
+        <v>6313</v>
       </c>
       <c r="W231" t="n">
         <v>17.2</v>
@@ -18808,10 +18808,10 @@
         <v>11570</v>
       </c>
       <c r="N232" t="n">
-        <v>49093</v>
+        <v>49073</v>
       </c>
       <c r="O232" t="n">
-        <v>28929</v>
+        <v>28949</v>
       </c>
       <c r="P232" t="n">
         <v>5368</v>
@@ -18823,19 +18823,19 @@
         <v>13664</v>
       </c>
       <c r="S232" t="n">
-        <v>14997</v>
+        <v>15017</v>
       </c>
       <c r="T232" t="n">
-        <v>8679</v>
+        <v>8685</v>
       </c>
       <c r="U232" t="n">
-        <v>4339</v>
+        <v>4342</v>
       </c>
       <c r="V232" t="n">
-        <v>1979</v>
+        <v>1990</v>
       </c>
       <c r="W232" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X232" t="inlineStr">
         <is>
@@ -18890,10 +18890,10 @@
         <v>3901</v>
       </c>
       <c r="N233" t="n">
-        <v>41572</v>
+        <v>41552</v>
       </c>
       <c r="O233" t="n">
-        <v>36450</v>
+        <v>36470</v>
       </c>
       <c r="P233" t="n">
         <v>1</v>
@@ -18905,16 +18905,16 @@
         <v>13664</v>
       </c>
       <c r="S233" t="n">
-        <v>27284</v>
+        <v>27304</v>
       </c>
       <c r="T233" t="n">
-        <v>10935</v>
+        <v>10941</v>
       </c>
       <c r="U233" t="n">
-        <v>5468</v>
+        <v>5470</v>
       </c>
       <c r="V233" t="n">
-        <v>10882</v>
+        <v>10892</v>
       </c>
       <c r="W233" t="n">
         <v>29.9</v>
@@ -18972,10 +18972,10 @@
         <v>11570</v>
       </c>
       <c r="N234" t="n">
-        <v>49093</v>
+        <v>49073</v>
       </c>
       <c r="O234" t="n">
-        <v>28929</v>
+        <v>28949</v>
       </c>
       <c r="P234" t="n">
         <v>3099</v>
@@ -18987,19 +18987,19 @@
         <v>13664</v>
       </c>
       <c r="S234" t="n">
-        <v>14965</v>
+        <v>14985</v>
       </c>
       <c r="T234" t="n">
-        <v>8679</v>
+        <v>8685</v>
       </c>
       <c r="U234" t="n">
-        <v>4339</v>
+        <v>4342</v>
       </c>
       <c r="V234" t="n">
-        <v>1947</v>
+        <v>1958</v>
       </c>
       <c r="W234" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X234" t="inlineStr">
         <is>
@@ -19054,10 +19054,10 @@
         <v>7669</v>
       </c>
       <c r="N235" t="n">
-        <v>45192</v>
+        <v>45172</v>
       </c>
       <c r="O235" t="n">
-        <v>32830</v>
+        <v>32850</v>
       </c>
       <c r="P235" t="n">
         <v>7495</v>
@@ -19069,16 +19069,16 @@
         <v>13664</v>
       </c>
       <c r="S235" t="n">
-        <v>20020</v>
+        <v>20040</v>
       </c>
       <c r="T235" t="n">
-        <v>9849</v>
+        <v>9855</v>
       </c>
       <c r="U235" t="n">
-        <v>4924</v>
+        <v>4928</v>
       </c>
       <c r="V235" t="n">
-        <v>5246</v>
+        <v>5258</v>
       </c>
       <c r="W235" t="n">
         <v>16</v>
@@ -19136,10 +19136,10 @@
         <v>11570</v>
       </c>
       <c r="N236" t="n">
-        <v>49093</v>
+        <v>49073</v>
       </c>
       <c r="O236" t="n">
-        <v>28929</v>
+        <v>28949</v>
       </c>
       <c r="P236" t="n">
         <v>3099</v>
@@ -19151,16 +19151,16 @@
         <v>13664</v>
       </c>
       <c r="S236" t="n">
-        <v>14666</v>
+        <v>14686</v>
       </c>
       <c r="T236" t="n">
-        <v>8679</v>
+        <v>8685</v>
       </c>
       <c r="U236" t="n">
-        <v>4339</v>
+        <v>4342</v>
       </c>
       <c r="V236" t="n">
-        <v>1648</v>
+        <v>1659</v>
       </c>
       <c r="W236" t="n">
         <v>5.7</v>
@@ -19218,10 +19218,10 @@
         <v>4569</v>
       </c>
       <c r="N237" t="n">
-        <v>42376</v>
+        <v>42356</v>
       </c>
       <c r="O237" t="n">
-        <v>35646</v>
+        <v>35666</v>
       </c>
       <c r="P237" t="n">
         <v>4136</v>
@@ -19233,16 +19233,16 @@
         <v>13664</v>
       </c>
       <c r="S237" t="n">
-        <v>22146</v>
+        <v>22166</v>
       </c>
       <c r="T237" t="n">
-        <v>10694</v>
+        <v>10700</v>
       </c>
       <c r="U237" t="n">
-        <v>5347</v>
+        <v>5350</v>
       </c>
       <c r="V237" t="n">
-        <v>6105</v>
+        <v>6116</v>
       </c>
       <c r="W237" t="n">
         <v>17.1</v>
@@ -19300,10 +19300,10 @@
         <v>11575</v>
       </c>
       <c r="N238" t="n">
-        <v>49100</v>
+        <v>49080</v>
       </c>
       <c r="O238" t="n">
-        <v>28922</v>
+        <v>28942</v>
       </c>
       <c r="P238" t="n">
         <v>4136</v>
@@ -19315,16 +19315,16 @@
         <v>13664</v>
       </c>
       <c r="S238" t="n">
-        <v>15621</v>
+        <v>15641</v>
       </c>
       <c r="T238" t="n">
-        <v>8677</v>
+        <v>8683</v>
       </c>
       <c r="U238" t="n">
-        <v>4338</v>
+        <v>4341</v>
       </c>
       <c r="V238" t="n">
-        <v>2606</v>
+        <v>2617</v>
       </c>
       <c r="W238" t="n">
         <v>9</v>
@@ -19382,10 +19382,10 @@
         <v>667</v>
       </c>
       <c r="N239" t="n">
-        <v>42376</v>
+        <v>42356</v>
       </c>
       <c r="O239" t="n">
-        <v>35646</v>
+        <v>35666</v>
       </c>
       <c r="P239" t="n">
         <v>1000</v>
@@ -19397,19 +19397,19 @@
         <v>13664</v>
       </c>
       <c r="S239" t="n">
-        <v>23681</v>
+        <v>23701</v>
       </c>
       <c r="T239" t="n">
-        <v>10694</v>
+        <v>10700</v>
       </c>
       <c r="U239" t="n">
-        <v>5347</v>
+        <v>5350</v>
       </c>
       <c r="V239" t="n">
-        <v>7640</v>
+        <v>7651</v>
       </c>
       <c r="W239" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="X239" t="inlineStr">
         <is>
@@ -19464,10 +19464,10 @@
         <v>7011</v>
       </c>
       <c r="N240" t="n">
-        <v>43878</v>
+        <v>43858</v>
       </c>
       <c r="O240" t="n">
-        <v>34022</v>
+        <v>34042</v>
       </c>
       <c r="P240" t="n">
         <v>207</v>
@@ -19479,16 +19479,16 @@
         <v>11912</v>
       </c>
       <c r="S240" t="n">
-        <v>26402</v>
+        <v>26422</v>
       </c>
       <c r="T240" t="n">
-        <v>10207</v>
+        <v>10213</v>
       </c>
       <c r="U240" t="n">
-        <v>5103</v>
+        <v>5106</v>
       </c>
       <c r="V240" t="n">
-        <v>11092</v>
+        <v>11103</v>
       </c>
       <c r="W240" t="n">
         <v>32.6</v>
@@ -19546,10 +19546,10 @@
         <v>7011</v>
       </c>
       <c r="N241" t="n">
-        <v>44617</v>
+        <v>44597</v>
       </c>
       <c r="O241" t="n">
-        <v>33283</v>
+        <v>33303</v>
       </c>
       <c r="P241" t="n">
         <v>7749</v>
@@ -19561,16 +19561,16 @@
         <v>11912</v>
       </c>
       <c r="S241" t="n">
-        <v>18622</v>
+        <v>18642</v>
       </c>
       <c r="T241" t="n">
-        <v>9985</v>
+        <v>9991</v>
       </c>
       <c r="U241" t="n">
-        <v>4992</v>
+        <v>4995</v>
       </c>
       <c r="V241" t="n">
-        <v>3645</v>
+        <v>3656</v>
       </c>
       <c r="W241" t="n">
         <v>11</v>
@@ -19628,10 +19628,10 @@
         <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>37608</v>
+        <v>37588</v>
       </c>
       <c r="O242" t="n">
-        <v>40292</v>
+        <v>40312</v>
       </c>
       <c r="P242" t="n">
         <v>5441</v>
@@ -19640,22 +19640,22 @@
         <v>4999</v>
       </c>
       <c r="R242" t="n">
-        <v>16349</v>
+        <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>23501</v>
+        <v>39870</v>
       </c>
       <c r="T242" t="n">
-        <v>12088</v>
+        <v>12094</v>
       </c>
       <c r="U242" t="n">
-        <v>6044</v>
+        <v>6047</v>
       </c>
       <c r="V242" t="n">
-        <v>5370</v>
+        <v>21730</v>
       </c>
       <c r="W242" t="n">
-        <v>13.3</v>
+        <v>53.9</v>
       </c>
       <c r="X242" t="inlineStr">
         <is>
@@ -19710,10 +19710,10 @@
         <v>46696</v>
       </c>
       <c r="N243" t="n">
-        <v>84158</v>
+        <v>84138</v>
       </c>
       <c r="O243" t="n">
-        <v>-6258</v>
+        <v>-6238</v>
       </c>
       <c r="P243" t="n">
         <v>4197</v>
@@ -19725,16 +19725,16 @@
         <v>16349</v>
       </c>
       <c r="S243" t="n">
-        <v>-22504</v>
+        <v>-22484</v>
       </c>
       <c r="T243" t="n">
-        <v>-1877</v>
+        <v>-1871</v>
       </c>
       <c r="U243" t="n">
-        <v>-939</v>
+        <v>-936</v>
       </c>
       <c r="V243" t="n">
-        <v>-19688</v>
+        <v>-19677</v>
       </c>
       <c r="X243" t="inlineStr">
         <is>
@@ -19789,10 +19789,10 @@
         <v>3845</v>
       </c>
       <c r="N244" t="n">
-        <v>44084</v>
+        <v>44064</v>
       </c>
       <c r="O244" t="n">
-        <v>32816</v>
+        <v>32836</v>
       </c>
       <c r="P244" t="n">
         <v>1000</v>
@@ -19804,16 +19804,16 @@
         <v>12651</v>
       </c>
       <c r="S244" t="n">
-        <v>21665</v>
+        <v>21685</v>
       </c>
       <c r="T244" t="n">
-        <v>9845</v>
+        <v>9851</v>
       </c>
       <c r="U244" t="n">
-        <v>4922</v>
+        <v>4925</v>
       </c>
       <c r="V244" t="n">
-        <v>6898</v>
+        <v>6909</v>
       </c>
       <c r="W244" t="n">
         <v>21</v>
@@ -19871,10 +19871,10 @@
         <v>5313</v>
       </c>
       <c r="N245" t="n">
-        <v>41945</v>
+        <v>41925</v>
       </c>
       <c r="O245" t="n">
-        <v>33955</v>
+        <v>33975</v>
       </c>
       <c r="P245" t="n">
         <v>0</v>
@@ -19886,16 +19886,16 @@
         <v>11465</v>
       </c>
       <c r="S245" t="n">
-        <v>29140</v>
+        <v>29160</v>
       </c>
       <c r="T245" t="n">
-        <v>10186</v>
+        <v>10192</v>
       </c>
       <c r="U245" t="n">
-        <v>5093</v>
+        <v>5096</v>
       </c>
       <c r="V245" t="n">
-        <v>13860</v>
+        <v>13871</v>
       </c>
       <c r="W245" t="n">
         <v>40.8</v>
@@ -19953,10 +19953,10 @@
         <v>5313</v>
       </c>
       <c r="N246" t="n">
-        <v>42000</v>
+        <v>41980</v>
       </c>
       <c r="O246" t="n">
-        <v>33900</v>
+        <v>33920</v>
       </c>
       <c r="P246" t="n">
         <v>3099</v>
@@ -19968,16 +19968,16 @@
         <v>11465</v>
       </c>
       <c r="S246" t="n">
-        <v>22035</v>
+        <v>22055</v>
       </c>
       <c r="T246" t="n">
-        <v>10170</v>
+        <v>10176</v>
       </c>
       <c r="U246" t="n">
-        <v>5085</v>
+        <v>5088</v>
       </c>
       <c r="V246" t="n">
-        <v>6780</v>
+        <v>6791</v>
       </c>
       <c r="W246" t="n">
         <v>20</v>
@@ -20035,10 +20035,10 @@
         <v>10541</v>
       </c>
       <c r="N247" t="n">
-        <v>47114</v>
+        <v>47094</v>
       </c>
       <c r="O247" t="n">
-        <v>28786</v>
+        <v>28806</v>
       </c>
       <c r="P247" t="n">
         <v>5103</v>
@@ -20050,16 +20050,16 @@
         <v>13482</v>
       </c>
       <c r="S247" t="n">
-        <v>13200</v>
+        <v>13220</v>
       </c>
       <c r="T247" t="n">
-        <v>8636</v>
+        <v>8642</v>
       </c>
       <c r="U247" t="n">
-        <v>4318</v>
+        <v>4321</v>
       </c>
       <c r="V247" t="n">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="W247" t="n">
         <v>0.9</v>
@@ -20117,10 +20117,10 @@
         <v>3795</v>
       </c>
       <c r="N248" t="n">
-        <v>40440</v>
+        <v>40420</v>
       </c>
       <c r="O248" t="n">
-        <v>35460</v>
+        <v>35480</v>
       </c>
       <c r="P248" t="n">
         <v>1000</v>
@@ -20132,16 +20132,16 @@
         <v>11465</v>
       </c>
       <c r="S248" t="n">
-        <v>25594</v>
+        <v>25614</v>
       </c>
       <c r="T248" t="n">
-        <v>10638</v>
+        <v>10644</v>
       </c>
       <c r="U248" t="n">
-        <v>5319</v>
+        <v>5322</v>
       </c>
       <c r="V248" t="n">
-        <v>9637</v>
+        <v>9648</v>
       </c>
       <c r="W248" t="n">
         <v>27.2</v>
@@ -20195,10 +20195,10 @@
         <v>11453</v>
       </c>
       <c r="N249" t="n">
-        <v>47869</v>
+        <v>47849</v>
       </c>
       <c r="O249" t="n">
-        <v>27812</v>
+        <v>27832</v>
       </c>
       <c r="P249" t="n">
         <v>3099</v>
@@ -20210,16 +20210,16 @@
         <v>13664</v>
       </c>
       <c r="S249" t="n">
-        <v>13848</v>
+        <v>13868</v>
       </c>
       <c r="T249" t="n">
-        <v>8344</v>
+        <v>8350</v>
       </c>
       <c r="U249" t="n">
-        <v>4172</v>
+        <v>4175</v>
       </c>
       <c r="V249" t="n">
-        <v>1333</v>
+        <v>1344</v>
       </c>
       <c r="W249" t="n">
         <v>4.8</v>
@@ -20277,10 +20277,10 @@
         <v>4487</v>
       </c>
       <c r="N250" t="n">
-        <v>6042</v>
+        <v>6022</v>
       </c>
       <c r="O250" t="n">
-        <v>69183</v>
+        <v>69203</v>
       </c>
       <c r="P250" t="n">
         <v>1000</v>
@@ -20292,16 +20292,16 @@
         <v>13482</v>
       </c>
       <c r="S250" t="n">
-        <v>57300</v>
+        <v>57320</v>
       </c>
       <c r="T250" t="n">
-        <v>20755</v>
+        <v>20761</v>
       </c>
       <c r="U250" t="n">
-        <v>10377</v>
+        <v>10380</v>
       </c>
       <c r="V250" t="n">
-        <v>26168</v>
+        <v>26179</v>
       </c>
       <c r="W250" t="n">
         <v>37.8</v>
@@ -20359,10 +20359,10 @@
         <v>5139</v>
       </c>
       <c r="N251" t="n">
-        <v>41810</v>
+        <v>41790</v>
       </c>
       <c r="O251" t="n">
-        <v>33090</v>
+        <v>33110</v>
       </c>
       <c r="P251" t="n">
         <v>3549</v>
@@ -20374,16 +20374,16 @@
         <v>12464</v>
       </c>
       <c r="S251" t="n">
-        <v>19377</v>
+        <v>19397</v>
       </c>
       <c r="T251" t="n">
-        <v>9927</v>
+        <v>9933</v>
       </c>
       <c r="U251" t="n">
-        <v>4964</v>
+        <v>4966</v>
       </c>
       <c r="V251" t="n">
-        <v>4486</v>
+        <v>4498</v>
       </c>
       <c r="W251" t="n">
         <v>13.6</v>
@@ -20442,10 +20442,10 @@
         <v>727</v>
       </c>
       <c r="N252" t="n">
-        <v>36732</v>
+        <v>36712</v>
       </c>
       <c r="O252" t="n">
-        <v>38168</v>
+        <v>38188</v>
       </c>
       <c r="P252" t="n">
         <v>2948</v>
@@ -20457,16 +20457,16 @@
         <v>13482</v>
       </c>
       <c r="S252" t="n">
-        <v>24437</v>
+        <v>24457</v>
       </c>
       <c r="T252" t="n">
-        <v>11450</v>
+        <v>11456</v>
       </c>
       <c r="U252" t="n">
-        <v>5725</v>
+        <v>5728</v>
       </c>
       <c r="V252" t="n">
-        <v>7261</v>
+        <v>7272</v>
       </c>
       <c r="W252" t="n">
         <v>19</v>
@@ -20603,10 +20603,10 @@
         <v>10162</v>
       </c>
       <c r="N254" t="n">
-        <v>46332</v>
+        <v>46312</v>
       </c>
       <c r="O254" t="n">
-        <v>28568</v>
+        <v>28588</v>
       </c>
       <c r="P254" t="n">
         <v>5179</v>
@@ -20618,16 +20618,16 @@
         <v>12464</v>
       </c>
       <c r="S254" t="n">
-        <v>16775</v>
+        <v>16795</v>
       </c>
       <c r="T254" t="n">
-        <v>8570</v>
+        <v>8576</v>
       </c>
       <c r="U254" t="n">
-        <v>4285</v>
+        <v>4288</v>
       </c>
       <c r="V254" t="n">
-        <v>3919</v>
+        <v>3930</v>
       </c>
       <c r="W254" t="n">
         <v>13.7</v>
@@ -20685,10 +20685,10 @@
         <v>10491</v>
       </c>
       <c r="N255" t="n">
-        <v>46591</v>
+        <v>46571</v>
       </c>
       <c r="O255" t="n">
-        <v>28309</v>
+        <v>28329</v>
       </c>
       <c r="P255" t="n">
         <v>2004</v>
@@ -20700,16 +20700,16 @@
         <v>13482</v>
       </c>
       <c r="S255" t="n">
-        <v>15622</v>
+        <v>15642</v>
       </c>
       <c r="T255" t="n">
-        <v>8493</v>
+        <v>8499</v>
       </c>
       <c r="U255" t="n">
-        <v>4246</v>
+        <v>4249</v>
       </c>
       <c r="V255" t="n">
-        <v>2883</v>
+        <v>2894</v>
       </c>
       <c r="W255" t="n">
         <v>10.2</v>
@@ -20767,10 +20767,10 @@
         <v>727</v>
       </c>
       <c r="N256" t="n">
-        <v>36732</v>
+        <v>36712</v>
       </c>
       <c r="O256" t="n">
-        <v>38168</v>
+        <v>38188</v>
       </c>
       <c r="P256" t="n">
         <v>5270</v>
@@ -20782,16 +20782,16 @@
         <v>13482</v>
       </c>
       <c r="S256" t="n">
-        <v>24416</v>
+        <v>24436</v>
       </c>
       <c r="T256" t="n">
-        <v>11450</v>
+        <v>11456</v>
       </c>
       <c r="U256" t="n">
-        <v>5725</v>
+        <v>5728</v>
       </c>
       <c r="V256" t="n">
-        <v>7240</v>
+        <v>7251</v>
       </c>
       <c r="W256" t="n">
         <v>19</v>
@@ -20849,10 +20849,10 @@
         <v>5243</v>
       </c>
       <c r="N257" t="n">
-        <v>40618</v>
+        <v>40598</v>
       </c>
       <c r="O257" t="n">
-        <v>34282</v>
+        <v>34302</v>
       </c>
       <c r="P257" t="n">
         <v>3074</v>
@@ -20864,19 +20864,19 @@
         <v>13482</v>
       </c>
       <c r="S257" t="n">
-        <v>20926</v>
+        <v>20946</v>
       </c>
       <c r="T257" t="n">
-        <v>10285</v>
+        <v>10291</v>
       </c>
       <c r="U257" t="n">
-        <v>5142</v>
+        <v>5145</v>
       </c>
       <c r="V257" t="n">
-        <v>5499</v>
+        <v>5510</v>
       </c>
       <c r="W257" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="X257" t="inlineStr">
         <is>
@@ -20931,10 +20931,10 @@
         <v>6735</v>
       </c>
       <c r="N258" t="n">
-        <v>43116</v>
+        <v>43096</v>
       </c>
       <c r="O258" t="n">
-        <v>31718</v>
+        <v>31738</v>
       </c>
       <c r="P258" t="n">
         <v>3978</v>
@@ -20946,16 +20946,16 @@
         <v>13482</v>
       </c>
       <c r="S258" t="n">
-        <v>17858</v>
+        <v>17878</v>
       </c>
       <c r="T258" t="n">
-        <v>9515</v>
+        <v>9521</v>
       </c>
       <c r="U258" t="n">
-        <v>4758</v>
+        <v>4761</v>
       </c>
       <c r="V258" t="n">
-        <v>3585</v>
+        <v>3596</v>
       </c>
       <c r="W258" t="n">
         <v>11.3</v>
@@ -21013,10 +21013,10 @@
         <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>40072</v>
+        <v>40052</v>
       </c>
       <c r="O259" t="n">
-        <v>34762</v>
+        <v>34782</v>
       </c>
       <c r="P259" t="n">
         <v>3099</v>
@@ -21028,16 +21028,16 @@
         <v>13482</v>
       </c>
       <c r="S259" t="n">
-        <v>20880</v>
+        <v>20900</v>
       </c>
       <c r="T259" t="n">
-        <v>10429</v>
+        <v>10435</v>
       </c>
       <c r="U259" t="n">
-        <v>5214</v>
+        <v>5217</v>
       </c>
       <c r="V259" t="n">
-        <v>5237</v>
+        <v>5248</v>
       </c>
       <c r="W259" t="n">
         <v>15.1</v>
@@ -21095,10 +21095,10 @@
         <v>8013</v>
       </c>
       <c r="N260" t="n">
-        <v>43868</v>
+        <v>43848</v>
       </c>
       <c r="O260" t="n">
-        <v>30966</v>
+        <v>30986</v>
       </c>
       <c r="P260" t="n">
         <v>0</v>
@@ -21110,16 +21110,16 @@
         <v>13482</v>
       </c>
       <c r="S260" t="n">
-        <v>20083</v>
+        <v>20103</v>
       </c>
       <c r="T260" t="n">
-        <v>9290</v>
+        <v>9296</v>
       </c>
       <c r="U260" t="n">
-        <v>4645</v>
+        <v>4648</v>
       </c>
       <c r="V260" t="n">
-        <v>6148</v>
+        <v>6159</v>
       </c>
       <c r="W260" t="n">
         <v>19.9</v>
@@ -21177,10 +21177,10 @@
         <v>3757</v>
       </c>
       <c r="N261" t="n">
-        <v>39780</v>
+        <v>39760</v>
       </c>
       <c r="O261" t="n">
-        <v>35054</v>
+        <v>35074</v>
       </c>
       <c r="P261" t="n">
         <v>4589</v>
@@ -21192,16 +21192,16 @@
         <v>13482</v>
       </c>
       <c r="S261" t="n">
-        <v>21982</v>
+        <v>22002</v>
       </c>
       <c r="T261" t="n">
-        <v>10516</v>
+        <v>10522</v>
       </c>
       <c r="U261" t="n">
-        <v>5258</v>
+        <v>5261</v>
       </c>
       <c r="V261" t="n">
-        <v>6208</v>
+        <v>6219</v>
       </c>
       <c r="W261" t="n">
         <v>17.7</v>
@@ -21259,10 +21259,10 @@
         <v>4271</v>
       </c>
       <c r="N262" t="n">
-        <v>43868</v>
+        <v>43848</v>
       </c>
       <c r="O262" t="n">
-        <v>30966</v>
+        <v>30986</v>
       </c>
       <c r="P262" t="n">
         <v>4801</v>
@@ -21274,16 +21274,16 @@
         <v>13482</v>
       </c>
       <c r="S262" t="n">
-        <v>17982</v>
+        <v>18002</v>
       </c>
       <c r="T262" t="n">
-        <v>9290</v>
+        <v>9296</v>
       </c>
       <c r="U262" t="n">
-        <v>4645</v>
+        <v>4648</v>
       </c>
       <c r="V262" t="n">
-        <v>4047</v>
+        <v>4058</v>
       </c>
       <c r="W262" t="n">
         <v>13.1</v>
@@ -21341,10 +21341,10 @@
         <v>6690</v>
       </c>
       <c r="N263" t="n">
-        <v>42585</v>
+        <v>42565</v>
       </c>
       <c r="O263" t="n">
-        <v>31747</v>
+        <v>31767</v>
       </c>
       <c r="P263" t="n">
         <v>2948</v>
@@ -21356,19 +21356,19 @@
         <v>13410</v>
       </c>
       <c r="S263" t="n">
-        <v>18489</v>
+        <v>18509</v>
       </c>
       <c r="T263" t="n">
-        <v>9524</v>
+        <v>9530</v>
       </c>
       <c r="U263" t="n">
-        <v>4762</v>
+        <v>4765</v>
       </c>
       <c r="V263" t="n">
-        <v>4203</v>
+        <v>4214</v>
       </c>
       <c r="W263" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="X263" t="inlineStr">
         <is>
@@ -21423,10 +21423,10 @@
         <v>11820</v>
       </c>
       <c r="N264" t="n">
-        <v>47429</v>
+        <v>47409</v>
       </c>
       <c r="O264" t="n">
-        <v>26809</v>
+        <v>26829</v>
       </c>
       <c r="P264" t="n">
         <v>4670</v>
@@ -21438,16 +21438,16 @@
         <v>12464</v>
       </c>
       <c r="S264" t="n">
-        <v>13674</v>
+        <v>13694</v>
       </c>
       <c r="T264" t="n">
-        <v>8043</v>
+        <v>8049</v>
       </c>
       <c r="U264" t="n">
-        <v>4021</v>
+        <v>4024</v>
       </c>
       <c r="V264" t="n">
-        <v>1610</v>
+        <v>1621</v>
       </c>
       <c r="W264" t="n">
         <v>6</v>
@@ -21506,10 +21506,10 @@
         <v>6131</v>
       </c>
       <c r="N265" t="n">
-        <v>41677</v>
+        <v>41657</v>
       </c>
       <c r="O265" t="n">
-        <v>32223</v>
+        <v>32243</v>
       </c>
       <c r="P265" t="n">
         <v>0</v>
@@ -21521,16 +21521,16 @@
         <v>11912</v>
       </c>
       <c r="S265" t="n">
-        <v>23110</v>
+        <v>23130</v>
       </c>
       <c r="T265" t="n">
-        <v>9667</v>
+        <v>9673</v>
       </c>
       <c r="U265" t="n">
-        <v>4833</v>
+        <v>4836</v>
       </c>
       <c r="V265" t="n">
-        <v>8610</v>
+        <v>8621</v>
       </c>
       <c r="W265" t="n">
         <v>26.7</v>
@@ -21588,10 +21588,10 @@
         <v>3595</v>
       </c>
       <c r="N266" t="n">
-        <v>38312</v>
+        <v>38292</v>
       </c>
       <c r="O266" t="n">
-        <v>33588</v>
+        <v>33608</v>
       </c>
       <c r="P266" t="n">
         <v>6472</v>
@@ -21603,16 +21603,16 @@
         <v>11225</v>
       </c>
       <c r="S266" t="n">
-        <v>21090</v>
+        <v>21110</v>
       </c>
       <c r="T266" t="n">
-        <v>10076</v>
+        <v>10082</v>
       </c>
       <c r="U266" t="n">
-        <v>5038</v>
+        <v>5041</v>
       </c>
       <c r="V266" t="n">
-        <v>5975</v>
+        <v>5986</v>
       </c>
       <c r="W266" t="n">
         <v>17.8</v>
@@ -21670,10 +21670,10 @@
         <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>38290</v>
+        <v>38270</v>
       </c>
       <c r="O267" t="n">
-        <v>33610</v>
+        <v>33630</v>
       </c>
       <c r="P267" t="n">
         <v>0</v>
@@ -21685,16 +21685,16 @@
         <v>11225</v>
       </c>
       <c r="S267" t="n">
-        <v>27535</v>
+        <v>27555</v>
       </c>
       <c r="T267" t="n">
-        <v>10083</v>
+        <v>10089</v>
       </c>
       <c r="U267" t="n">
-        <v>5042</v>
+        <v>5044</v>
       </c>
       <c r="V267" t="n">
-        <v>12410</v>
+        <v>12422</v>
       </c>
       <c r="W267" t="n">
         <v>36.9</v>
@@ -21748,10 +21748,10 @@
         <v>10120</v>
       </c>
       <c r="N268" t="n">
-        <v>44271</v>
+        <v>44251</v>
       </c>
       <c r="O268" t="n">
-        <v>26886</v>
+        <v>26906</v>
       </c>
       <c r="P268" t="n">
         <v>7175</v>
@@ -21763,16 +21763,16 @@
         <v>12464</v>
       </c>
       <c r="S268" t="n">
-        <v>11147</v>
+        <v>11167</v>
       </c>
       <c r="T268" t="n">
-        <v>8066</v>
+        <v>8072</v>
       </c>
       <c r="U268" t="n">
-        <v>4033</v>
+        <v>4036</v>
       </c>
       <c r="V268" t="n">
-        <v>-952</v>
+        <v>-941</v>
       </c>
       <c r="W268" t="n">
         <v>-3.5</v>
@@ -21831,10 +21831,10 @@
         <v>15</v>
       </c>
       <c r="N269" t="n">
-        <v>38020</v>
+        <v>38000</v>
       </c>
       <c r="O269" t="n">
-        <v>33073</v>
+        <v>33093</v>
       </c>
       <c r="P269" t="n">
         <v>2948</v>
@@ -21846,16 +21846,16 @@
         <v>13482</v>
       </c>
       <c r="S269" t="n">
-        <v>19142</v>
+        <v>19162</v>
       </c>
       <c r="T269" t="n">
-        <v>9922</v>
+        <v>9928</v>
       </c>
       <c r="U269" t="n">
-        <v>4961</v>
+        <v>4964</v>
       </c>
       <c r="V269" t="n">
-        <v>4259</v>
+        <v>4270</v>
       </c>
       <c r="W269" t="n">
         <v>12.9</v>
@@ -21913,10 +21913,10 @@
         <v>4963</v>
       </c>
       <c r="N270" t="n">
-        <v>39222</v>
+        <v>39202</v>
       </c>
       <c r="O270" t="n">
-        <v>31678</v>
+        <v>31698</v>
       </c>
       <c r="P270" t="n">
         <v>10180</v>
@@ -21928,19 +21928,19 @@
         <v>12490</v>
       </c>
       <c r="S270" t="n">
-        <v>19307</v>
+        <v>19327</v>
       </c>
       <c r="T270" t="n">
-        <v>9503</v>
+        <v>9509</v>
       </c>
       <c r="U270" t="n">
-        <v>4752</v>
+        <v>4755</v>
       </c>
       <c r="V270" t="n">
-        <v>5052</v>
+        <v>5063</v>
       </c>
       <c r="W270" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="X270" t="inlineStr">
         <is>
@@ -21995,10 +21995,10 @@
         <v>7830</v>
       </c>
       <c r="N271" t="n">
-        <v>44465</v>
+        <v>44445</v>
       </c>
       <c r="O271" t="n">
-        <v>23435</v>
+        <v>23455</v>
       </c>
       <c r="P271" t="n">
         <v>3932</v>
@@ -22010,19 +22010,19 @@
         <v>11225</v>
       </c>
       <c r="S271" t="n">
-        <v>12478</v>
+        <v>12498</v>
       </c>
       <c r="T271" t="n">
-        <v>7030</v>
+        <v>7036</v>
       </c>
       <c r="U271" t="n">
-        <v>3515</v>
+        <v>3518</v>
       </c>
       <c r="V271" t="n">
-        <v>1932</v>
+        <v>1943</v>
       </c>
       <c r="W271" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X271" t="inlineStr">
         <is>
@@ -22077,10 +22077,10 @@
         <v>6021</v>
       </c>
       <c r="N272" t="n">
-        <v>41207</v>
+        <v>41187</v>
       </c>
       <c r="O272" t="n">
-        <v>25693</v>
+        <v>25713</v>
       </c>
       <c r="P272" t="n">
         <v>1629</v>
@@ -22092,19 +22092,19 @@
         <v>11909</v>
       </c>
       <c r="S272" t="n">
-        <v>14755</v>
+        <v>14775</v>
       </c>
       <c r="T272" t="n">
-        <v>7708</v>
+        <v>7714</v>
       </c>
       <c r="U272" t="n">
-        <v>3854</v>
+        <v>3857</v>
       </c>
       <c r="V272" t="n">
-        <v>3193</v>
+        <v>3204</v>
       </c>
       <c r="W272" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="X272" t="inlineStr">
         <is>
@@ -22159,10 +22159,10 @@
         <v>4263</v>
       </c>
       <c r="N273" t="n">
-        <v>33952</v>
+        <v>33932</v>
       </c>
       <c r="O273" t="n">
-        <v>26948</v>
+        <v>26968</v>
       </c>
       <c r="P273" t="n">
         <v>4170</v>
@@ -22174,16 +22174,16 @@
         <v>10373</v>
       </c>
       <c r="S273" t="n">
-        <v>16705</v>
+        <v>16725</v>
       </c>
       <c r="T273" t="n">
-        <v>8084</v>
+        <v>8090</v>
       </c>
       <c r="U273" t="n">
-        <v>4042</v>
+        <v>4045</v>
       </c>
       <c r="V273" t="n">
-        <v>4578</v>
+        <v>4589</v>
       </c>
       <c r="W273" t="n">
         <v>17</v>
@@ -22241,10 +22241,10 @@
         <v>10666</v>
       </c>
       <c r="N274" t="n">
-        <v>39881</v>
+        <v>39861</v>
       </c>
       <c r="O274" t="n">
-        <v>21019</v>
+        <v>21039</v>
       </c>
       <c r="P274" t="n">
         <v>5627</v>
@@ -22256,16 +22256,16 @@
         <v>10373</v>
       </c>
       <c r="S274" t="n">
-        <v>9219</v>
+        <v>9239</v>
       </c>
       <c r="T274" t="n">
-        <v>6306</v>
+        <v>6312</v>
       </c>
       <c r="U274" t="n">
-        <v>3153</v>
+        <v>3156</v>
       </c>
       <c r="V274" t="n">
-        <v>-240</v>
+        <v>-229</v>
       </c>
       <c r="W274" t="n">
         <v>-1.1</v>
@@ -22323,10 +22323,10 @@
         <v>5481</v>
       </c>
       <c r="N275" t="n">
-        <v>34857</v>
+        <v>34837</v>
       </c>
       <c r="O275" t="n">
-        <v>26043</v>
+        <v>26063</v>
       </c>
       <c r="P275" t="n">
         <v>3978</v>
@@ -22338,19 +22338,19 @@
         <v>10373</v>
       </c>
       <c r="S275" t="n">
-        <v>15192</v>
+        <v>15212</v>
       </c>
       <c r="T275" t="n">
-        <v>7813</v>
+        <v>7819</v>
       </c>
       <c r="U275" t="n">
-        <v>3906</v>
+        <v>3909</v>
       </c>
       <c r="V275" t="n">
-        <v>3473</v>
+        <v>3484</v>
       </c>
       <c r="W275" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="X275" t="inlineStr">
         <is>
@@ -22405,10 +22405,10 @@
         <v>59515</v>
       </c>
       <c r="N276" t="n">
-        <v>89658</v>
+        <v>89638</v>
       </c>
       <c r="O276" t="n">
-        <v>-32758</v>
+        <v>-32738</v>
       </c>
       <c r="P276" t="n">
         <v>3139</v>
@@ -22420,16 +22420,16 @@
         <v>9760</v>
       </c>
       <c r="S276" t="n">
-        <v>-41658</v>
+        <v>-41638</v>
       </c>
       <c r="T276" t="n">
-        <v>-9827</v>
+        <v>-9821</v>
       </c>
       <c r="U276" t="n">
-        <v>-4914</v>
+        <v>-4911</v>
       </c>
       <c r="V276" t="n">
-        <v>-26917</v>
+        <v>-26906</v>
       </c>
       <c r="X276" t="inlineStr">
         <is>
@@ -22484,10 +22484,10 @@
         <v>3987</v>
       </c>
       <c r="N277" t="n">
-        <v>30933</v>
+        <v>30913</v>
       </c>
       <c r="O277" t="n">
-        <v>25047</v>
+        <v>25067</v>
       </c>
       <c r="P277" t="n">
         <v>2948</v>
@@ -22499,19 +22499,19 @@
         <v>9760</v>
       </c>
       <c r="S277" t="n">
-        <v>15039</v>
+        <v>15059</v>
       </c>
       <c r="T277" t="n">
-        <v>7514</v>
+        <v>7520</v>
       </c>
       <c r="U277" t="n">
-        <v>3757</v>
+        <v>3760</v>
       </c>
       <c r="V277" t="n">
-        <v>3768</v>
+        <v>3779</v>
       </c>
       <c r="W277" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="X277" t="inlineStr">
         <is>
@@ -22566,10 +22566,10 @@
         <v>9025</v>
       </c>
       <c r="N278" t="n">
-        <v>35971</v>
+        <v>35951</v>
       </c>
       <c r="O278" t="n">
-        <v>20009</v>
+        <v>20029</v>
       </c>
       <c r="P278" t="n">
         <v>3849</v>
@@ -22581,16 +22581,16 @@
         <v>9760</v>
       </c>
       <c r="S278" t="n">
-        <v>9800</v>
+        <v>9820</v>
       </c>
       <c r="T278" t="n">
-        <v>6003</v>
+        <v>6009</v>
       </c>
       <c r="U278" t="n">
-        <v>3001</v>
+        <v>3004</v>
       </c>
       <c r="V278" t="n">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="W278" t="n">
         <v>4</v>
@@ -22648,10 +22648,10 @@
         <v>11434</v>
       </c>
       <c r="N279" t="n">
-        <v>38284</v>
+        <v>38264</v>
       </c>
       <c r="O279" t="n">
-        <v>17616</v>
+        <v>17636</v>
       </c>
       <c r="P279" t="n">
         <v>4794</v>
@@ -22663,19 +22663,19 @@
         <v>10373</v>
       </c>
       <c r="S279" t="n">
-        <v>4948</v>
+        <v>4968</v>
       </c>
       <c r="T279" t="n">
-        <v>5285</v>
+        <v>5291</v>
       </c>
       <c r="U279" t="n">
-        <v>2642</v>
+        <v>2645</v>
       </c>
       <c r="V279" t="n">
-        <v>-2979</v>
+        <v>-2968</v>
       </c>
       <c r="W279" t="n">
-        <v>-16.9</v>
+        <v>-16.8</v>
       </c>
       <c r="X279" t="inlineStr">
         <is>
@@ -22730,10 +22730,10 @@
         <v>9197</v>
       </c>
       <c r="N280" t="n">
-        <v>36046</v>
+        <v>36026</v>
       </c>
       <c r="O280" t="n">
-        <v>19854</v>
+        <v>19874</v>
       </c>
       <c r="P280" t="n">
         <v>1694</v>
@@ -22745,19 +22745,19 @@
         <v>10373</v>
       </c>
       <c r="S280" t="n">
-        <v>10287</v>
+        <v>10307</v>
       </c>
       <c r="T280" t="n">
-        <v>5956</v>
+        <v>5962</v>
       </c>
       <c r="U280" t="n">
-        <v>2978</v>
+        <v>2981</v>
       </c>
       <c r="V280" t="n">
-        <v>1353</v>
+        <v>1364</v>
       </c>
       <c r="W280" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X280" t="inlineStr">
         <is>
@@ -22812,10 +22812,10 @@
         <v>2655</v>
       </c>
       <c r="N281" t="n">
-        <v>28047</v>
+        <v>28027</v>
       </c>
       <c r="O281" t="n">
-        <v>25058</v>
+        <v>25078</v>
       </c>
       <c r="P281" t="n">
         <v>3099</v>
@@ -22827,16 +22827,16 @@
         <v>10373</v>
       </c>
       <c r="S281" t="n">
-        <v>14385</v>
+        <v>14405</v>
       </c>
       <c r="T281" t="n">
-        <v>7517</v>
+        <v>7523</v>
       </c>
       <c r="U281" t="n">
-        <v>3759</v>
+        <v>3762</v>
       </c>
       <c r="V281" t="n">
-        <v>3109</v>
+        <v>3120</v>
       </c>
       <c r="W281" t="n">
         <v>12.4</v>
@@ -22894,10 +22894,10 @@
         <v>56988</v>
       </c>
       <c r="N282" t="n">
-        <v>81637</v>
+        <v>81617</v>
       </c>
       <c r="O282" t="n">
-        <v>-29737</v>
+        <v>-29717</v>
       </c>
       <c r="P282" t="n">
         <v>3099</v>
@@ -22909,16 +22909,16 @@
         <v>9760</v>
       </c>
       <c r="S282" t="n">
-        <v>-39897</v>
+        <v>-39877</v>
       </c>
       <c r="T282" t="n">
-        <v>-8921</v>
+        <v>-8915</v>
       </c>
       <c r="U282" t="n">
-        <v>-4461</v>
+        <v>-4458</v>
       </c>
       <c r="V282" t="n">
-        <v>-26515</v>
+        <v>-26504</v>
       </c>
       <c r="X282" t="inlineStr">
         <is>
@@ -22973,10 +22973,10 @@
         <v>27733</v>
       </c>
       <c r="N283" t="n">
-        <v>52699</v>
+        <v>52679</v>
       </c>
       <c r="O283" t="n">
-        <v>-799</v>
+        <v>-779</v>
       </c>
       <c r="P283" t="n">
         <v>3099</v>
@@ -22988,16 +22988,16 @@
         <v>9760</v>
       </c>
       <c r="S283" t="n">
-        <v>-11158</v>
+        <v>-11138</v>
       </c>
       <c r="T283" t="n">
-        <v>-240</v>
+        <v>-234</v>
       </c>
       <c r="U283" t="n">
-        <v>-120</v>
+        <v>-117</v>
       </c>
       <c r="V283" t="n">
-        <v>-10798</v>
+        <v>-10787</v>
       </c>
       <c r="X283" t="inlineStr">
         <is>
@@ -23052,10 +23052,10 @@
         <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>25065</v>
+        <v>25045</v>
       </c>
       <c r="O284" t="n">
-        <v>26835</v>
+        <v>26855</v>
       </c>
       <c r="P284" t="n">
         <v>6419</v>
@@ -23067,16 +23067,16 @@
         <v>9760</v>
       </c>
       <c r="S284" t="n">
-        <v>15855</v>
+        <v>15875</v>
       </c>
       <c r="T284" t="n">
-        <v>8050</v>
+        <v>8056</v>
       </c>
       <c r="U284" t="n">
-        <v>4025</v>
+        <v>4028</v>
       </c>
       <c r="V284" t="n">
-        <v>3779</v>
+        <v>3790</v>
       </c>
       <c r="W284" t="n">
         <v>14.1</v>
@@ -23134,10 +23134,10 @@
         <v>6549</v>
       </c>
       <c r="N285" t="n">
-        <v>31249</v>
+        <v>31229</v>
       </c>
       <c r="O285" t="n">
-        <v>19982</v>
+        <v>20002</v>
       </c>
       <c r="P285" t="n">
         <v>3099</v>
@@ -23149,16 +23149,16 @@
         <v>9760</v>
       </c>
       <c r="S285" t="n">
-        <v>9423</v>
+        <v>9443</v>
       </c>
       <c r="T285" t="n">
-        <v>5995</v>
+        <v>6001</v>
       </c>
       <c r="U285" t="n">
-        <v>2997</v>
+        <v>3000</v>
       </c>
       <c r="V285" t="n">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="W285" t="n">
         <v>2.2</v>
@@ -23216,10 +23216,10 @@
         <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>21220</v>
+        <v>21200</v>
       </c>
       <c r="O286" t="n">
-        <v>18680</v>
+        <v>18700</v>
       </c>
       <c r="P286" t="n">
         <v>1689</v>
@@ -23231,19 +23231,19 @@
         <v>0</v>
       </c>
       <c r="S286" t="n">
-        <v>22691</v>
+        <v>22711</v>
       </c>
       <c r="T286" t="n">
-        <v>5604</v>
+        <v>5610</v>
       </c>
       <c r="U286" t="n">
-        <v>2802</v>
+        <v>2805</v>
       </c>
       <c r="V286" t="n">
-        <v>14285</v>
+        <v>14296</v>
       </c>
       <c r="W286" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="X286" t="inlineStr">
         <is>
@@ -23292,16 +23292,16 @@
         <v>421</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M287" t="n">
         <v>1619</v>
       </c>
       <c r="N287" t="n">
-        <v>18638</v>
+        <v>18646</v>
       </c>
       <c r="O287" t="n">
-        <v>13739</v>
+        <v>13731</v>
       </c>
       <c r="P287" t="n">
         <v>0</v>
@@ -23313,16 +23313,16 @@
         <v>4411</v>
       </c>
       <c r="S287" t="n">
-        <v>9328</v>
+        <v>9320</v>
       </c>
       <c r="T287" t="n">
-        <v>4122</v>
+        <v>4119</v>
       </c>
       <c r="U287" t="n">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="V287" t="n">
-        <v>3145</v>
+        <v>3141</v>
       </c>
       <c r="W287" t="n">
         <v>22.9</v>
@@ -23370,16 +23370,16 @@
         <v>421</v>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M288" t="n">
         <v>1619</v>
       </c>
       <c r="N288" t="n">
-        <v>18709</v>
+        <v>18718</v>
       </c>
       <c r="O288" t="n">
-        <v>13668</v>
+        <v>13659</v>
       </c>
       <c r="P288" t="n">
         <v>0</v>
@@ -23391,16 +23391,16 @@
         <v>4411</v>
       </c>
       <c r="S288" t="n">
-        <v>9257</v>
+        <v>9248</v>
       </c>
       <c r="T288" t="n">
-        <v>4100</v>
+        <v>4098</v>
       </c>
       <c r="U288" t="n">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="V288" t="n">
-        <v>3106</v>
+        <v>3101</v>
       </c>
       <c r="W288" t="n">
         <v>22.7</v>
@@ -23448,16 +23448,16 @@
         <v>421</v>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M289" t="n">
         <v>0</v>
       </c>
       <c r="N289" t="n">
-        <v>16670</v>
+        <v>16680</v>
       </c>
       <c r="O289" t="n">
-        <v>15707</v>
+        <v>15697</v>
       </c>
       <c r="P289" t="n">
         <v>0</v>
@@ -23469,16 +23469,16 @@
         <v>4411</v>
       </c>
       <c r="S289" t="n">
-        <v>11296</v>
+        <v>11286</v>
       </c>
       <c r="T289" t="n">
-        <v>4712</v>
+        <v>4709</v>
       </c>
       <c r="U289" t="n">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="V289" t="n">
-        <v>4228</v>
+        <v>4222</v>
       </c>
       <c r="W289" t="n">
         <v>26.9</v>
@@ -23526,16 +23526,16 @@
         <v>410</v>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M290" t="n">
         <v>5682</v>
       </c>
       <c r="N290" t="n">
-        <v>23195</v>
+        <v>23209</v>
       </c>
       <c r="O290" t="n">
-        <v>8371</v>
+        <v>8357</v>
       </c>
       <c r="P290" t="n">
         <v>0</v>
@@ -23547,19 +23547,19 @@
         <v>4411</v>
       </c>
       <c r="S290" t="n">
-        <v>3960</v>
+        <v>3946</v>
       </c>
       <c r="T290" t="n">
-        <v>2511</v>
+        <v>2507</v>
       </c>
       <c r="U290" t="n">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="V290" t="n">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="W290" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="X290" t="inlineStr"/>
     </row>
@@ -23682,16 +23682,16 @@
         <v>410</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M292" t="n">
         <v>0</v>
       </c>
       <c r="N292" t="n">
-        <v>16840</v>
+        <v>16849</v>
       </c>
       <c r="O292" t="n">
-        <v>14726</v>
+        <v>14717</v>
       </c>
       <c r="P292" t="n">
         <v>0</v>
@@ -23703,16 +23703,16 @@
         <v>4411</v>
       </c>
       <c r="S292" t="n">
-        <v>10315</v>
+        <v>10306</v>
       </c>
       <c r="T292" t="n">
-        <v>4418</v>
+        <v>4415</v>
       </c>
       <c r="U292" t="n">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="V292" t="n">
-        <v>3688</v>
+        <v>3683</v>
       </c>
       <c r="W292" t="n">
         <v>25</v>
@@ -23760,16 +23760,16 @@
         <v>410</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M293" t="n">
         <v>1578</v>
       </c>
       <c r="N293" t="n">
-        <v>17833</v>
+        <v>17840</v>
       </c>
       <c r="O293" t="n">
-        <v>13733</v>
+        <v>13726</v>
       </c>
       <c r="P293" t="n">
         <v>0</v>
@@ -23781,16 +23781,16 @@
         <v>4411</v>
       </c>
       <c r="S293" t="n">
-        <v>9322</v>
+        <v>9315</v>
       </c>
       <c r="T293" t="n">
-        <v>4120</v>
+        <v>4118</v>
       </c>
       <c r="U293" t="n">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="V293" t="n">
-        <v>3142</v>
+        <v>3138</v>
       </c>
       <c r="W293" t="n">
         <v>22.9</v>
@@ -23844,10 +23844,10 @@
         <v>3428</v>
       </c>
       <c r="N294" t="n">
-        <v>7816</v>
+        <v>7796</v>
       </c>
       <c r="O294" t="n">
-        <v>1374</v>
+        <v>1394</v>
       </c>
       <c r="P294" t="n">
         <v>0</v>
@@ -23859,19 +23859,19 @@
         <v>11759</v>
       </c>
       <c r="S294" t="n">
-        <v>-6185</v>
+        <v>-6165</v>
       </c>
       <c r="T294" t="n">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="U294" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="V294" t="n">
-        <v>-6803</v>
+        <v>-6792</v>
       </c>
       <c r="W294" t="n">
-        <v>-495.1</v>
+        <v>-487.3</v>
       </c>
       <c r="X294" t="inlineStr"/>
     </row>
@@ -23922,10 +23922,10 @@
         <v>8994</v>
       </c>
       <c r="N295" t="n">
-        <v>13725</v>
+        <v>13705</v>
       </c>
       <c r="O295" t="n">
-        <v>-4536</v>
+        <v>-4516</v>
       </c>
       <c r="P295" t="n">
         <v>0</v>
@@ -23937,16 +23937,16 @@
         <v>11759</v>
       </c>
       <c r="S295" t="n">
-        <v>-14195</v>
+        <v>-14175</v>
       </c>
       <c r="T295" t="n">
-        <v>-1361</v>
+        <v>-1355</v>
       </c>
       <c r="U295" t="n">
-        <v>-680</v>
+        <v>-677</v>
       </c>
       <c r="V295" t="n">
-        <v>-12154</v>
+        <v>-12143</v>
       </c>
       <c r="X295" t="inlineStr"/>
     </row>
@@ -23997,10 +23997,10 @@
         <v>6448</v>
       </c>
       <c r="N296" t="n">
-        <v>10204</v>
+        <v>10184</v>
       </c>
       <c r="O296" t="n">
-        <v>-4110</v>
+        <v>-4090</v>
       </c>
       <c r="P296" t="n">
         <v>0</v>
@@ -24012,16 +24012,16 @@
         <v>16933</v>
       </c>
       <c r="S296" t="n">
-        <v>-18943</v>
+        <v>-18923</v>
       </c>
       <c r="T296" t="n">
-        <v>-1233</v>
+        <v>-1227</v>
       </c>
       <c r="U296" t="n">
-        <v>-616</v>
+        <v>-614</v>
       </c>
       <c r="V296" t="n">
-        <v>-17094</v>
+        <v>-17082</v>
       </c>
       <c r="X296" t="inlineStr">
         <is>
@@ -24076,10 +24076,10 @@
         <v>18442</v>
       </c>
       <c r="N297" t="n">
-        <v>20796</v>
+        <v>20776</v>
       </c>
       <c r="O297" t="n">
-        <v>-16200</v>
+        <v>-16180</v>
       </c>
       <c r="P297" t="n">
         <v>0</v>
@@ -24091,16 +24091,16 @@
         <v>11759</v>
       </c>
       <c r="S297" t="n">
-        <v>-25759</v>
+        <v>-25739</v>
       </c>
       <c r="T297" t="n">
-        <v>-4860</v>
+        <v>-4854</v>
       </c>
       <c r="U297" t="n">
-        <v>-2430</v>
+        <v>-2427</v>
       </c>
       <c r="V297" t="n">
-        <v>-18469</v>
+        <v>-18458</v>
       </c>
       <c r="X297" t="inlineStr"/>
     </row>
@@ -24151,10 +24151,10 @@
         <v>8884</v>
       </c>
       <c r="N298" t="n">
-        <v>10352</v>
+        <v>10332</v>
       </c>
       <c r="O298" t="n">
-        <v>-10352</v>
+        <v>-10332</v>
       </c>
       <c r="P298" t="n">
         <v>3761</v>
@@ -24166,16 +24166,16 @@
         <v>12464</v>
       </c>
       <c r="S298" t="n">
-        <v>-26577</v>
+        <v>-26557</v>
       </c>
       <c r="T298" t="n">
-        <v>-3106</v>
+        <v>-3100</v>
       </c>
       <c r="U298" t="n">
-        <v>-1553</v>
+        <v>-1550</v>
       </c>
       <c r="V298" t="n">
-        <v>-21919</v>
+        <v>-21908</v>
       </c>
       <c r="X298" t="inlineStr">
         <is>
@@ -24723,16 +24723,16 @@
         <v>402</v>
       </c>
       <c r="L306" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M306" t="n">
         <v>1545</v>
       </c>
       <c r="N306" t="n">
-        <v>17661</v>
+        <v>17670</v>
       </c>
       <c r="O306" t="n">
-        <v>13239</v>
+        <v>13230</v>
       </c>
       <c r="P306" t="n">
         <v>0</v>
@@ -24744,16 +24744,16 @@
         <v>3744</v>
       </c>
       <c r="S306" t="n">
-        <v>9495</v>
+        <v>9486</v>
       </c>
       <c r="T306" t="n">
-        <v>3972</v>
+        <v>3969</v>
       </c>
       <c r="U306" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="V306" t="n">
-        <v>3537</v>
+        <v>3532</v>
       </c>
       <c r="W306" t="n">
         <v>26.7</v>
@@ -24801,16 +24801,16 @@
         <v>402</v>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M307" t="n">
         <v>1545</v>
       </c>
       <c r="N307" t="n">
-        <v>18174</v>
+        <v>18182</v>
       </c>
       <c r="O307" t="n">
-        <v>12726</v>
+        <v>12718</v>
       </c>
       <c r="P307" t="n">
         <v>0</v>
@@ -24822,16 +24822,16 @@
         <v>3744</v>
       </c>
       <c r="S307" t="n">
-        <v>8982</v>
+        <v>8974</v>
       </c>
       <c r="T307" t="n">
-        <v>3818</v>
+        <v>3815</v>
       </c>
       <c r="U307" t="n">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="V307" t="n">
-        <v>3255</v>
+        <v>3251</v>
       </c>
       <c r="W307" t="n">
         <v>25.6</v>
@@ -25425,16 +25425,16 @@
         <v>358</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M315" t="n">
         <v>0</v>
       </c>
       <c r="N315" t="n">
-        <v>15558</v>
+        <v>15567</v>
       </c>
       <c r="O315" t="n">
-        <v>11950</v>
+        <v>11941</v>
       </c>
       <c r="P315" t="n">
         <v>0</v>
@@ -25446,16 +25446,16 @@
         <v>3230</v>
       </c>
       <c r="S315" t="n">
-        <v>8720</v>
+        <v>8711</v>
       </c>
       <c r="T315" t="n">
-        <v>3585</v>
+        <v>3582</v>
       </c>
       <c r="U315" t="n">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="V315" t="n">
-        <v>3342</v>
+        <v>3338</v>
       </c>
       <c r="W315" t="n">
         <v>28</v>
@@ -25503,16 +25503,16 @@
         <v>358</v>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M316" t="n">
         <v>1375</v>
       </c>
       <c r="N316" t="n">
-        <v>16702</v>
+        <v>16710</v>
       </c>
       <c r="O316" t="n">
-        <v>10806</v>
+        <v>10798</v>
       </c>
       <c r="P316" t="n">
         <v>0</v>
@@ -25524,16 +25524,16 @@
         <v>3230</v>
       </c>
       <c r="S316" t="n">
-        <v>7576</v>
+        <v>7568</v>
       </c>
       <c r="T316" t="n">
-        <v>3242</v>
+        <v>3239</v>
       </c>
       <c r="U316" t="n">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="V316" t="n">
-        <v>2713</v>
+        <v>2709</v>
       </c>
       <c r="W316" t="n">
         <v>25.1</v>
@@ -25581,16 +25581,16 @@
         <v>288</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M317" t="n">
         <v>1997</v>
       </c>
       <c r="N317" t="n">
-        <v>14740</v>
+        <v>14750</v>
       </c>
       <c r="O317" t="n">
-        <v>7447</v>
+        <v>7437</v>
       </c>
       <c r="P317" t="n">
         <v>0</v>
@@ -25602,16 +25602,16 @@
         <v>3230</v>
       </c>
       <c r="S317" t="n">
-        <v>4217</v>
+        <v>4207</v>
       </c>
       <c r="T317" t="n">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="U317" t="n">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="V317" t="n">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="W317" t="n">
         <v>11.6</v>
@@ -25738,16 +25738,16 @@
         <v>402</v>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M319" t="n">
         <v>0</v>
       </c>
       <c r="N319" t="n">
-        <v>1822</v>
+        <v>1843</v>
       </c>
       <c r="O319" t="n">
-        <v>-1822</v>
+        <v>-1843</v>
       </c>
       <c r="P319" t="n">
         <v>0</v>
@@ -25759,16 +25759,16 @@
         <v>3744</v>
       </c>
       <c r="S319" t="n">
-        <v>-5566</v>
+        <v>-5587</v>
       </c>
       <c r="T319" t="n">
-        <v>-547</v>
+        <v>-553</v>
       </c>
       <c r="U319" t="n">
-        <v>-273</v>
+        <v>-276</v>
       </c>
       <c r="V319" t="n">
-        <v>-4746</v>
+        <v>-4758</v>
       </c>
       <c r="X319" t="inlineStr"/>
     </row>
@@ -25805,16 +25805,16 @@
         <v>477480</v>
       </c>
       <c r="L320" s="3" t="n">
-        <v>90924</v>
+        <v>70083</v>
       </c>
       <c r="M320" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>568404</v>
+        <v>547563</v>
       </c>
       <c r="O320" s="3" t="n">
-        <v>-568404</v>
+        <v>-547563</v>
       </c>
       <c r="P320" s="3" t="n">
         <v>0</v>
@@ -25826,16 +25826,16 @@
         <v>0</v>
       </c>
       <c r="S320" s="3" t="n">
-        <v>-568404</v>
+        <v>-547563</v>
       </c>
       <c r="T320" s="3" t="n">
-        <v>-170521</v>
+        <v>-164269</v>
       </c>
       <c r="U320" s="3" t="n">
-        <v>-85261</v>
+        <v>-82134</v>
       </c>
       <c r="V320" s="3" t="n">
-        <v>-312622</v>
+        <v>-301160</v>
       </c>
       <c r="W320" s="3" t="n"/>
       <c r="X320" s="3" t="inlineStr"/>
@@ -25879,10 +25879,10 @@
         <v>2105807</v>
       </c>
       <c r="N321" s="4" t="n">
-        <v>12968284</v>
+        <v>12932645</v>
       </c>
       <c r="O321" s="4" t="n">
-        <v>8046189</v>
+        <v>8081828</v>
       </c>
       <c r="P321" s="4" t="n">
         <v>646086</v>
@@ -25891,22 +25891,22 @@
         <v>645498</v>
       </c>
       <c r="R321" s="4" t="n">
-        <v>3335298</v>
+        <v>3318949</v>
       </c>
       <c r="S321" s="4" t="n">
-        <v>4710303</v>
+        <v>4762291</v>
       </c>
       <c r="T321" s="4" t="n">
-        <v>2413857</v>
+        <v>2424548</v>
       </c>
       <c r="U321" s="4" t="n">
-        <v>1206928</v>
+        <v>1212274</v>
       </c>
       <c r="V321" s="4" t="n">
-        <v>1089518</v>
+        <v>1125468</v>
       </c>
       <c r="W321" s="4" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="X321" s="4" t="inlineStr"/>
     </row>

--- a/analytics-mvp/exports/orders_analytics_2026-08.xlsx
+++ b/analytics-mvp/exports/orders_analytics_2026-08.xlsx
@@ -25805,16 +25805,16 @@
         <v>477480</v>
       </c>
       <c r="L320" s="3" t="n">
-        <v>70083</v>
+        <v>63</v>
       </c>
       <c r="M320" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>547563</v>
+        <v>477543</v>
       </c>
       <c r="O320" s="3" t="n">
-        <v>-547563</v>
+        <v>-477543</v>
       </c>
       <c r="P320" s="3" t="n">
         <v>0</v>
@@ -25826,16 +25826,16 @@
         <v>0</v>
       </c>
       <c r="S320" s="3" t="n">
-        <v>-547563</v>
+        <v>-477543</v>
       </c>
       <c r="T320" s="3" t="n">
-        <v>-164269</v>
+        <v>-143263</v>
       </c>
       <c r="U320" s="3" t="n">
-        <v>-82134</v>
+        <v>-71631</v>
       </c>
       <c r="V320" s="3" t="n">
-        <v>-301160</v>
+        <v>-262649</v>
       </c>
       <c r="W320" s="3" t="n"/>
       <c r="X320" s="3" t="inlineStr"/>
@@ -25873,16 +25873,16 @@
         <v>822520</v>
       </c>
       <c r="L321" s="4" t="n">
-        <v>90924</v>
+        <v>20904</v>
       </c>
       <c r="M321" s="4" t="n">
         <v>2105807</v>
       </c>
       <c r="N321" s="4" t="n">
-        <v>12932645</v>
+        <v>12862625</v>
       </c>
       <c r="O321" s="4" t="n">
-        <v>8081828</v>
+        <v>8151848</v>
       </c>
       <c r="P321" s="4" t="n">
         <v>646086</v>
@@ -25894,19 +25894,19 @@
         <v>3318949</v>
       </c>
       <c r="S321" s="4" t="n">
-        <v>4762291</v>
+        <v>4832311</v>
       </c>
       <c r="T321" s="4" t="n">
-        <v>2424548</v>
+        <v>2445554</v>
       </c>
       <c r="U321" s="4" t="n">
-        <v>1212274</v>
+        <v>1222777</v>
       </c>
       <c r="V321" s="4" t="n">
-        <v>1125468</v>
+        <v>1163979</v>
       </c>
       <c r="W321" s="4" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="X321" s="4" t="inlineStr"/>
     </row>

--- a/analytics-mvp/exports/orders_analytics_2026-08.xlsx
+++ b/analytics-mvp/exports/orders_analytics_2026-08.xlsx
@@ -662,16 +662,16 @@
         <v>1885</v>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>66851</v>
+        <v>66843</v>
       </c>
       <c r="O3" t="n">
-        <v>56624</v>
+        <v>56632</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -683,16 +683,16 @@
         <v>13231</v>
       </c>
       <c r="S3" t="n">
-        <v>43393</v>
+        <v>43401</v>
       </c>
       <c r="T3" t="n">
-        <v>16987</v>
+        <v>16990</v>
       </c>
       <c r="U3" t="n">
-        <v>8494</v>
+        <v>8495</v>
       </c>
       <c r="V3" t="n">
-        <v>17912</v>
+        <v>17917</v>
       </c>
       <c r="W3" t="n">
         <v>31.6</v>
@@ -740,16 +740,16 @@
         <v>1483</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M4" t="n">
         <v>5706</v>
       </c>
       <c r="N4" t="n">
-        <v>68403</v>
+        <v>68423</v>
       </c>
       <c r="O4" t="n">
-        <v>45711</v>
+        <v>45691</v>
       </c>
       <c r="P4" t="n">
         <v>1028</v>
@@ -761,16 +761,16 @@
         <v>11827</v>
       </c>
       <c r="S4" t="n">
-        <v>35056</v>
+        <v>35036</v>
       </c>
       <c r="T4" t="n">
-        <v>13713</v>
+        <v>13707</v>
       </c>
       <c r="U4" t="n">
-        <v>6857</v>
+        <v>6854</v>
       </c>
       <c r="V4" t="n">
-        <v>14486</v>
+        <v>14475</v>
       </c>
       <c r="W4" t="n">
         <v>31.7</v>
@@ -978,16 +978,16 @@
         <v>1312</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M7" t="n">
         <v>5045</v>
       </c>
       <c r="N7" t="n">
-        <v>60286</v>
+        <v>60306</v>
       </c>
       <c r="O7" t="n">
-        <v>40614</v>
+        <v>40594</v>
       </c>
       <c r="P7" t="n">
         <v>4056</v>
@@ -999,19 +999,19 @@
         <v>13231</v>
       </c>
       <c r="S7" t="n">
-        <v>28577</v>
+        <v>28557</v>
       </c>
       <c r="T7" t="n">
-        <v>12184</v>
+        <v>12178</v>
       </c>
       <c r="U7" t="n">
-        <v>6092</v>
+        <v>6089</v>
       </c>
       <c r="V7" t="n">
-        <v>10301</v>
+        <v>10290</v>
       </c>
       <c r="W7" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1138,16 +1138,16 @@
         <v>1143</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M9" t="n">
         <v>4395</v>
       </c>
       <c r="N9" t="n">
-        <v>51979</v>
+        <v>51999</v>
       </c>
       <c r="O9" t="n">
-        <v>35921</v>
+        <v>35901</v>
       </c>
       <c r="P9" t="n">
         <v>28</v>
@@ -1159,16 +1159,16 @@
         <v>11827</v>
       </c>
       <c r="S9" t="n">
-        <v>26466</v>
+        <v>26446</v>
       </c>
       <c r="T9" t="n">
-        <v>10776</v>
+        <v>10770</v>
       </c>
       <c r="U9" t="n">
-        <v>5388</v>
+        <v>5385</v>
       </c>
       <c r="V9" t="n">
-        <v>10302</v>
+        <v>10291</v>
       </c>
       <c r="W9" t="n">
         <v>28.7</v>
@@ -1220,16 +1220,16 @@
         <v>1143</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>47584</v>
+        <v>47604</v>
       </c>
       <c r="O10" t="n">
-        <v>40316</v>
+        <v>40296</v>
       </c>
       <c r="P10" t="n">
         <v>3195</v>
@@ -1241,16 +1241,16 @@
         <v>11827</v>
       </c>
       <c r="S10" t="n">
-        <v>27794</v>
+        <v>27774</v>
       </c>
       <c r="T10" t="n">
-        <v>12095</v>
+        <v>12089</v>
       </c>
       <c r="U10" t="n">
-        <v>6047</v>
+        <v>6044</v>
       </c>
       <c r="V10" t="n">
-        <v>9652</v>
+        <v>9641</v>
       </c>
       <c r="W10" t="n">
         <v>23.9</v>
@@ -1302,16 +1302,16 @@
         <v>1046</v>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>4022</v>
       </c>
       <c r="N11" t="n">
-        <v>49524</v>
+        <v>49514</v>
       </c>
       <c r="O11" t="n">
-        <v>30907</v>
+        <v>30917</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1323,16 +1323,16 @@
         <v>8528</v>
       </c>
       <c r="S11" t="n">
-        <v>22379</v>
+        <v>22389</v>
       </c>
       <c r="T11" t="n">
-        <v>9272</v>
+        <v>9275</v>
       </c>
       <c r="U11" t="n">
-        <v>4636</v>
+        <v>4638</v>
       </c>
       <c r="V11" t="n">
-        <v>8471</v>
+        <v>8476</v>
       </c>
       <c r="W11" t="n">
         <v>27.4</v>
@@ -1380,16 +1380,16 @@
         <v>1677</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>6561</v>
       </c>
       <c r="N12" t="n">
-        <v>47871</v>
+        <v>47863</v>
       </c>
       <c r="O12" t="n">
-        <v>25029</v>
+        <v>25037</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1401,16 +1401,16 @@
         <v>6945</v>
       </c>
       <c r="S12" t="n">
-        <v>18084</v>
+        <v>18092</v>
       </c>
       <c r="T12" t="n">
-        <v>7509</v>
+        <v>7511</v>
       </c>
       <c r="U12" t="n">
-        <v>3754</v>
+        <v>3756</v>
       </c>
       <c r="V12" t="n">
-        <v>6821</v>
+        <v>6825</v>
       </c>
       <c r="W12" t="n">
         <v>27.3</v>
@@ -1692,16 +1692,16 @@
         <v>4853</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M16" t="n">
         <v>6492</v>
       </c>
       <c r="N16" t="n">
-        <v>50119</v>
+        <v>50139</v>
       </c>
       <c r="O16" t="n">
-        <v>22009</v>
+        <v>21989</v>
       </c>
       <c r="P16" t="n">
         <v>3099</v>
@@ -1713,16 +1713,16 @@
         <v>11827</v>
       </c>
       <c r="S16" t="n">
-        <v>9782</v>
+        <v>9762</v>
       </c>
       <c r="T16" t="n">
-        <v>6603</v>
+        <v>6597</v>
       </c>
       <c r="U16" t="n">
-        <v>3301</v>
+        <v>3298</v>
       </c>
       <c r="V16" t="n">
-        <v>-122</v>
+        <v>-133</v>
       </c>
       <c r="W16" t="n">
         <v>-0.6</v>
@@ -1852,16 +1852,16 @@
         <v>926</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>39258</v>
+        <v>39278</v>
       </c>
       <c r="O18" t="n">
-        <v>31981</v>
+        <v>31961</v>
       </c>
       <c r="P18" t="n">
         <v>1000</v>
@@ -1873,16 +1873,16 @@
         <v>9687</v>
       </c>
       <c r="S18" t="n">
-        <v>23794</v>
+        <v>23774</v>
       </c>
       <c r="T18" t="n">
-        <v>9594</v>
+        <v>9588</v>
       </c>
       <c r="U18" t="n">
-        <v>4797</v>
+        <v>4794</v>
       </c>
       <c r="V18" t="n">
-        <v>9403</v>
+        <v>9392</v>
       </c>
       <c r="W18" t="n">
         <v>29.4</v>
@@ -2172,16 +2172,16 @@
         <v>805</v>
       </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>33544</v>
+        <v>33535</v>
       </c>
       <c r="O22" t="n">
-        <v>28356</v>
+        <v>28365</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2193,16 +2193,16 @@
         <v>8528</v>
       </c>
       <c r="S22" t="n">
-        <v>19828</v>
+        <v>19837</v>
       </c>
       <c r="T22" t="n">
-        <v>8507</v>
+        <v>8510</v>
       </c>
       <c r="U22" t="n">
-        <v>4253</v>
+        <v>4255</v>
       </c>
       <c r="V22" t="n">
-        <v>7068</v>
+        <v>7073</v>
       </c>
       <c r="W22" t="n">
         <v>24.9</v>
@@ -2406,16 +2406,16 @@
         <v>797</v>
       </c>
       <c r="L25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>10008</v>
       </c>
       <c r="N25" t="n">
-        <v>45752</v>
+        <v>45745</v>
       </c>
       <c r="O25" t="n">
-        <v>15562</v>
+        <v>15569</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2427,16 +2427,16 @@
         <v>7673</v>
       </c>
       <c r="S25" t="n">
-        <v>7889</v>
+        <v>7896</v>
       </c>
       <c r="T25" t="n">
-        <v>4669</v>
+        <v>4671</v>
       </c>
       <c r="U25" t="n">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="V25" t="n">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="W25" t="n">
         <v>5.7</v>
@@ -2484,16 +2484,16 @@
         <v>797</v>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>8782</v>
       </c>
       <c r="N26" t="n">
-        <v>45097</v>
+        <v>45088</v>
       </c>
       <c r="O26" t="n">
-        <v>16217</v>
+        <v>16226</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2505,16 +2505,16 @@
         <v>7673</v>
       </c>
       <c r="S26" t="n">
-        <v>8544</v>
+        <v>8553</v>
       </c>
       <c r="T26" t="n">
-        <v>4865</v>
+        <v>4868</v>
       </c>
       <c r="U26" t="n">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="V26" t="n">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="W26" t="n">
         <v>7.7</v>
@@ -2640,16 +2640,16 @@
         <v>797</v>
       </c>
       <c r="L28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>10008</v>
       </c>
       <c r="N28" t="n">
-        <v>44477</v>
+        <v>44470</v>
       </c>
       <c r="O28" t="n">
-        <v>16837</v>
+        <v>16844</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2661,16 +2661,16 @@
         <v>7673</v>
       </c>
       <c r="S28" t="n">
-        <v>9164</v>
+        <v>9171</v>
       </c>
       <c r="T28" t="n">
-        <v>5051</v>
+        <v>5053</v>
       </c>
       <c r="U28" t="n">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="V28" t="n">
-        <v>1587</v>
+        <v>1591</v>
       </c>
       <c r="W28" t="n">
         <v>9.4</v>
@@ -2874,16 +2874,16 @@
         <v>765</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M31" t="n">
         <v>2944</v>
       </c>
       <c r="N31" t="n">
-        <v>35431</v>
+        <v>35451</v>
       </c>
       <c r="O31" t="n">
-        <v>23441</v>
+        <v>23421</v>
       </c>
       <c r="P31" t="n">
         <v>769</v>
@@ -2895,16 +2895,16 @@
         <v>8295</v>
       </c>
       <c r="S31" t="n">
-        <v>19676</v>
+        <v>19656</v>
       </c>
       <c r="T31" t="n">
-        <v>7032</v>
+        <v>7026</v>
       </c>
       <c r="U31" t="n">
-        <v>3516</v>
+        <v>3513</v>
       </c>
       <c r="V31" t="n">
-        <v>9128</v>
+        <v>9117</v>
       </c>
       <c r="W31" t="n">
         <v>38.9</v>
@@ -2956,16 +2956,16 @@
         <v>765</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M32" t="n">
         <v>2944</v>
       </c>
       <c r="N32" t="n">
-        <v>35429</v>
+        <v>35449</v>
       </c>
       <c r="O32" t="n">
-        <v>23443</v>
+        <v>23423</v>
       </c>
       <c r="P32" t="n">
         <v>1769</v>
@@ -2977,19 +2977,19 @@
         <v>8295</v>
       </c>
       <c r="S32" t="n">
-        <v>15979</v>
+        <v>15959</v>
       </c>
       <c r="T32" t="n">
-        <v>7033</v>
+        <v>7027</v>
       </c>
       <c r="U32" t="n">
-        <v>3516</v>
+        <v>3513</v>
       </c>
       <c r="V32" t="n">
-        <v>5430</v>
+        <v>5419</v>
       </c>
       <c r="W32" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3194,16 +3194,16 @@
         <v>753</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M35" t="n">
         <v>4053</v>
       </c>
       <c r="N35" t="n">
-        <v>35966</v>
+        <v>35986</v>
       </c>
       <c r="O35" t="n">
-        <v>21934</v>
+        <v>21914</v>
       </c>
       <c r="P35" t="n">
         <v>7352</v>
@@ -3215,19 +3215,19 @@
         <v>6691</v>
       </c>
       <c r="S35" t="n">
-        <v>12390</v>
+        <v>12370</v>
       </c>
       <c r="T35" t="n">
-        <v>6580</v>
+        <v>6574</v>
       </c>
       <c r="U35" t="n">
-        <v>3290</v>
+        <v>3287</v>
       </c>
       <c r="V35" t="n">
-        <v>2520</v>
+        <v>2509</v>
       </c>
       <c r="W35" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -3276,16 +3276,16 @@
         <v>1329</v>
       </c>
       <c r="L36" t="n">
-        <v>2939</v>
+        <v>2959</v>
       </c>
       <c r="M36" t="n">
         <v>4046</v>
       </c>
       <c r="N36" t="n">
-        <v>39468</v>
+        <v>39488</v>
       </c>
       <c r="O36" t="n">
-        <v>18332</v>
+        <v>18312</v>
       </c>
       <c r="P36" t="n">
         <v>769</v>
@@ -3297,19 +3297,19 @@
         <v>8295</v>
       </c>
       <c r="S36" t="n">
-        <v>9677</v>
+        <v>9657</v>
       </c>
       <c r="T36" t="n">
-        <v>5500</v>
+        <v>5494</v>
       </c>
       <c r="U36" t="n">
-        <v>2750</v>
+        <v>2747</v>
       </c>
       <c r="V36" t="n">
-        <v>1428</v>
+        <v>1417</v>
       </c>
       <c r="W36" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -3358,16 +3358,16 @@
         <v>1329</v>
       </c>
       <c r="L37" t="n">
-        <v>2538</v>
+        <v>2558</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>35021</v>
+        <v>35041</v>
       </c>
       <c r="O37" t="n">
-        <v>22779</v>
+        <v>22759</v>
       </c>
       <c r="P37" t="n">
         <v>769</v>
@@ -3379,19 +3379,19 @@
         <v>8295</v>
       </c>
       <c r="S37" t="n">
-        <v>14228</v>
+        <v>14208</v>
       </c>
       <c r="T37" t="n">
-        <v>6834</v>
+        <v>6828</v>
       </c>
       <c r="U37" t="n">
-        <v>3417</v>
+        <v>3414</v>
       </c>
       <c r="V37" t="n">
-        <v>3977</v>
+        <v>3966</v>
       </c>
       <c r="W37" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -3440,16 +3440,16 @@
         <v>740</v>
       </c>
       <c r="L38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>28396</v>
+        <v>28385</v>
       </c>
       <c r="O38" t="n">
-        <v>28544</v>
+        <v>28555</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3461,19 +3461,19 @@
         <v>3497</v>
       </c>
       <c r="S38" t="n">
-        <v>25047</v>
+        <v>25058</v>
       </c>
       <c r="T38" t="n">
-        <v>8563</v>
+        <v>8566</v>
       </c>
       <c r="U38" t="n">
-        <v>4282</v>
+        <v>4283</v>
       </c>
       <c r="V38" t="n">
-        <v>12202</v>
+        <v>12208</v>
       </c>
       <c r="W38" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="X38" t="inlineStr"/>
     </row>
@@ -3518,16 +3518,16 @@
         <v>721</v>
       </c>
       <c r="L39" t="n">
-        <v>11136</v>
+        <v>11156</v>
       </c>
       <c r="M39" t="n">
         <v>3893</v>
       </c>
       <c r="N39" t="n">
-        <v>45585</v>
+        <v>45605</v>
       </c>
       <c r="O39" t="n">
-        <v>9890</v>
+        <v>9870</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -3539,16 +3539,16 @@
         <v>8414</v>
       </c>
       <c r="S39" t="n">
-        <v>8322</v>
+        <v>8302</v>
       </c>
       <c r="T39" t="n">
-        <v>2967</v>
+        <v>2961</v>
       </c>
       <c r="U39" t="n">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="V39" t="n">
-        <v>3872</v>
+        <v>3860</v>
       </c>
       <c r="W39" t="n">
         <v>39.1</v>
@@ -3752,16 +3752,16 @@
         <v>1217</v>
       </c>
       <c r="L42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>4761</v>
       </c>
       <c r="N42" t="n">
-        <v>33700</v>
+        <v>33690</v>
       </c>
       <c r="O42" t="n">
-        <v>19200</v>
+        <v>19210</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -3773,16 +3773,16 @@
         <v>6448</v>
       </c>
       <c r="S42" t="n">
-        <v>12752</v>
+        <v>12762</v>
       </c>
       <c r="T42" t="n">
-        <v>5760</v>
+        <v>5763</v>
       </c>
       <c r="U42" t="n">
-        <v>2880</v>
+        <v>2882</v>
       </c>
       <c r="V42" t="n">
-        <v>4112</v>
+        <v>4118</v>
       </c>
       <c r="W42" t="n">
         <v>21.4</v>
@@ -3908,16 +3908,16 @@
         <v>687</v>
       </c>
       <c r="L44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>2643</v>
       </c>
       <c r="N44" t="n">
-        <v>30915</v>
+        <v>30908</v>
       </c>
       <c r="O44" t="n">
-        <v>21943</v>
+        <v>21950</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -3929,16 +3929,16 @@
         <v>6380</v>
       </c>
       <c r="S44" t="n">
-        <v>15563</v>
+        <v>15570</v>
       </c>
       <c r="T44" t="n">
-        <v>6583</v>
+        <v>6585</v>
       </c>
       <c r="U44" t="n">
-        <v>3291</v>
+        <v>3292</v>
       </c>
       <c r="V44" t="n">
-        <v>5689</v>
+        <v>5692</v>
       </c>
       <c r="W44" t="n">
         <v>25.9</v>
@@ -4220,16 +4220,16 @@
         <v>662</v>
       </c>
       <c r="L48" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>2659</v>
       </c>
       <c r="N48" t="n">
-        <v>38582</v>
+        <v>38561</v>
       </c>
       <c r="O48" t="n">
-        <v>12318</v>
+        <v>12339</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -4241,19 +4241,19 @@
         <v>10434</v>
       </c>
       <c r="S48" t="n">
-        <v>1884</v>
+        <v>1905</v>
       </c>
       <c r="T48" t="n">
-        <v>3695</v>
+        <v>3702</v>
       </c>
       <c r="U48" t="n">
-        <v>1848</v>
+        <v>1851</v>
       </c>
       <c r="V48" t="n">
-        <v>-3659</v>
+        <v>-3648</v>
       </c>
       <c r="W48" t="n">
-        <v>-29.7</v>
+        <v>-29.6</v>
       </c>
       <c r="X48" t="inlineStr"/>
     </row>
@@ -4298,16 +4298,16 @@
         <v>659</v>
       </c>
       <c r="L49" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>3549</v>
       </c>
       <c r="N49" t="n">
-        <v>30953</v>
+        <v>30942</v>
       </c>
       <c r="O49" t="n">
-        <v>19750</v>
+        <v>19761</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -4319,16 +4319,16 @@
         <v>6380</v>
       </c>
       <c r="S49" t="n">
-        <v>13370</v>
+        <v>13381</v>
       </c>
       <c r="T49" t="n">
-        <v>5925</v>
+        <v>5928</v>
       </c>
       <c r="U49" t="n">
-        <v>2962</v>
+        <v>2964</v>
       </c>
       <c r="V49" t="n">
-        <v>4482</v>
+        <v>4489</v>
       </c>
       <c r="W49" t="n">
         <v>22.7</v>
@@ -4454,16 +4454,16 @@
         <v>652</v>
       </c>
       <c r="L51" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>2622</v>
       </c>
       <c r="N51" t="n">
-        <v>35881</v>
+        <v>35872</v>
       </c>
       <c r="O51" t="n">
-        <v>14286</v>
+        <v>14295</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
@@ -4475,16 +4475,16 @@
         <v>10434</v>
       </c>
       <c r="S51" t="n">
-        <v>3852</v>
+        <v>3861</v>
       </c>
       <c r="T51" t="n">
-        <v>4286</v>
+        <v>4288</v>
       </c>
       <c r="U51" t="n">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="V51" t="n">
-        <v>-2577</v>
+        <v>-2572</v>
       </c>
       <c r="W51" t="n">
         <v>-18</v>
@@ -4532,16 +4532,16 @@
         <v>647</v>
       </c>
       <c r="L52" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>2490</v>
       </c>
       <c r="N52" t="n">
-        <v>29503</v>
+        <v>29489</v>
       </c>
       <c r="O52" t="n">
-        <v>20297</v>
+        <v>20311</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -4553,16 +4553,16 @@
         <v>6034</v>
       </c>
       <c r="S52" t="n">
-        <v>14263</v>
+        <v>14277</v>
       </c>
       <c r="T52" t="n">
-        <v>6089</v>
+        <v>6093</v>
       </c>
       <c r="U52" t="n">
-        <v>3045</v>
+        <v>3047</v>
       </c>
       <c r="V52" t="n">
-        <v>5129</v>
+        <v>5137</v>
       </c>
       <c r="W52" t="n">
         <v>25.3</v>
@@ -4610,16 +4610,16 @@
         <v>637</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M53" t="n">
         <v>356</v>
       </c>
       <c r="N53" t="n">
-        <v>26948</v>
+        <v>26968</v>
       </c>
       <c r="O53" t="n">
-        <v>22025</v>
+        <v>22005</v>
       </c>
       <c r="P53" t="n">
         <v>4824</v>
@@ -4631,16 +4631,16 @@
         <v>9352</v>
       </c>
       <c r="S53" t="n">
-        <v>11749</v>
+        <v>11729</v>
       </c>
       <c r="T53" t="n">
-        <v>6608</v>
+        <v>6602</v>
       </c>
       <c r="U53" t="n">
-        <v>3304</v>
+        <v>3301</v>
       </c>
       <c r="V53" t="n">
-        <v>1838</v>
+        <v>1827</v>
       </c>
       <c r="W53" t="n">
         <v>8.300000000000001</v>
@@ -4692,16 +4692,16 @@
         <v>631</v>
       </c>
       <c r="L54" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>6458</v>
       </c>
       <c r="N54" t="n">
-        <v>31893</v>
+        <v>31872</v>
       </c>
       <c r="O54" t="n">
-        <v>16679</v>
+        <v>16700</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -4713,19 +4713,19 @@
         <v>6448</v>
       </c>
       <c r="S54" t="n">
-        <v>10231</v>
+        <v>10252</v>
       </c>
       <c r="T54" t="n">
-        <v>5004</v>
+        <v>5010</v>
       </c>
       <c r="U54" t="n">
-        <v>2502</v>
+        <v>2505</v>
       </c>
       <c r="V54" t="n">
-        <v>2725</v>
+        <v>2737</v>
       </c>
       <c r="W54" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="X54" t="inlineStr"/>
     </row>
@@ -4926,16 +4926,16 @@
         <v>623</v>
       </c>
       <c r="L57" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>25734</v>
+        <v>25723</v>
       </c>
       <c r="O57" t="n">
-        <v>22166</v>
+        <v>22177</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -4947,16 +4947,16 @@
         <v>5882</v>
       </c>
       <c r="S57" t="n">
-        <v>16284</v>
+        <v>16295</v>
       </c>
       <c r="T57" t="n">
-        <v>6650</v>
+        <v>6653</v>
       </c>
       <c r="U57" t="n">
-        <v>3325</v>
+        <v>3327</v>
       </c>
       <c r="V57" t="n">
-        <v>6309</v>
+        <v>6315</v>
       </c>
       <c r="W57" t="n">
         <v>28.5</v>
@@ -5004,16 +5004,16 @@
         <v>621</v>
       </c>
       <c r="L58" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>26173</v>
+        <v>26163</v>
       </c>
       <c r="O58" t="n">
-        <v>21627</v>
+        <v>21637</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -5025,16 +5025,16 @@
         <v>5662</v>
       </c>
       <c r="S58" t="n">
-        <v>15965</v>
+        <v>15975</v>
       </c>
       <c r="T58" t="n">
-        <v>6488</v>
+        <v>6491</v>
       </c>
       <c r="U58" t="n">
-        <v>3244</v>
+        <v>3246</v>
       </c>
       <c r="V58" t="n">
-        <v>6233</v>
+        <v>6238</v>
       </c>
       <c r="W58" t="n">
         <v>28.8</v>
@@ -5082,16 +5082,16 @@
         <v>614</v>
       </c>
       <c r="L59" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>2363</v>
       </c>
       <c r="N59" t="n">
-        <v>27843</v>
+        <v>27828</v>
       </c>
       <c r="O59" t="n">
-        <v>19418</v>
+        <v>19433</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
@@ -5103,19 +5103,19 @@
         <v>5662</v>
       </c>
       <c r="S59" t="n">
-        <v>13756</v>
+        <v>13771</v>
       </c>
       <c r="T59" t="n">
-        <v>5825</v>
+        <v>5830</v>
       </c>
       <c r="U59" t="n">
-        <v>2913</v>
+        <v>2915</v>
       </c>
       <c r="V59" t="n">
-        <v>5018</v>
+        <v>5026</v>
       </c>
       <c r="W59" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="X59" t="inlineStr"/>
     </row>
@@ -5800,16 +5800,16 @@
         <v>851</v>
       </c>
       <c r="L68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
         <v>3951</v>
       </c>
       <c r="N68" t="n">
-        <v>31504</v>
+        <v>31496</v>
       </c>
       <c r="O68" t="n">
-        <v>12396</v>
+        <v>12404</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -5821,16 +5821,16 @@
         <v>4971</v>
       </c>
       <c r="S68" t="n">
-        <v>7425</v>
+        <v>7433</v>
       </c>
       <c r="T68" t="n">
-        <v>3719</v>
+        <v>3721</v>
       </c>
       <c r="U68" t="n">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="V68" t="n">
-        <v>1847</v>
+        <v>1851</v>
       </c>
       <c r="W68" t="n">
         <v>14.9</v>
@@ -6124,16 +6124,16 @@
         <v>569</v>
       </c>
       <c r="L72" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>2190</v>
       </c>
       <c r="N72" t="n">
-        <v>29416</v>
+        <v>29408</v>
       </c>
       <c r="O72" t="n">
-        <v>14384</v>
+        <v>14392</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -6145,16 +6145,16 @@
         <v>4565</v>
       </c>
       <c r="S72" t="n">
-        <v>9819</v>
+        <v>9827</v>
       </c>
       <c r="T72" t="n">
-        <v>4315</v>
+        <v>4318</v>
       </c>
       <c r="U72" t="n">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="V72" t="n">
-        <v>3346</v>
+        <v>3351</v>
       </c>
       <c r="W72" t="n">
         <v>23.3</v>
@@ -6202,16 +6202,16 @@
         <v>569</v>
       </c>
       <c r="L73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
         <v>1758</v>
       </c>
       <c r="N73" t="n">
-        <v>28971</v>
+        <v>28963</v>
       </c>
       <c r="O73" t="n">
-        <v>14829</v>
+        <v>14837</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -6223,16 +6223,16 @@
         <v>4971</v>
       </c>
       <c r="S73" t="n">
-        <v>9858</v>
+        <v>9866</v>
       </c>
       <c r="T73" t="n">
-        <v>4449</v>
+        <v>4451</v>
       </c>
       <c r="U73" t="n">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="V73" t="n">
-        <v>3185</v>
+        <v>3189</v>
       </c>
       <c r="W73" t="n">
         <v>21.5</v>
@@ -6362,16 +6362,16 @@
         <v>569</v>
       </c>
       <c r="L75" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>7110</v>
       </c>
       <c r="N75" t="n">
-        <v>31918</v>
+        <v>31911</v>
       </c>
       <c r="O75" t="n">
-        <v>11860</v>
+        <v>11867</v>
       </c>
       <c r="P75" t="n">
         <v>0</v>
@@ -6383,16 +6383,16 @@
         <v>4565</v>
       </c>
       <c r="S75" t="n">
-        <v>7295</v>
+        <v>7302</v>
       </c>
       <c r="T75" t="n">
-        <v>3558</v>
+        <v>3560</v>
       </c>
       <c r="U75" t="n">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="V75" t="n">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="W75" t="n">
         <v>16.5</v>
@@ -6518,16 +6518,16 @@
         <v>569</v>
       </c>
       <c r="L77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
         <v>7110</v>
       </c>
       <c r="N77" t="n">
-        <v>31920</v>
+        <v>31912</v>
       </c>
       <c r="O77" t="n">
-        <v>11858</v>
+        <v>11866</v>
       </c>
       <c r="P77" t="n">
         <v>0</v>
@@ -6539,16 +6539,16 @@
         <v>4565</v>
       </c>
       <c r="S77" t="n">
-        <v>7293</v>
+        <v>7301</v>
       </c>
       <c r="T77" t="n">
-        <v>3557</v>
+        <v>3560</v>
       </c>
       <c r="U77" t="n">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="V77" t="n">
-        <v>1957</v>
+        <v>1961</v>
       </c>
       <c r="W77" t="n">
         <v>16.5</v>
@@ -6674,16 +6674,16 @@
         <v>569</v>
       </c>
       <c r="L79" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
         <v>7111</v>
       </c>
       <c r="N79" t="n">
-        <v>32359</v>
+        <v>32351</v>
       </c>
       <c r="O79" t="n">
-        <v>11419</v>
+        <v>11427</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -6695,19 +6695,19 @@
         <v>4565</v>
       </c>
       <c r="S79" t="n">
-        <v>6854</v>
+        <v>6862</v>
       </c>
       <c r="T79" t="n">
-        <v>3426</v>
+        <v>3428</v>
       </c>
       <c r="U79" t="n">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="V79" t="n">
-        <v>1715</v>
+        <v>1720</v>
       </c>
       <c r="W79" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="X79" t="inlineStr"/>
     </row>
@@ -6830,16 +6830,16 @@
         <v>541</v>
       </c>
       <c r="L81" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
         <v>2079</v>
       </c>
       <c r="N81" t="n">
-        <v>24267</v>
+        <v>24258</v>
       </c>
       <c r="O81" t="n">
-        <v>17313</v>
+        <v>17322</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -6851,16 +6851,16 @@
         <v>4768</v>
       </c>
       <c r="S81" t="n">
-        <v>12545</v>
+        <v>12554</v>
       </c>
       <c r="T81" t="n">
-        <v>5194</v>
+        <v>5197</v>
       </c>
       <c r="U81" t="n">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="V81" t="n">
-        <v>4754</v>
+        <v>4759</v>
       </c>
       <c r="W81" t="n">
         <v>27.5</v>
@@ -6908,16 +6908,16 @@
         <v>519</v>
       </c>
       <c r="L82" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>3591</v>
       </c>
       <c r="N82" t="n">
-        <v>26378</v>
+        <v>26370</v>
       </c>
       <c r="O82" t="n">
-        <v>13522</v>
+        <v>13530</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
@@ -6929,16 +6929,16 @@
         <v>4196</v>
       </c>
       <c r="S82" t="n">
-        <v>9326</v>
+        <v>9334</v>
       </c>
       <c r="T82" t="n">
-        <v>4057</v>
+        <v>4059</v>
       </c>
       <c r="U82" t="n">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="V82" t="n">
-        <v>3241</v>
+        <v>3246</v>
       </c>
       <c r="W82" t="n">
         <v>24</v>
@@ -6986,16 +6986,16 @@
         <v>510</v>
       </c>
       <c r="L83" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>2432</v>
       </c>
       <c r="N83" t="n">
-        <v>23437</v>
+        <v>23425</v>
       </c>
       <c r="O83" t="n">
-        <v>15824</v>
+        <v>15836</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -7007,19 +7007,19 @@
         <v>6815</v>
       </c>
       <c r="S83" t="n">
-        <v>9009</v>
+        <v>9021</v>
       </c>
       <c r="T83" t="n">
-        <v>4747</v>
+        <v>4751</v>
       </c>
       <c r="U83" t="n">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="V83" t="n">
-        <v>1888</v>
+        <v>1895</v>
       </c>
       <c r="W83" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="X83" t="inlineStr"/>
     </row>
@@ -7142,16 +7142,16 @@
         <v>786</v>
       </c>
       <c r="L85" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
         <v>234</v>
       </c>
       <c r="N85" t="n">
-        <v>22990</v>
+        <v>22975</v>
       </c>
       <c r="O85" t="n">
-        <v>15910</v>
+        <v>15925</v>
       </c>
       <c r="P85" t="n">
         <v>0</v>
@@ -7163,16 +7163,16 @@
         <v>4971</v>
       </c>
       <c r="S85" t="n">
-        <v>10939</v>
+        <v>10954</v>
       </c>
       <c r="T85" t="n">
-        <v>4773</v>
+        <v>4778</v>
       </c>
       <c r="U85" t="n">
-        <v>2386</v>
+        <v>2389</v>
       </c>
       <c r="V85" t="n">
-        <v>3780</v>
+        <v>3788</v>
       </c>
       <c r="W85" t="n">
         <v>23.8</v>
@@ -7298,16 +7298,16 @@
         <v>467</v>
       </c>
       <c r="L87" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>3235</v>
       </c>
       <c r="N87" t="n">
-        <v>23067</v>
+        <v>23059</v>
       </c>
       <c r="O87" t="n">
-        <v>12861</v>
+        <v>12869</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
@@ -7319,16 +7319,16 @@
         <v>6422</v>
       </c>
       <c r="S87" t="n">
-        <v>6439</v>
+        <v>6447</v>
       </c>
       <c r="T87" t="n">
-        <v>3858</v>
+        <v>3861</v>
       </c>
       <c r="U87" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="V87" t="n">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="W87" t="n">
         <v>5.1</v>
@@ -7454,16 +7454,16 @@
         <v>467</v>
       </c>
       <c r="L89" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>3231</v>
       </c>
       <c r="N89" t="n">
-        <v>22835</v>
+        <v>22824</v>
       </c>
       <c r="O89" t="n">
-        <v>13065</v>
+        <v>13076</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
@@ -7475,16 +7475,16 @@
         <v>3737</v>
       </c>
       <c r="S89" t="n">
-        <v>9328</v>
+        <v>9339</v>
       </c>
       <c r="T89" t="n">
-        <v>3920</v>
+        <v>3923</v>
       </c>
       <c r="U89" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="V89" t="n">
-        <v>3449</v>
+        <v>3455</v>
       </c>
       <c r="W89" t="n">
         <v>26.4</v>
@@ -7532,16 +7532,16 @@
         <v>467</v>
       </c>
       <c r="L90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
         <v>1795</v>
       </c>
       <c r="N90" t="n">
-        <v>21377</v>
+        <v>21367</v>
       </c>
       <c r="O90" t="n">
-        <v>14523</v>
+        <v>14533</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -7553,16 +7553,16 @@
         <v>3737</v>
       </c>
       <c r="S90" t="n">
-        <v>10786</v>
+        <v>10796</v>
       </c>
       <c r="T90" t="n">
-        <v>4357</v>
+        <v>4360</v>
       </c>
       <c r="U90" t="n">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="V90" t="n">
-        <v>4251</v>
+        <v>4256</v>
       </c>
       <c r="W90" t="n">
         <v>29.3</v>
@@ -8468,16 +8468,16 @@
         <v>778</v>
       </c>
       <c r="L102" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
         <v>3046</v>
       </c>
       <c r="N102" t="n">
-        <v>21655</v>
+        <v>21645</v>
       </c>
       <c r="O102" t="n">
-        <v>12187</v>
+        <v>12197</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
@@ -8489,19 +8489,19 @@
         <v>3419</v>
       </c>
       <c r="S102" t="n">
-        <v>8768</v>
+        <v>8778</v>
       </c>
       <c r="T102" t="n">
-        <v>3656</v>
+        <v>3659</v>
       </c>
       <c r="U102" t="n">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="V102" t="n">
-        <v>3284</v>
+        <v>3289</v>
       </c>
       <c r="W102" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="X102" t="inlineStr"/>
     </row>
@@ -8546,16 +8546,16 @@
         <v>424</v>
       </c>
       <c r="L103" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
         <v>2938</v>
       </c>
       <c r="N103" t="n">
-        <v>20572</v>
+        <v>20565</v>
       </c>
       <c r="O103" t="n">
-        <v>12071</v>
+        <v>12078</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
@@ -8567,16 +8567,16 @@
         <v>3419</v>
       </c>
       <c r="S103" t="n">
-        <v>8652</v>
+        <v>8659</v>
       </c>
       <c r="T103" t="n">
-        <v>3621</v>
+        <v>3623</v>
       </c>
       <c r="U103" t="n">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="V103" t="n">
-        <v>3220</v>
+        <v>3224</v>
       </c>
       <c r="W103" t="n">
         <v>26.7</v>
@@ -8624,16 +8624,16 @@
         <v>424</v>
       </c>
       <c r="L104" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
         <v>1632</v>
       </c>
       <c r="N104" t="n">
-        <v>18985</v>
+        <v>18976</v>
       </c>
       <c r="O104" t="n">
-        <v>13658</v>
+        <v>13667</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
@@ -8645,16 +8645,16 @@
         <v>3419</v>
       </c>
       <c r="S104" t="n">
-        <v>10239</v>
+        <v>10248</v>
       </c>
       <c r="T104" t="n">
-        <v>4097</v>
+        <v>4100</v>
       </c>
       <c r="U104" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="V104" t="n">
-        <v>4093</v>
+        <v>4098</v>
       </c>
       <c r="W104" t="n">
         <v>30</v>
@@ -8780,16 +8780,16 @@
         <v>550</v>
       </c>
       <c r="L106" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
         <v>2151</v>
       </c>
       <c r="N106" t="n">
-        <v>15764</v>
+        <v>15756</v>
       </c>
       <c r="O106" t="n">
-        <v>8136</v>
+        <v>8144</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
@@ -8801,16 +8801,16 @@
         <v>3233</v>
       </c>
       <c r="S106" t="n">
-        <v>4903</v>
+        <v>4911</v>
       </c>
       <c r="T106" t="n">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="U106" t="n">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="V106" t="n">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="W106" t="n">
         <v>15.3</v>
@@ -8858,16 +8858,16 @@
         <v>535</v>
       </c>
       <c r="L107" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
         <v>2094</v>
       </c>
       <c r="N107" t="n">
-        <v>15381</v>
+        <v>15366</v>
       </c>
       <c r="O107" t="n">
-        <v>7882</v>
+        <v>7897</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
@@ -8879,19 +8879,19 @@
         <v>3233</v>
       </c>
       <c r="S107" t="n">
-        <v>4649</v>
+        <v>4664</v>
       </c>
       <c r="T107" t="n">
-        <v>2365</v>
+        <v>2369</v>
       </c>
       <c r="U107" t="n">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="V107" t="n">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="W107" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="X107" t="inlineStr"/>
     </row>
@@ -8936,16 +8936,16 @@
         <v>298</v>
       </c>
       <c r="L108" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
         <v>1861</v>
       </c>
       <c r="N108" t="n">
-        <v>14205</v>
+        <v>14194</v>
       </c>
       <c r="O108" t="n">
-        <v>8695</v>
+        <v>8706</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
@@ -8957,16 +8957,16 @@
         <v>3419</v>
       </c>
       <c r="S108" t="n">
-        <v>5276</v>
+        <v>5287</v>
       </c>
       <c r="T108" t="n">
-        <v>2608</v>
+        <v>2612</v>
       </c>
       <c r="U108" t="n">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="V108" t="n">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="W108" t="n">
         <v>15.7</v>
@@ -9014,16 +9014,16 @@
         <v>233</v>
       </c>
       <c r="L109" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
         <v>895</v>
       </c>
       <c r="N109" t="n">
-        <v>10136</v>
+        <v>10125</v>
       </c>
       <c r="O109" t="n">
-        <v>7764</v>
+        <v>7775</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
@@ -9035,16 +9035,16 @@
         <v>2889</v>
       </c>
       <c r="S109" t="n">
-        <v>4875</v>
+        <v>4886</v>
       </c>
       <c r="T109" t="n">
-        <v>2329</v>
+        <v>2332</v>
       </c>
       <c r="U109" t="n">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="V109" t="n">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="W109" t="n">
         <v>17.8</v>
@@ -9092,16 +9092,16 @@
         <v>751</v>
       </c>
       <c r="L110" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
         <v>2938</v>
       </c>
       <c r="N110" t="n">
-        <v>4345</v>
+        <v>4336</v>
       </c>
       <c r="O110" t="n">
-        <v>-4345</v>
+        <v>-4336</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
@@ -9113,16 +9113,16 @@
         <v>3419</v>
       </c>
       <c r="S110" t="n">
-        <v>-7764</v>
+        <v>-7755</v>
       </c>
       <c r="T110" t="n">
-        <v>-1304</v>
+        <v>-1301</v>
       </c>
       <c r="U110" t="n">
-        <v>-652</v>
+        <v>-650</v>
       </c>
       <c r="V110" t="n">
-        <v>-5809</v>
+        <v>-5804</v>
       </c>
       <c r="X110" t="inlineStr"/>
     </row>
@@ -9242,16 +9242,16 @@
         <v>874</v>
       </c>
       <c r="L112" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
         <v>3362</v>
       </c>
       <c r="N112" t="n">
-        <v>5969</v>
+        <v>5959</v>
       </c>
       <c r="O112" t="n">
-        <v>-5969</v>
+        <v>-5959</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
@@ -9263,16 +9263,16 @@
         <v>7453</v>
       </c>
       <c r="S112" t="n">
-        <v>-13422</v>
+        <v>-13412</v>
       </c>
       <c r="T112" t="n">
-        <v>-1791</v>
+        <v>-1788</v>
       </c>
       <c r="U112" t="n">
-        <v>-895</v>
+        <v>-894</v>
       </c>
       <c r="V112" t="n">
-        <v>-10736</v>
+        <v>-10730</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
@@ -9351,16 +9351,16 @@
         <v>987</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M114" t="n">
         <v>3795</v>
       </c>
       <c r="N114" t="n">
-        <v>44143</v>
+        <v>44163</v>
       </c>
       <c r="O114" t="n">
-        <v>31757</v>
+        <v>31737</v>
       </c>
       <c r="P114" t="n">
         <v>3245</v>
@@ -9372,19 +9372,19 @@
         <v>11477</v>
       </c>
       <c r="S114" t="n">
-        <v>19834</v>
+        <v>19814</v>
       </c>
       <c r="T114" t="n">
-        <v>9527</v>
+        <v>9521</v>
       </c>
       <c r="U114" t="n">
-        <v>4764</v>
+        <v>4761</v>
       </c>
       <c r="V114" t="n">
-        <v>5543</v>
+        <v>5532</v>
       </c>
       <c r="W114" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
@@ -9433,16 +9433,16 @@
         <v>994</v>
       </c>
       <c r="L115" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
         <v>2745</v>
       </c>
       <c r="N115" t="n">
-        <v>32479</v>
+        <v>32470</v>
       </c>
       <c r="O115" t="n">
-        <v>22421</v>
+        <v>22430</v>
       </c>
       <c r="P115" t="n">
         <v>0</v>
@@ -9454,16 +9454,16 @@
         <v>10263</v>
       </c>
       <c r="S115" t="n">
-        <v>12158</v>
+        <v>12167</v>
       </c>
       <c r="T115" t="n">
-        <v>6726</v>
+        <v>6729</v>
       </c>
       <c r="U115" t="n">
-        <v>3363</v>
+        <v>3364</v>
       </c>
       <c r="V115" t="n">
-        <v>2069</v>
+        <v>2074</v>
       </c>
       <c r="W115" t="n">
         <v>9.199999999999999</v>
@@ -9515,16 +9515,16 @@
         <v>994</v>
       </c>
       <c r="L116" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>29038</v>
+        <v>29027</v>
       </c>
       <c r="O116" t="n">
-        <v>25862</v>
+        <v>25873</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
@@ -9536,16 +9536,16 @@
         <v>10263</v>
       </c>
       <c r="S116" t="n">
-        <v>15599</v>
+        <v>15610</v>
       </c>
       <c r="T116" t="n">
-        <v>7759</v>
+        <v>7762</v>
       </c>
       <c r="U116" t="n">
-        <v>3879</v>
+        <v>3881</v>
       </c>
       <c r="V116" t="n">
-        <v>3961</v>
+        <v>3967</v>
       </c>
       <c r="W116" t="n">
         <v>15.3</v>
@@ -9679,16 +9679,16 @@
         <v>531</v>
       </c>
       <c r="L118" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>25061</v>
+        <v>25045</v>
       </c>
       <c r="O118" t="n">
-        <v>15819</v>
+        <v>15835</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
@@ -9700,16 +9700,16 @@
         <v>7962</v>
       </c>
       <c r="S118" t="n">
-        <v>7857</v>
+        <v>7873</v>
       </c>
       <c r="T118" t="n">
-        <v>4746</v>
+        <v>4750</v>
       </c>
       <c r="U118" t="n">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="V118" t="n">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="W118" t="n">
         <v>4.7</v>
@@ -10007,16 +10007,16 @@
         <v>772</v>
       </c>
       <c r="L122" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
         <v>6818</v>
       </c>
       <c r="N122" t="n">
-        <v>27507</v>
+        <v>27488</v>
       </c>
       <c r="O122" t="n">
-        <v>10373</v>
+        <v>10392</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
@@ -10028,19 +10028,19 @@
         <v>6061</v>
       </c>
       <c r="S122" t="n">
-        <v>4312</v>
+        <v>4331</v>
       </c>
       <c r="T122" t="n">
-        <v>3112</v>
+        <v>3118</v>
       </c>
       <c r="U122" t="n">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="V122" t="n">
-        <v>-356</v>
+        <v>-345</v>
       </c>
       <c r="W122" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
@@ -10405,16 +10405,16 @@
         <v>310</v>
       </c>
       <c r="L127" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
         <v>2149</v>
       </c>
       <c r="N127" t="n">
-        <v>16129</v>
+        <v>16122</v>
       </c>
       <c r="O127" t="n">
-        <v>7751</v>
+        <v>7758</v>
       </c>
       <c r="P127" t="n">
         <v>0</v>
@@ -10426,16 +10426,16 @@
         <v>4287</v>
       </c>
       <c r="S127" t="n">
-        <v>3464</v>
+        <v>3471</v>
       </c>
       <c r="T127" t="n">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="U127" t="n">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="V127" t="n">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="W127" t="n">
         <v>-0.3</v>
@@ -10513,16 +10513,16 @@
         <v>1059</v>
       </c>
       <c r="L129" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>27500</v>
+        <v>27492</v>
       </c>
       <c r="O129" t="n">
-        <v>32400</v>
+        <v>32408</v>
       </c>
       <c r="P129" t="n">
         <v>0</v>
@@ -10534,19 +10534,19 @@
         <v>7340</v>
       </c>
       <c r="S129" t="n">
-        <v>25060</v>
+        <v>25068</v>
       </c>
       <c r="T129" t="n">
-        <v>9720</v>
+        <v>9722</v>
       </c>
       <c r="U129" t="n">
-        <v>4860</v>
+        <v>4861</v>
       </c>
       <c r="V129" t="n">
-        <v>10480</v>
+        <v>10484</v>
       </c>
       <c r="W129" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="X129" t="inlineStr"/>
     </row>
@@ -10673,16 +10673,16 @@
         <v>675</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M131" t="n">
         <v>2595</v>
       </c>
       <c r="N131" t="n">
-        <v>27639</v>
+        <v>27659</v>
       </c>
       <c r="O131" t="n">
-        <v>24261</v>
+        <v>24241</v>
       </c>
       <c r="P131" t="n">
         <v>1854</v>
@@ -10694,16 +10694,16 @@
         <v>8494</v>
       </c>
       <c r="S131" t="n">
-        <v>17613</v>
+        <v>17593</v>
       </c>
       <c r="T131" t="n">
-        <v>7278</v>
+        <v>7272</v>
       </c>
       <c r="U131" t="n">
-        <v>3639</v>
+        <v>3636</v>
       </c>
       <c r="V131" t="n">
-        <v>6696</v>
+        <v>6685</v>
       </c>
       <c r="W131" t="n">
         <v>27.6</v>
@@ -10755,16 +10755,16 @@
         <v>571</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M132" t="n">
         <v>3073</v>
       </c>
       <c r="N132" t="n">
-        <v>23838</v>
+        <v>23858</v>
       </c>
       <c r="O132" t="n">
-        <v>20062</v>
+        <v>20042</v>
       </c>
       <c r="P132" t="n">
         <v>3987</v>
@@ -10776,19 +10776,19 @@
         <v>9446</v>
       </c>
       <c r="S132" t="n">
-        <v>10829</v>
+        <v>10809</v>
       </c>
       <c r="T132" t="n">
-        <v>6019</v>
+        <v>6013</v>
       </c>
       <c r="U132" t="n">
-        <v>3009</v>
+        <v>3006</v>
       </c>
       <c r="V132" t="n">
-        <v>1801</v>
+        <v>1790</v>
       </c>
       <c r="W132" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
@@ -10941,16 +10941,16 @@
         <v>1702</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M135" t="n">
         <v>9163</v>
       </c>
       <c r="N135" t="n">
-        <v>78717</v>
+        <v>78737</v>
       </c>
       <c r="O135" t="n">
-        <v>52183</v>
+        <v>52163</v>
       </c>
       <c r="P135" t="n">
         <v>6317</v>
@@ -10962,16 +10962,16 @@
         <v>22283</v>
       </c>
       <c r="S135" t="n">
-        <v>28883</v>
+        <v>28863</v>
       </c>
       <c r="T135" t="n">
-        <v>15655</v>
+        <v>15649</v>
       </c>
       <c r="U135" t="n">
-        <v>7827</v>
+        <v>7824</v>
       </c>
       <c r="V135" t="n">
-        <v>5401</v>
+        <v>5390</v>
       </c>
       <c r="W135" t="n">
         <v>10.3</v>
@@ -11019,16 +11019,16 @@
         <v>1546</v>
       </c>
       <c r="L136" t="n">
-        <v>3628</v>
+        <v>3648</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>66823</v>
+        <v>66843</v>
       </c>
       <c r="O136" t="n">
-        <v>52077</v>
+        <v>52057</v>
       </c>
       <c r="P136" t="n">
         <v>0</v>
@@ -11040,16 +11040,16 @@
         <v>18384</v>
       </c>
       <c r="S136" t="n">
-        <v>35051</v>
+        <v>35031</v>
       </c>
       <c r="T136" t="n">
-        <v>15623</v>
+        <v>15617</v>
       </c>
       <c r="U136" t="n">
-        <v>7812</v>
+        <v>7809</v>
       </c>
       <c r="V136" t="n">
-        <v>11616</v>
+        <v>11605</v>
       </c>
       <c r="W136" t="n">
         <v>22.3</v>
@@ -11101,16 +11101,16 @@
         <v>1455</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M137" t="n">
         <v>7833</v>
       </c>
       <c r="N137" t="n">
-        <v>67331</v>
+        <v>67351</v>
       </c>
       <c r="O137" t="n">
-        <v>44569</v>
+        <v>44549</v>
       </c>
       <c r="P137" t="n">
         <v>1000</v>
@@ -11122,16 +11122,16 @@
         <v>20508</v>
       </c>
       <c r="S137" t="n">
-        <v>26660</v>
+        <v>26640</v>
       </c>
       <c r="T137" t="n">
-        <v>13371</v>
+        <v>13365</v>
       </c>
       <c r="U137" t="n">
-        <v>6685</v>
+        <v>6682</v>
       </c>
       <c r="V137" t="n">
-        <v>6604</v>
+        <v>6593</v>
       </c>
       <c r="W137" t="n">
         <v>14.8</v>
@@ -11179,16 +11179,16 @@
         <v>1429</v>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M138" t="n">
         <v>25470</v>
       </c>
       <c r="N138" t="n">
-        <v>83700</v>
+        <v>83720</v>
       </c>
       <c r="O138" t="n">
-        <v>26200</v>
+        <v>26180</v>
       </c>
       <c r="P138" t="n">
         <v>5275</v>
@@ -11200,16 +11200,16 @@
         <v>16996</v>
       </c>
       <c r="S138" t="n">
-        <v>8129</v>
+        <v>8109</v>
       </c>
       <c r="T138" t="n">
-        <v>7860</v>
+        <v>7854</v>
       </c>
       <c r="U138" t="n">
-        <v>3930</v>
+        <v>3927</v>
       </c>
       <c r="V138" t="n">
-        <v>-3661</v>
+        <v>-3672</v>
       </c>
       <c r="W138" t="n">
         <v>-14</v>
@@ -11291,16 +11291,16 @@
         <v>2367</v>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>87250</v>
+        <v>87270</v>
       </c>
       <c r="O140" t="n">
-        <v>94793</v>
+        <v>94773</v>
       </c>
       <c r="P140" t="n">
         <v>3666</v>
@@ -11312,16 +11312,16 @@
         <v>37395</v>
       </c>
       <c r="S140" t="n">
-        <v>56531</v>
+        <v>56511</v>
       </c>
       <c r="T140" t="n">
-        <v>28438</v>
+        <v>28432</v>
       </c>
       <c r="U140" t="n">
-        <v>14219</v>
+        <v>14216</v>
       </c>
       <c r="V140" t="n">
-        <v>13874</v>
+        <v>13863</v>
       </c>
       <c r="W140" t="n">
         <v>14.6</v>
@@ -11369,16 +11369,16 @@
         <v>2103</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>76527</v>
+        <v>76547</v>
       </c>
       <c r="O141" t="n">
-        <v>85264</v>
+        <v>85244</v>
       </c>
       <c r="P141" t="n">
         <v>1000</v>
@@ -11390,16 +11390,16 @@
         <v>16435</v>
       </c>
       <c r="S141" t="n">
-        <v>70329</v>
+        <v>70309</v>
       </c>
       <c r="T141" t="n">
-        <v>25579</v>
+        <v>25573</v>
       </c>
       <c r="U141" t="n">
-        <v>12790</v>
+        <v>12787</v>
       </c>
       <c r="V141" t="n">
-        <v>31960</v>
+        <v>31949</v>
       </c>
       <c r="W141" t="n">
         <v>37.5</v>
@@ -11451,16 +11451,16 @@
         <v>1585</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M142" t="n">
         <v>23350</v>
       </c>
       <c r="N142" t="n">
-        <v>81804</v>
+        <v>81824</v>
       </c>
       <c r="O142" t="n">
-        <v>40096</v>
+        <v>40076</v>
       </c>
       <c r="P142" t="n">
         <v>6539</v>
@@ -11472,16 +11472,16 @@
         <v>16933</v>
       </c>
       <c r="S142" t="n">
-        <v>21824</v>
+        <v>21804</v>
       </c>
       <c r="T142" t="n">
-        <v>12029</v>
+        <v>12023</v>
       </c>
       <c r="U142" t="n">
-        <v>6014</v>
+        <v>6011</v>
       </c>
       <c r="V142" t="n">
-        <v>3781</v>
+        <v>3770</v>
       </c>
       <c r="W142" t="n">
         <v>9.4</v>
@@ -11533,16 +11533,16 @@
         <v>1585</v>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M143" t="n">
         <v>14676</v>
       </c>
       <c r="N143" t="n">
-        <v>73189</v>
+        <v>73209</v>
       </c>
       <c r="O143" t="n">
-        <v>48711</v>
+        <v>48691</v>
       </c>
       <c r="P143" t="n">
         <v>5929</v>
@@ -11554,16 +11554,16 @@
         <v>16933</v>
       </c>
       <c r="S143" t="n">
-        <v>29749</v>
+        <v>29729</v>
       </c>
       <c r="T143" t="n">
-        <v>14613</v>
+        <v>14607</v>
       </c>
       <c r="U143" t="n">
-        <v>7307</v>
+        <v>7304</v>
       </c>
       <c r="V143" t="n">
-        <v>7829</v>
+        <v>7818</v>
       </c>
       <c r="W143" t="n">
         <v>16.1</v>
@@ -11615,16 +11615,16 @@
         <v>1585</v>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M144" t="n">
         <v>24001</v>
       </c>
       <c r="N144" t="n">
-        <v>82489</v>
+        <v>82509</v>
       </c>
       <c r="O144" t="n">
-        <v>39411</v>
+        <v>39391</v>
       </c>
       <c r="P144" t="n">
         <v>5398</v>
@@ -11636,16 +11636,16 @@
         <v>16933</v>
       </c>
       <c r="S144" t="n">
-        <v>21079</v>
+        <v>21059</v>
       </c>
       <c r="T144" t="n">
-        <v>11823</v>
+        <v>11817</v>
       </c>
       <c r="U144" t="n">
-        <v>5912</v>
+        <v>5909</v>
       </c>
       <c r="V144" t="n">
-        <v>3344</v>
+        <v>3333</v>
       </c>
       <c r="W144" t="n">
         <v>8.5</v>
@@ -11697,16 +11697,16 @@
         <v>1585</v>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M145" t="n">
         <v>17253</v>
       </c>
       <c r="N145" t="n">
-        <v>75705</v>
+        <v>75725</v>
       </c>
       <c r="O145" t="n">
-        <v>46195</v>
+        <v>46175</v>
       </c>
       <c r="P145" t="n">
         <v>6539</v>
@@ -11718,16 +11718,16 @@
         <v>16933</v>
       </c>
       <c r="S145" t="n">
-        <v>28272</v>
+        <v>28252</v>
       </c>
       <c r="T145" t="n">
-        <v>13858</v>
+        <v>13852</v>
       </c>
       <c r="U145" t="n">
-        <v>6929</v>
+        <v>6926</v>
       </c>
       <c r="V145" t="n">
-        <v>7484</v>
+        <v>7473</v>
       </c>
       <c r="W145" t="n">
         <v>16.2</v>
@@ -11779,16 +11779,16 @@
         <v>1585</v>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M146" t="n">
         <v>6095</v>
       </c>
       <c r="N146" t="n">
-        <v>70120</v>
+        <v>70140</v>
       </c>
       <c r="O146" t="n">
-        <v>51780</v>
+        <v>51760</v>
       </c>
       <c r="P146" t="n">
         <v>3099</v>
@@ -11800,16 +11800,16 @@
         <v>16933</v>
       </c>
       <c r="S146" t="n">
-        <v>34247</v>
+        <v>34227</v>
       </c>
       <c r="T146" t="n">
-        <v>15534</v>
+        <v>15528</v>
       </c>
       <c r="U146" t="n">
-        <v>7767</v>
+        <v>7764</v>
       </c>
       <c r="V146" t="n">
-        <v>10946</v>
+        <v>10935</v>
       </c>
       <c r="W146" t="n">
         <v>21.1</v>
@@ -11861,16 +11861,16 @@
         <v>1584</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M147" t="n">
         <v>10969</v>
       </c>
       <c r="N147" t="n">
-        <v>68889</v>
+        <v>68909</v>
       </c>
       <c r="O147" t="n">
-        <v>52991</v>
+        <v>52971</v>
       </c>
       <c r="P147" t="n">
         <v>3099</v>
@@ -11882,16 +11882,16 @@
         <v>16933</v>
       </c>
       <c r="S147" t="n">
-        <v>35259</v>
+        <v>35239</v>
       </c>
       <c r="T147" t="n">
-        <v>15897</v>
+        <v>15891</v>
       </c>
       <c r="U147" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="V147" t="n">
-        <v>11413</v>
+        <v>11402</v>
       </c>
       <c r="W147" t="n">
         <v>21.5</v>
@@ -11943,16 +11943,16 @@
         <v>1584</v>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M148" t="n">
         <v>17255</v>
       </c>
       <c r="N148" t="n">
-        <v>75699</v>
+        <v>75719</v>
       </c>
       <c r="O148" t="n">
-        <v>46181</v>
+        <v>46161</v>
       </c>
       <c r="P148" t="n">
         <v>3099</v>
@@ -11964,16 +11964,16 @@
         <v>16933</v>
       </c>
       <c r="S148" t="n">
-        <v>29048</v>
+        <v>29028</v>
       </c>
       <c r="T148" t="n">
-        <v>13854</v>
+        <v>13848</v>
       </c>
       <c r="U148" t="n">
-        <v>6927</v>
+        <v>6924</v>
       </c>
       <c r="V148" t="n">
-        <v>8267</v>
+        <v>8256</v>
       </c>
       <c r="W148" t="n">
         <v>17.9</v>
@@ -12025,16 +12025,16 @@
         <v>1584</v>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M149" t="n">
         <v>23349</v>
       </c>
       <c r="N149" t="n">
-        <v>81793</v>
+        <v>81813</v>
       </c>
       <c r="O149" t="n">
-        <v>40087</v>
+        <v>40067</v>
       </c>
       <c r="P149" t="n">
         <v>3099</v>
@@ -12046,19 +12046,19 @@
         <v>16933</v>
       </c>
       <c r="S149" t="n">
-        <v>22754</v>
+        <v>22734</v>
       </c>
       <c r="T149" t="n">
-        <v>12026</v>
+        <v>12020</v>
       </c>
       <c r="U149" t="n">
-        <v>6013</v>
+        <v>6010</v>
       </c>
       <c r="V149" t="n">
-        <v>4715</v>
+        <v>4704</v>
       </c>
       <c r="W149" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
@@ -12107,16 +12107,16 @@
         <v>1584</v>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M150" t="n">
         <v>8532</v>
       </c>
       <c r="N150" t="n">
-        <v>67368</v>
+        <v>67388</v>
       </c>
       <c r="O150" t="n">
-        <v>54512</v>
+        <v>54492</v>
       </c>
       <c r="P150" t="n">
         <v>9369</v>
@@ -12128,19 +12128,19 @@
         <v>16933</v>
       </c>
       <c r="S150" t="n">
-        <v>30610</v>
+        <v>30590</v>
       </c>
       <c r="T150" t="n">
-        <v>16354</v>
+        <v>16348</v>
       </c>
       <c r="U150" t="n">
-        <v>8177</v>
+        <v>8174</v>
       </c>
       <c r="V150" t="n">
-        <v>6080</v>
+        <v>6069</v>
       </c>
       <c r="W150" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
@@ -12189,16 +12189,16 @@
         <v>1576</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M151" t="n">
         <v>12206</v>
       </c>
       <c r="N151" t="n">
-        <v>70413</v>
+        <v>70433</v>
       </c>
       <c r="O151" t="n">
-        <v>50841</v>
+        <v>50821</v>
       </c>
       <c r="P151" t="n">
         <v>4575</v>
@@ -12210,16 +12210,16 @@
         <v>16933</v>
       </c>
       <c r="S151" t="n">
-        <v>33733</v>
+        <v>33713</v>
       </c>
       <c r="T151" t="n">
-        <v>15252</v>
+        <v>15246</v>
       </c>
       <c r="U151" t="n">
-        <v>7626</v>
+        <v>7623</v>
       </c>
       <c r="V151" t="n">
-        <v>10855</v>
+        <v>10844</v>
       </c>
       <c r="W151" t="n">
         <v>21.3</v>
@@ -12271,16 +12271,16 @@
         <v>1520</v>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M152" t="n">
         <v>17907</v>
       </c>
       <c r="N152" t="n">
-        <v>74029</v>
+        <v>74049</v>
       </c>
       <c r="O152" t="n">
-        <v>42871</v>
+        <v>42851</v>
       </c>
       <c r="P152" t="n">
         <v>4282</v>
@@ -12292,16 +12292,16 @@
         <v>16933</v>
       </c>
       <c r="S152" t="n">
-        <v>24256</v>
+        <v>24236</v>
       </c>
       <c r="T152" t="n">
-        <v>12861</v>
+        <v>12855</v>
       </c>
       <c r="U152" t="n">
-        <v>6431</v>
+        <v>6428</v>
       </c>
       <c r="V152" t="n">
-        <v>4964</v>
+        <v>4953</v>
       </c>
       <c r="W152" t="n">
         <v>11.6</v>
@@ -12353,16 +12353,16 @@
         <v>1520</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M153" t="n">
         <v>28428</v>
       </c>
       <c r="N153" t="n">
-        <v>84550</v>
+        <v>84570</v>
       </c>
       <c r="O153" t="n">
-        <v>32350</v>
+        <v>32330</v>
       </c>
       <c r="P153" t="n">
         <v>4282</v>
@@ -12374,19 +12374,19 @@
         <v>16933</v>
       </c>
       <c r="S153" t="n">
-        <v>14035</v>
+        <v>14015</v>
       </c>
       <c r="T153" t="n">
-        <v>9705</v>
+        <v>9699</v>
       </c>
       <c r="U153" t="n">
-        <v>4852</v>
+        <v>4850</v>
       </c>
       <c r="V153" t="n">
-        <v>-522</v>
+        <v>-534</v>
       </c>
       <c r="W153" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
@@ -12435,16 +12435,16 @@
         <v>1520</v>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M154" t="n">
         <v>26090</v>
       </c>
       <c r="N154" t="n">
-        <v>82212</v>
+        <v>82232</v>
       </c>
       <c r="O154" t="n">
-        <v>34688</v>
+        <v>34668</v>
       </c>
       <c r="P154" t="n">
         <v>7722</v>
@@ -12456,19 +12456,19 @@
         <v>16933</v>
       </c>
       <c r="S154" t="n">
-        <v>15283</v>
+        <v>15263</v>
       </c>
       <c r="T154" t="n">
-        <v>10406</v>
+        <v>10400</v>
       </c>
       <c r="U154" t="n">
-        <v>5203</v>
+        <v>5200</v>
       </c>
       <c r="V154" t="n">
-        <v>-327</v>
+        <v>-338</v>
       </c>
       <c r="W154" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
@@ -12517,16 +12517,16 @@
         <v>2672</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M155" t="n">
         <v>468</v>
       </c>
       <c r="N155" t="n">
-        <v>56775</v>
+        <v>56795</v>
       </c>
       <c r="O155" t="n">
-        <v>59401</v>
+        <v>59381</v>
       </c>
       <c r="P155" t="n">
         <v>23377</v>
@@ -12538,16 +12538,16 @@
         <v>17660</v>
       </c>
       <c r="S155" t="n">
-        <v>23663</v>
+        <v>23643</v>
       </c>
       <c r="T155" t="n">
-        <v>17820</v>
+        <v>17814</v>
       </c>
       <c r="U155" t="n">
-        <v>8910</v>
+        <v>8907</v>
       </c>
       <c r="V155" t="n">
-        <v>-3067</v>
+        <v>-3078</v>
       </c>
       <c r="W155" t="n">
         <v>-5.2</v>
@@ -12599,16 +12599,16 @@
         <v>6802</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M156" t="n">
         <v>23044</v>
       </c>
       <c r="N156" t="n">
-        <v>83903</v>
+        <v>83923</v>
       </c>
       <c r="O156" t="n">
-        <v>31883</v>
+        <v>31863</v>
       </c>
       <c r="P156" t="n">
         <v>5530</v>
@@ -12620,16 +12620,16 @@
         <v>16933</v>
       </c>
       <c r="S156" t="n">
-        <v>14920</v>
+        <v>14900</v>
       </c>
       <c r="T156" t="n">
-        <v>9565</v>
+        <v>9559</v>
       </c>
       <c r="U156" t="n">
-        <v>4782</v>
+        <v>4779</v>
       </c>
       <c r="V156" t="n">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="W156" t="n">
         <v>1.8</v>
@@ -12681,16 +12681,16 @@
         <v>1490</v>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M157" t="n">
         <v>11872</v>
       </c>
       <c r="N157" t="n">
-        <v>72654</v>
+        <v>72674</v>
       </c>
       <c r="O157" t="n">
-        <v>41932</v>
+        <v>41912</v>
       </c>
       <c r="P157" t="n">
         <v>1000</v>
@@ -12702,16 +12702,16 @@
         <v>16933</v>
       </c>
       <c r="S157" t="n">
-        <v>26299</v>
+        <v>26279</v>
       </c>
       <c r="T157" t="n">
-        <v>12580</v>
+        <v>12574</v>
       </c>
       <c r="U157" t="n">
-        <v>6290</v>
+        <v>6287</v>
       </c>
       <c r="V157" t="n">
-        <v>7430</v>
+        <v>7419</v>
       </c>
       <c r="W157" t="n">
         <v>17.7</v>
@@ -12841,16 +12841,16 @@
         <v>1444</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M159" t="n">
         <v>27902</v>
       </c>
       <c r="N159" t="n">
-        <v>81259</v>
+        <v>81279</v>
       </c>
       <c r="O159" t="n">
-        <v>29796</v>
+        <v>29776</v>
       </c>
       <c r="P159" t="n">
         <v>6374</v>
@@ -12862,16 +12862,16 @@
         <v>16933</v>
       </c>
       <c r="S159" t="n">
-        <v>11388</v>
+        <v>11368</v>
       </c>
       <c r="T159" t="n">
-        <v>8939</v>
+        <v>8933</v>
       </c>
       <c r="U159" t="n">
-        <v>4469</v>
+        <v>4466</v>
       </c>
       <c r="V159" t="n">
-        <v>-2020</v>
+        <v>-2031</v>
       </c>
       <c r="W159" t="n">
         <v>-6.8</v>
@@ -12997,16 +12997,16 @@
         <v>1415</v>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M161" t="n">
         <v>6143</v>
       </c>
       <c r="N161" t="n">
-        <v>63929</v>
+        <v>63949</v>
       </c>
       <c r="O161" t="n">
-        <v>44928</v>
+        <v>44908</v>
       </c>
       <c r="P161" t="n">
         <v>1000</v>
@@ -13018,16 +13018,16 @@
         <v>16933</v>
       </c>
       <c r="S161" t="n">
-        <v>29495</v>
+        <v>29475</v>
       </c>
       <c r="T161" t="n">
-        <v>13478</v>
+        <v>13472</v>
       </c>
       <c r="U161" t="n">
-        <v>6739</v>
+        <v>6736</v>
       </c>
       <c r="V161" t="n">
-        <v>9277</v>
+        <v>9266</v>
       </c>
       <c r="W161" t="n">
         <v>20.6</v>
@@ -13079,16 +13079,16 @@
         <v>1415</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M162" t="n">
         <v>11586</v>
       </c>
       <c r="N162" t="n">
-        <v>69372</v>
+        <v>69392</v>
       </c>
       <c r="O162" t="n">
-        <v>39485</v>
+        <v>39465</v>
       </c>
       <c r="P162" t="n">
         <v>1000</v>
@@ -13100,19 +13100,19 @@
         <v>16933</v>
       </c>
       <c r="S162" t="n">
-        <v>24151</v>
+        <v>24131</v>
       </c>
       <c r="T162" t="n">
-        <v>11846</v>
+        <v>11840</v>
       </c>
       <c r="U162" t="n">
-        <v>5923</v>
+        <v>5920</v>
       </c>
       <c r="V162" t="n">
-        <v>6383</v>
+        <v>6372</v>
       </c>
       <c r="W162" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="X162" t="inlineStr">
         <is>
@@ -13161,16 +13161,16 @@
         <v>1406</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M163" t="n">
         <v>11548</v>
       </c>
       <c r="N163" t="n">
-        <v>68978</v>
+        <v>68998</v>
       </c>
       <c r="O163" t="n">
-        <v>39196</v>
+        <v>39176</v>
       </c>
       <c r="P163" t="n">
         <v>3041</v>
@@ -13182,16 +13182,16 @@
         <v>16933</v>
       </c>
       <c r="S163" t="n">
-        <v>23721</v>
+        <v>23701</v>
       </c>
       <c r="T163" t="n">
-        <v>11759</v>
+        <v>11753</v>
       </c>
       <c r="U163" t="n">
-        <v>5879</v>
+        <v>5876</v>
       </c>
       <c r="V163" t="n">
-        <v>6083</v>
+        <v>6072</v>
       </c>
       <c r="W163" t="n">
         <v>15.5</v>
@@ -13243,16 +13243,16 @@
         <v>1401</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>50977</v>
+        <v>50997</v>
       </c>
       <c r="O164" t="n">
-        <v>56796</v>
+        <v>56776</v>
       </c>
       <c r="P164" t="n">
         <v>1000</v>
@@ -13264,16 +13264,16 @@
         <v>17660</v>
       </c>
       <c r="S164" t="n">
-        <v>40436</v>
+        <v>40416</v>
       </c>
       <c r="T164" t="n">
-        <v>17039</v>
+        <v>17033</v>
       </c>
       <c r="U164" t="n">
-        <v>8519</v>
+        <v>8516</v>
       </c>
       <c r="V164" t="n">
-        <v>14878</v>
+        <v>14867</v>
       </c>
       <c r="W164" t="n">
         <v>26.2</v>
@@ -13325,16 +13325,16 @@
         <v>1401</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M165" t="n">
         <v>5389</v>
       </c>
       <c r="N165" t="n">
-        <v>57374</v>
+        <v>57394</v>
       </c>
       <c r="O165" t="n">
-        <v>50399</v>
+        <v>50379</v>
       </c>
       <c r="P165" t="n">
         <v>3099</v>
@@ -13346,16 +13346,16 @@
         <v>17660</v>
       </c>
       <c r="S165" t="n">
-        <v>32240</v>
+        <v>32220</v>
       </c>
       <c r="T165" t="n">
-        <v>15120</v>
+        <v>15114</v>
       </c>
       <c r="U165" t="n">
-        <v>7560</v>
+        <v>7557</v>
       </c>
       <c r="V165" t="n">
-        <v>9560</v>
+        <v>9549</v>
       </c>
       <c r="W165" t="n">
         <v>19</v>
@@ -13407,16 +13407,16 @@
         <v>1401</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>57338</v>
+        <v>57358</v>
       </c>
       <c r="O166" t="n">
-        <v>50435</v>
+        <v>50415</v>
       </c>
       <c r="P166" t="n">
         <v>4136</v>
@@ -13428,16 +13428,16 @@
         <v>17660</v>
       </c>
       <c r="S166" t="n">
-        <v>32939</v>
+        <v>32919</v>
       </c>
       <c r="T166" t="n">
-        <v>15130</v>
+        <v>15124</v>
       </c>
       <c r="U166" t="n">
-        <v>7565</v>
+        <v>7562</v>
       </c>
       <c r="V166" t="n">
-        <v>10243</v>
+        <v>10232</v>
       </c>
       <c r="W166" t="n">
         <v>20.3</v>
@@ -13489,16 +13489,16 @@
         <v>1377</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M167" t="n">
         <v>554</v>
       </c>
       <c r="N167" t="n">
-        <v>51536</v>
+        <v>51556</v>
       </c>
       <c r="O167" t="n">
-        <v>54364</v>
+        <v>54344</v>
       </c>
       <c r="P167" t="n">
         <v>3154</v>
@@ -13510,19 +13510,19 @@
         <v>17189</v>
       </c>
       <c r="S167" t="n">
-        <v>36620</v>
+        <v>36600</v>
       </c>
       <c r="T167" t="n">
-        <v>16309</v>
+        <v>16303</v>
       </c>
       <c r="U167" t="n">
-        <v>8155</v>
+        <v>8152</v>
       </c>
       <c r="V167" t="n">
-        <v>12156</v>
+        <v>12145</v>
       </c>
       <c r="W167" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="X167" t="inlineStr">
         <is>
@@ -13571,16 +13571,16 @@
         <v>1377</v>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M168" t="n">
         <v>6265</v>
       </c>
       <c r="N168" t="n">
-        <v>57244</v>
+        <v>57264</v>
       </c>
       <c r="O168" t="n">
-        <v>48656</v>
+        <v>48636</v>
       </c>
       <c r="P168" t="n">
         <v>3813</v>
@@ -13592,19 +13592,19 @@
         <v>17660</v>
       </c>
       <c r="S168" t="n">
-        <v>30583</v>
+        <v>30563</v>
       </c>
       <c r="T168" t="n">
-        <v>14597</v>
+        <v>14591</v>
       </c>
       <c r="U168" t="n">
-        <v>7298</v>
+        <v>7295</v>
       </c>
       <c r="V168" t="n">
-        <v>8688</v>
+        <v>8677</v>
       </c>
       <c r="W168" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="X168" t="inlineStr">
         <is>
@@ -13653,16 +13653,16 @@
         <v>1377</v>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>12058</v>
       </c>
       <c r="M169" t="n">
         <v>6266</v>
       </c>
       <c r="N169" t="n">
-        <v>57245</v>
+        <v>69303</v>
       </c>
       <c r="O169" t="n">
-        <v>48655</v>
+        <v>36597</v>
       </c>
       <c r="P169" t="n">
         <v>0</v>
@@ -13674,19 +13674,19 @@
         <v>17660</v>
       </c>
       <c r="S169" t="n">
-        <v>40933</v>
+        <v>28875</v>
       </c>
       <c r="T169" t="n">
-        <v>14596</v>
+        <v>10979</v>
       </c>
       <c r="U169" t="n">
-        <v>7298</v>
+        <v>5490</v>
       </c>
       <c r="V169" t="n">
-        <v>19038</v>
+        <v>12406</v>
       </c>
       <c r="W169" t="n">
-        <v>39.1</v>
+        <v>33.9</v>
       </c>
       <c r="X169" t="inlineStr">
         <is>
@@ -13735,16 +13735,16 @@
         <v>1377</v>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M170" t="n">
         <v>29625</v>
       </c>
       <c r="N170" t="n">
-        <v>80706</v>
+        <v>80726</v>
       </c>
       <c r="O170" t="n">
-        <v>25194</v>
+        <v>25174</v>
       </c>
       <c r="P170" t="n">
         <v>3099</v>
@@ -13756,19 +13756,19 @@
         <v>17189</v>
       </c>
       <c r="S170" t="n">
-        <v>7906</v>
+        <v>7886</v>
       </c>
       <c r="T170" t="n">
-        <v>7558</v>
+        <v>7552</v>
       </c>
       <c r="U170" t="n">
-        <v>3779</v>
+        <v>3776</v>
       </c>
       <c r="V170" t="n">
-        <v>-3431</v>
+        <v>-3442</v>
       </c>
       <c r="W170" t="n">
-        <v>-13.6</v>
+        <v>-13.7</v>
       </c>
       <c r="X170" t="inlineStr">
         <is>
@@ -13817,16 +13817,16 @@
         <v>6093</v>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M171" t="n">
         <v>553</v>
       </c>
       <c r="N171" t="n">
-        <v>61546</v>
+        <v>61566</v>
       </c>
       <c r="O171" t="n">
-        <v>44354</v>
+        <v>44334</v>
       </c>
       <c r="P171" t="n">
         <v>3099</v>
@@ -13838,16 +13838,16 @@
         <v>17189</v>
       </c>
       <c r="S171" t="n">
-        <v>26565</v>
+        <v>26545</v>
       </c>
       <c r="T171" t="n">
-        <v>13306</v>
+        <v>13300</v>
       </c>
       <c r="U171" t="n">
-        <v>6653</v>
+        <v>6650</v>
       </c>
       <c r="V171" t="n">
-        <v>6606</v>
+        <v>6595</v>
       </c>
       <c r="W171" t="n">
         <v>14.9</v>
@@ -13899,16 +13899,16 @@
         <v>1349</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M172" t="n">
         <v>7265</v>
       </c>
       <c r="N172" t="n">
-        <v>57002</v>
+        <v>57022</v>
       </c>
       <c r="O172" t="n">
-        <v>46779</v>
+        <v>46759</v>
       </c>
       <c r="P172" t="n">
         <v>6009</v>
@@ -13920,16 +13920,16 @@
         <v>17189</v>
       </c>
       <c r="S172" t="n">
-        <v>29930</v>
+        <v>29910</v>
       </c>
       <c r="T172" t="n">
-        <v>14034</v>
+        <v>14028</v>
       </c>
       <c r="U172" t="n">
-        <v>7017</v>
+        <v>7014</v>
       </c>
       <c r="V172" t="n">
-        <v>8879</v>
+        <v>8868</v>
       </c>
       <c r="W172" t="n">
         <v>19</v>
@@ -13981,16 +13981,16 @@
         <v>1344</v>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M173" t="n">
         <v>11314</v>
       </c>
       <c r="N173" t="n">
-        <v>66255</v>
+        <v>66275</v>
       </c>
       <c r="O173" t="n">
-        <v>37161</v>
+        <v>37141</v>
       </c>
       <c r="P173" t="n">
         <v>0</v>
@@ -14002,16 +14002,16 @@
         <v>16933</v>
       </c>
       <c r="S173" t="n">
-        <v>24528</v>
+        <v>24508</v>
       </c>
       <c r="T173" t="n">
-        <v>11148</v>
+        <v>11142</v>
       </c>
       <c r="U173" t="n">
-        <v>5574</v>
+        <v>5571</v>
       </c>
       <c r="V173" t="n">
-        <v>7806</v>
+        <v>7795</v>
       </c>
       <c r="W173" t="n">
         <v>21</v>
@@ -14063,16 +14063,16 @@
         <v>2367</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M174" t="n">
         <v>20110</v>
       </c>
       <c r="N174" t="n">
-        <v>70276</v>
+        <v>70296</v>
       </c>
       <c r="O174" t="n">
-        <v>32624</v>
+        <v>32604</v>
       </c>
       <c r="P174" t="n">
         <v>3477</v>
@@ -14084,16 +14084,16 @@
         <v>14537</v>
       </c>
       <c r="S174" t="n">
-        <v>17910</v>
+        <v>17890</v>
       </c>
       <c r="T174" t="n">
-        <v>9787</v>
+        <v>9781</v>
       </c>
       <c r="U174" t="n">
-        <v>4894</v>
+        <v>4891</v>
       </c>
       <c r="V174" t="n">
-        <v>3229</v>
+        <v>3218</v>
       </c>
       <c r="W174" t="n">
         <v>9.9</v>
@@ -14145,16 +14145,16 @@
         <v>1338</v>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M175" t="n">
         <v>12907</v>
       </c>
       <c r="N175" t="n">
-        <v>62044</v>
+        <v>62064</v>
       </c>
       <c r="O175" t="n">
-        <v>40856</v>
+        <v>40836</v>
       </c>
       <c r="P175" t="n">
         <v>5117</v>
@@ -14166,16 +14166,16 @@
         <v>14537</v>
       </c>
       <c r="S175" t="n">
-        <v>26352</v>
+        <v>26332</v>
       </c>
       <c r="T175" t="n">
-        <v>12257</v>
+        <v>12251</v>
       </c>
       <c r="U175" t="n">
-        <v>6128</v>
+        <v>6125</v>
       </c>
       <c r="V175" t="n">
-        <v>7967</v>
+        <v>7956</v>
       </c>
       <c r="W175" t="n">
         <v>19.5</v>
@@ -14227,16 +14227,16 @@
         <v>1337</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M176" t="n">
         <v>12907</v>
       </c>
       <c r="N176" t="n">
-        <v>62034</v>
+        <v>62054</v>
       </c>
       <c r="O176" t="n">
-        <v>40846</v>
+        <v>40826</v>
       </c>
       <c r="P176" t="n">
         <v>5354</v>
@@ -14248,16 +14248,16 @@
         <v>14537</v>
       </c>
       <c r="S176" t="n">
-        <v>26254</v>
+        <v>26234</v>
       </c>
       <c r="T176" t="n">
-        <v>12254</v>
+        <v>12248</v>
       </c>
       <c r="U176" t="n">
-        <v>6127</v>
+        <v>6124</v>
       </c>
       <c r="V176" t="n">
-        <v>7873</v>
+        <v>7862</v>
       </c>
       <c r="W176" t="n">
         <v>19.3</v>
@@ -14309,16 +14309,16 @@
         <v>1337</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M177" t="n">
         <v>12907</v>
       </c>
       <c r="N177" t="n">
-        <v>62034</v>
+        <v>62054</v>
       </c>
       <c r="O177" t="n">
-        <v>40846</v>
+        <v>40826</v>
       </c>
       <c r="P177" t="n">
         <v>3652</v>
@@ -14330,16 +14330,16 @@
         <v>14537</v>
       </c>
       <c r="S177" t="n">
-        <v>25057</v>
+        <v>25037</v>
       </c>
       <c r="T177" t="n">
-        <v>12254</v>
+        <v>12248</v>
       </c>
       <c r="U177" t="n">
-        <v>6127</v>
+        <v>6124</v>
       </c>
       <c r="V177" t="n">
-        <v>6676</v>
+        <v>6665</v>
       </c>
       <c r="W177" t="n">
         <v>16.3</v>
@@ -14391,16 +14391,16 @@
         <v>2350</v>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M178" t="n">
         <v>12907</v>
       </c>
       <c r="N178" t="n">
-        <v>62723</v>
+        <v>62743</v>
       </c>
       <c r="O178" t="n">
-        <v>39453</v>
+        <v>39433</v>
       </c>
       <c r="P178" t="n">
         <v>4430</v>
@@ -14412,16 +14412,16 @@
         <v>14537</v>
       </c>
       <c r="S178" t="n">
-        <v>24686</v>
+        <v>24666</v>
       </c>
       <c r="T178" t="n">
-        <v>11836</v>
+        <v>11830</v>
       </c>
       <c r="U178" t="n">
-        <v>5918</v>
+        <v>5915</v>
       </c>
       <c r="V178" t="n">
-        <v>6932</v>
+        <v>6921</v>
       </c>
       <c r="W178" t="n">
         <v>17.6</v>
@@ -14551,16 +14551,16 @@
         <v>1305</v>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M180" t="n">
         <v>7027</v>
       </c>
       <c r="N180" t="n">
-        <v>55441</v>
+        <v>55461</v>
       </c>
       <c r="O180" t="n">
-        <v>44945</v>
+        <v>44925</v>
       </c>
       <c r="P180" t="n">
         <v>5929</v>
@@ -14572,16 +14572,16 @@
         <v>20103</v>
       </c>
       <c r="S180" t="n">
-        <v>23112</v>
+        <v>23092</v>
       </c>
       <c r="T180" t="n">
-        <v>13484</v>
+        <v>13478</v>
       </c>
       <c r="U180" t="n">
-        <v>6742</v>
+        <v>6739</v>
       </c>
       <c r="V180" t="n">
-        <v>2887</v>
+        <v>2876</v>
       </c>
       <c r="W180" t="n">
         <v>6.4</v>
@@ -14633,16 +14633,16 @@
         <v>1260</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>46760</v>
+        <v>46780</v>
       </c>
       <c r="O181" t="n">
-        <v>50140</v>
+        <v>50120</v>
       </c>
       <c r="P181" t="n">
         <v>3099</v>
@@ -14654,16 +14654,16 @@
         <v>14537</v>
       </c>
       <c r="S181" t="n">
-        <v>35103</v>
+        <v>35083</v>
       </c>
       <c r="T181" t="n">
-        <v>15042</v>
+        <v>15036</v>
       </c>
       <c r="U181" t="n">
-        <v>7521</v>
+        <v>7518</v>
       </c>
       <c r="V181" t="n">
-        <v>12540</v>
+        <v>12529</v>
       </c>
       <c r="W181" t="n">
         <v>25</v>
@@ -14715,16 +14715,16 @@
         <v>1238</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M182" t="n">
         <v>12907</v>
       </c>
       <c r="N182" t="n">
-        <v>63172</v>
+        <v>63192</v>
       </c>
       <c r="O182" t="n">
-        <v>32051</v>
+        <v>32031</v>
       </c>
       <c r="P182" t="n">
         <v>5451</v>
@@ -14736,16 +14736,16 @@
         <v>14537</v>
       </c>
       <c r="S182" t="n">
-        <v>15963</v>
+        <v>15943</v>
       </c>
       <c r="T182" t="n">
-        <v>9615</v>
+        <v>9609</v>
       </c>
       <c r="U182" t="n">
-        <v>4808</v>
+        <v>4805</v>
       </c>
       <c r="V182" t="n">
-        <v>1540</v>
+        <v>1529</v>
       </c>
       <c r="W182" t="n">
         <v>4.8</v>
@@ -14797,16 +14797,16 @@
         <v>2137</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M183" t="n">
         <v>7448</v>
       </c>
       <c r="N183" t="n">
-        <v>53219</v>
+        <v>53239</v>
       </c>
       <c r="O183" t="n">
-        <v>39681</v>
+        <v>39661</v>
       </c>
       <c r="P183" t="n">
         <v>5137</v>
@@ -14818,16 +14818,16 @@
         <v>17660</v>
       </c>
       <c r="S183" t="n">
-        <v>22134</v>
+        <v>22114</v>
       </c>
       <c r="T183" t="n">
-        <v>11904</v>
+        <v>11898</v>
       </c>
       <c r="U183" t="n">
-        <v>5952</v>
+        <v>5949</v>
       </c>
       <c r="V183" t="n">
-        <v>4278</v>
+        <v>4267</v>
       </c>
       <c r="W183" t="n">
         <v>10.8</v>
@@ -14879,16 +14879,16 @@
         <v>2137</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M184" t="n">
         <v>27597</v>
       </c>
       <c r="N184" t="n">
-        <v>73166</v>
+        <v>73186</v>
       </c>
       <c r="O184" t="n">
-        <v>19734</v>
+        <v>19714</v>
       </c>
       <c r="P184" t="n">
         <v>3559</v>
@@ -14900,19 +14900,19 @@
         <v>17660</v>
       </c>
       <c r="S184" t="n">
-        <v>914</v>
+        <v>894</v>
       </c>
       <c r="T184" t="n">
-        <v>5920</v>
+        <v>5914</v>
       </c>
       <c r="U184" t="n">
-        <v>2960</v>
+        <v>2957</v>
       </c>
       <c r="V184" t="n">
-        <v>-7966</v>
+        <v>-7977</v>
       </c>
       <c r="W184" t="n">
-        <v>-40.4</v>
+        <v>-40.5</v>
       </c>
       <c r="X184" t="inlineStr">
         <is>
@@ -14961,16 +14961,16 @@
         <v>1208</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M185" t="n">
         <v>7473</v>
       </c>
       <c r="N185" t="n">
-        <v>52303</v>
+        <v>52323</v>
       </c>
       <c r="O185" t="n">
-        <v>40597</v>
+        <v>40577</v>
       </c>
       <c r="P185" t="n">
         <v>3932</v>
@@ -14982,16 +14982,16 @@
         <v>17660</v>
       </c>
       <c r="S185" t="n">
-        <v>23305</v>
+        <v>23285</v>
       </c>
       <c r="T185" t="n">
-        <v>12179</v>
+        <v>12173</v>
       </c>
       <c r="U185" t="n">
-        <v>6090</v>
+        <v>6087</v>
       </c>
       <c r="V185" t="n">
-        <v>5036</v>
+        <v>5025</v>
       </c>
       <c r="W185" t="n">
         <v>12.4</v>
@@ -15043,16 +15043,16 @@
         <v>1208</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M186" t="n">
         <v>8361</v>
       </c>
       <c r="N186" t="n">
-        <v>53277</v>
+        <v>53297</v>
       </c>
       <c r="O186" t="n">
-        <v>39623</v>
+        <v>39603</v>
       </c>
       <c r="P186" t="n">
         <v>3139</v>
@@ -15064,16 +15064,16 @@
         <v>17660</v>
       </c>
       <c r="S186" t="n">
-        <v>22323</v>
+        <v>22303</v>
       </c>
       <c r="T186" t="n">
-        <v>11887</v>
+        <v>11881</v>
       </c>
       <c r="U186" t="n">
-        <v>5943</v>
+        <v>5940</v>
       </c>
       <c r="V186" t="n">
-        <v>4493</v>
+        <v>4482</v>
       </c>
       <c r="W186" t="n">
         <v>11.3</v>
@@ -15125,16 +15125,16 @@
         <v>5454</v>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M187" t="n">
         <v>27597</v>
       </c>
       <c r="N187" t="n">
-        <v>76483</v>
+        <v>76503</v>
       </c>
       <c r="O187" t="n">
-        <v>16417</v>
+        <v>16397</v>
       </c>
       <c r="P187" t="n">
         <v>3559</v>
@@ -15146,19 +15146,19 @@
         <v>17660</v>
       </c>
       <c r="S187" t="n">
-        <v>-1702</v>
+        <v>-1722</v>
       </c>
       <c r="T187" t="n">
-        <v>4925</v>
+        <v>4919</v>
       </c>
       <c r="U187" t="n">
-        <v>2463</v>
+        <v>2460</v>
       </c>
       <c r="V187" t="n">
-        <v>-9090</v>
+        <v>-9101</v>
       </c>
       <c r="W187" t="n">
-        <v>-55.4</v>
+        <v>-55.5</v>
       </c>
       <c r="X187" t="inlineStr">
         <is>
@@ -15207,16 +15207,16 @@
         <v>1208</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M188" t="n">
         <v>8361</v>
       </c>
       <c r="N188" t="n">
-        <v>53277</v>
+        <v>53297</v>
       </c>
       <c r="O188" t="n">
-        <v>39623</v>
+        <v>39603</v>
       </c>
       <c r="P188" t="n">
         <v>2948</v>
@@ -15228,19 +15228,19 @@
         <v>17660</v>
       </c>
       <c r="S188" t="n">
-        <v>22414</v>
+        <v>22394</v>
       </c>
       <c r="T188" t="n">
-        <v>11887</v>
+        <v>11881</v>
       </c>
       <c r="U188" t="n">
-        <v>5943</v>
+        <v>5940</v>
       </c>
       <c r="V188" t="n">
-        <v>4584</v>
+        <v>4573</v>
       </c>
       <c r="W188" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="X188" t="inlineStr">
         <is>
@@ -15289,16 +15289,16 @@
         <v>1208</v>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M189" t="n">
         <v>7448</v>
       </c>
       <c r="N189" t="n">
-        <v>52290</v>
+        <v>52310</v>
       </c>
       <c r="O189" t="n">
-        <v>40610</v>
+        <v>40590</v>
       </c>
       <c r="P189" t="n">
         <v>7335</v>
@@ -15310,16 +15310,16 @@
         <v>17660</v>
       </c>
       <c r="S189" t="n">
-        <v>20665</v>
+        <v>20645</v>
       </c>
       <c r="T189" t="n">
-        <v>12183</v>
+        <v>12177</v>
       </c>
       <c r="U189" t="n">
-        <v>6092</v>
+        <v>6088</v>
       </c>
       <c r="V189" t="n">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="W189" t="n">
         <v>5.9</v>
@@ -15371,16 +15371,16 @@
         <v>1208</v>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M190" t="n">
         <v>7449</v>
       </c>
       <c r="N190" t="n">
-        <v>52292</v>
+        <v>52312</v>
       </c>
       <c r="O190" t="n">
-        <v>40608</v>
+        <v>40588</v>
       </c>
       <c r="P190" t="n">
         <v>6538</v>
@@ -15392,16 +15392,16 @@
         <v>17660</v>
       </c>
       <c r="S190" t="n">
-        <v>19610</v>
+        <v>19590</v>
       </c>
       <c r="T190" t="n">
-        <v>12182</v>
+        <v>12176</v>
       </c>
       <c r="U190" t="n">
-        <v>6091</v>
+        <v>6088</v>
       </c>
       <c r="V190" t="n">
-        <v>1336</v>
+        <v>1325</v>
       </c>
       <c r="W190" t="n">
         <v>3.3</v>
@@ -15453,16 +15453,16 @@
         <v>1208</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M191" t="n">
         <v>27597</v>
       </c>
       <c r="N191" t="n">
-        <v>72237</v>
+        <v>72257</v>
       </c>
       <c r="O191" t="n">
-        <v>20663</v>
+        <v>20643</v>
       </c>
       <c r="P191" t="n">
         <v>3559</v>
@@ -15474,19 +15474,19 @@
         <v>17660</v>
       </c>
       <c r="S191" t="n">
-        <v>2143</v>
+        <v>2123</v>
       </c>
       <c r="T191" t="n">
-        <v>6199</v>
+        <v>6193</v>
       </c>
       <c r="U191" t="n">
-        <v>3099</v>
+        <v>3096</v>
       </c>
       <c r="V191" t="n">
-        <v>-7155</v>
+        <v>-7166</v>
       </c>
       <c r="W191" t="n">
-        <v>-34.6</v>
+        <v>-34.7</v>
       </c>
       <c r="X191" t="inlineStr">
         <is>
@@ -15535,16 +15535,16 @@
         <v>1208</v>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M192" t="n">
         <v>27597</v>
       </c>
       <c r="N192" t="n">
-        <v>72237</v>
+        <v>72257</v>
       </c>
       <c r="O192" t="n">
-        <v>20663</v>
+        <v>20643</v>
       </c>
       <c r="P192" t="n">
         <v>611</v>
@@ -15556,19 +15556,19 @@
         <v>17660</v>
       </c>
       <c r="S192" t="n">
-        <v>7391</v>
+        <v>7371</v>
       </c>
       <c r="T192" t="n">
-        <v>6199</v>
+        <v>6193</v>
       </c>
       <c r="U192" t="n">
-        <v>3099</v>
+        <v>3096</v>
       </c>
       <c r="V192" t="n">
-        <v>-1907</v>
+        <v>-1918</v>
       </c>
       <c r="W192" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="X192" t="inlineStr">
         <is>
@@ -15617,16 +15617,16 @@
         <v>1208</v>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M193" t="n">
         <v>8361</v>
       </c>
       <c r="N193" t="n">
-        <v>52303</v>
+        <v>52323</v>
       </c>
       <c r="O193" t="n">
-        <v>40597</v>
+        <v>40577</v>
       </c>
       <c r="P193" t="n">
         <v>0</v>
@@ -15638,16 +15638,16 @@
         <v>17660</v>
       </c>
       <c r="S193" t="n">
-        <v>29587</v>
+        <v>29567</v>
       </c>
       <c r="T193" t="n">
-        <v>12179</v>
+        <v>12173</v>
       </c>
       <c r="U193" t="n">
-        <v>6090</v>
+        <v>6087</v>
       </c>
       <c r="V193" t="n">
-        <v>11318</v>
+        <v>11307</v>
       </c>
       <c r="W193" t="n">
         <v>27.9</v>
@@ -15699,16 +15699,16 @@
         <v>1208</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M194" t="n">
         <v>23882</v>
       </c>
       <c r="N194" t="n">
-        <v>68522</v>
+        <v>68542</v>
       </c>
       <c r="O194" t="n">
-        <v>24378</v>
+        <v>24358</v>
       </c>
       <c r="P194" t="n">
         <v>611</v>
@@ -15720,19 +15720,19 @@
         <v>17660</v>
       </c>
       <c r="S194" t="n">
-        <v>11157</v>
+        <v>11137</v>
       </c>
       <c r="T194" t="n">
-        <v>7313</v>
+        <v>7307</v>
       </c>
       <c r="U194" t="n">
-        <v>3657</v>
+        <v>3654</v>
       </c>
       <c r="V194" t="n">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="W194" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="X194" t="inlineStr">
         <is>
@@ -15781,16 +15781,16 @@
         <v>1208</v>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>49537</v>
+        <v>49557</v>
       </c>
       <c r="O195" t="n">
-        <v>43363</v>
+        <v>43343</v>
       </c>
       <c r="P195" t="n">
         <v>0</v>
@@ -15802,16 +15802,16 @@
         <v>13664</v>
       </c>
       <c r="S195" t="n">
-        <v>32999</v>
+        <v>32979</v>
       </c>
       <c r="T195" t="n">
-        <v>13009</v>
+        <v>13003</v>
       </c>
       <c r="U195" t="n">
-        <v>6504</v>
+        <v>6501</v>
       </c>
       <c r="V195" t="n">
-        <v>13486</v>
+        <v>13475</v>
       </c>
       <c r="W195" t="n">
         <v>31.1</v>
@@ -15863,16 +15863,16 @@
         <v>1207</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M196" t="n">
         <v>4644</v>
       </c>
       <c r="N196" t="n">
-        <v>49162</v>
+        <v>49182</v>
       </c>
       <c r="O196" t="n">
-        <v>43718</v>
+        <v>43698</v>
       </c>
       <c r="P196" t="n">
         <v>0</v>
@@ -15884,19 +15884,19 @@
         <v>17660</v>
       </c>
       <c r="S196" t="n">
-        <v>28358</v>
+        <v>28338</v>
       </c>
       <c r="T196" t="n">
-        <v>13115</v>
+        <v>13109</v>
       </c>
       <c r="U196" t="n">
-        <v>6558</v>
+        <v>6555</v>
       </c>
       <c r="V196" t="n">
-        <v>8685</v>
+        <v>8674</v>
       </c>
       <c r="W196" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="X196" t="inlineStr"/>
     </row>
@@ -15941,16 +15941,16 @@
         <v>7256</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M197" t="n">
         <v>945</v>
       </c>
       <c r="N197" t="n">
-        <v>51587</v>
+        <v>51607</v>
       </c>
       <c r="O197" t="n">
-        <v>40773</v>
+        <v>40753</v>
       </c>
       <c r="P197" t="n">
         <v>4720</v>
@@ -15962,16 +15962,16 @@
         <v>17660</v>
       </c>
       <c r="S197" t="n">
-        <v>23243</v>
+        <v>23223</v>
       </c>
       <c r="T197" t="n">
-        <v>12232</v>
+        <v>12226</v>
       </c>
       <c r="U197" t="n">
-        <v>6116</v>
+        <v>6113</v>
       </c>
       <c r="V197" t="n">
-        <v>4895</v>
+        <v>4884</v>
       </c>
       <c r="W197" t="n">
         <v>12</v>
@@ -16023,16 +16023,16 @@
         <v>1199</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M198" t="n">
         <v>25694</v>
       </c>
       <c r="N198" t="n">
-        <v>70029</v>
+        <v>70049</v>
       </c>
       <c r="O198" t="n">
-        <v>22227</v>
+        <v>22207</v>
       </c>
       <c r="P198" t="n">
         <v>9546</v>
@@ -16044,19 +16044,19 @@
         <v>17660</v>
       </c>
       <c r="S198" t="n">
-        <v>1021</v>
+        <v>1001</v>
       </c>
       <c r="T198" t="n">
-        <v>6668</v>
+        <v>6662</v>
       </c>
       <c r="U198" t="n">
-        <v>3334</v>
+        <v>3331</v>
       </c>
       <c r="V198" t="n">
-        <v>-8981</v>
+        <v>-8992</v>
       </c>
       <c r="W198" t="n">
-        <v>-40.4</v>
+        <v>-40.5</v>
       </c>
       <c r="X198" t="inlineStr">
         <is>
@@ -16105,16 +16105,16 @@
         <v>1195</v>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M199" t="n">
         <v>23038</v>
       </c>
       <c r="N199" t="n">
-        <v>66668</v>
+        <v>66688</v>
       </c>
       <c r="O199" t="n">
-        <v>25232</v>
+        <v>25212</v>
       </c>
       <c r="P199" t="n">
         <v>2500</v>
@@ -16126,19 +16126,19 @@
         <v>11759</v>
       </c>
       <c r="S199" t="n">
-        <v>14073</v>
+        <v>14053</v>
       </c>
       <c r="T199" t="n">
-        <v>7570</v>
+        <v>7564</v>
       </c>
       <c r="U199" t="n">
-        <v>3785</v>
+        <v>3782</v>
       </c>
       <c r="V199" t="n">
-        <v>2719</v>
+        <v>2708</v>
       </c>
       <c r="W199" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="X199" t="inlineStr"/>
     </row>
@@ -16183,16 +16183,16 @@
         <v>1195</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M200" t="n">
         <v>13590</v>
       </c>
       <c r="N200" t="n">
-        <v>57424</v>
+        <v>57444</v>
       </c>
       <c r="O200" t="n">
-        <v>34476</v>
+        <v>34456</v>
       </c>
       <c r="P200" t="n">
         <v>1000</v>
@@ -16204,16 +16204,16 @@
         <v>11759</v>
       </c>
       <c r="S200" t="n">
-        <v>24416</v>
+        <v>24396</v>
       </c>
       <c r="T200" t="n">
-        <v>10343</v>
+        <v>10337</v>
       </c>
       <c r="U200" t="n">
-        <v>5171</v>
+        <v>5168</v>
       </c>
       <c r="V200" t="n">
-        <v>8902</v>
+        <v>8891</v>
       </c>
       <c r="W200" t="n">
         <v>25.8</v>
@@ -16261,16 +16261,16 @@
         <v>2068</v>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M201" t="n">
         <v>6847</v>
       </c>
       <c r="N201" t="n">
-        <v>51160</v>
+        <v>51180</v>
       </c>
       <c r="O201" t="n">
-        <v>38740</v>
+        <v>38720</v>
       </c>
       <c r="P201" t="n">
         <v>4992</v>
@@ -16282,16 +16282,16 @@
         <v>17189</v>
       </c>
       <c r="S201" t="n">
-        <v>21159</v>
+        <v>21139</v>
       </c>
       <c r="T201" t="n">
-        <v>11622</v>
+        <v>11616</v>
       </c>
       <c r="U201" t="n">
-        <v>5811</v>
+        <v>5808</v>
       </c>
       <c r="V201" t="n">
-        <v>3726</v>
+        <v>3715</v>
       </c>
       <c r="W201" t="n">
         <v>9.6</v>
@@ -16343,16 +16343,16 @@
         <v>2068</v>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M202" t="n">
         <v>6293</v>
       </c>
       <c r="N202" t="n">
-        <v>50575</v>
+        <v>50595</v>
       </c>
       <c r="O202" t="n">
-        <v>39325</v>
+        <v>39305</v>
       </c>
       <c r="P202" t="n">
         <v>4286</v>
@@ -16364,16 +16364,16 @@
         <v>17189</v>
       </c>
       <c r="S202" t="n">
-        <v>21749</v>
+        <v>21729</v>
       </c>
       <c r="T202" t="n">
-        <v>11798</v>
+        <v>11792</v>
       </c>
       <c r="U202" t="n">
-        <v>5899</v>
+        <v>5896</v>
       </c>
       <c r="V202" t="n">
-        <v>4053</v>
+        <v>4042</v>
       </c>
       <c r="W202" t="n">
         <v>10.3</v>
@@ -16425,16 +16425,16 @@
         <v>1169</v>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M203" t="n">
         <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>43377</v>
+        <v>43397</v>
       </c>
       <c r="O203" t="n">
-        <v>46523</v>
+        <v>46503</v>
       </c>
       <c r="P203" t="n">
         <v>6049</v>
@@ -16446,19 +16446,19 @@
         <v>17189</v>
       </c>
       <c r="S203" t="n">
-        <v>28735</v>
+        <v>28715</v>
       </c>
       <c r="T203" t="n">
-        <v>13957</v>
+        <v>13951</v>
       </c>
       <c r="U203" t="n">
-        <v>6978</v>
+        <v>6975</v>
       </c>
       <c r="V203" t="n">
-        <v>7800</v>
+        <v>7789</v>
       </c>
       <c r="W203" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="X203" t="inlineStr">
         <is>
@@ -16507,16 +16507,16 @@
         <v>1169</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M204" t="n">
         <v>8091</v>
       </c>
       <c r="N204" t="n">
-        <v>51475</v>
+        <v>51495</v>
       </c>
       <c r="O204" t="n">
-        <v>38425</v>
+        <v>38405</v>
       </c>
       <c r="P204" t="n">
         <v>2948</v>
@@ -16528,16 +16528,16 @@
         <v>17189</v>
       </c>
       <c r="S204" t="n">
-        <v>20787</v>
+        <v>20767</v>
       </c>
       <c r="T204" t="n">
-        <v>11528</v>
+        <v>11522</v>
       </c>
       <c r="U204" t="n">
-        <v>5764</v>
+        <v>5761</v>
       </c>
       <c r="V204" t="n">
-        <v>3496</v>
+        <v>3485</v>
       </c>
       <c r="W204" t="n">
         <v>9.1</v>
@@ -16589,16 +16589,16 @@
         <v>1169</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M205" t="n">
         <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>43173</v>
+        <v>43193</v>
       </c>
       <c r="O205" t="n">
-        <v>46727</v>
+        <v>46707</v>
       </c>
       <c r="P205" t="n">
         <v>4924</v>
@@ -16610,19 +16610,19 @@
         <v>17189</v>
       </c>
       <c r="S205" t="n">
-        <v>30164</v>
+        <v>30144</v>
       </c>
       <c r="T205" t="n">
-        <v>14018</v>
+        <v>14012</v>
       </c>
       <c r="U205" t="n">
-        <v>7009</v>
+        <v>7006</v>
       </c>
       <c r="V205" t="n">
-        <v>9137</v>
+        <v>9126</v>
       </c>
       <c r="W205" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="X205" t="inlineStr">
         <is>
@@ -16671,16 +16671,16 @@
         <v>1169</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M206" t="n">
         <v>554</v>
       </c>
       <c r="N206" t="n">
-        <v>43968</v>
+        <v>43988</v>
       </c>
       <c r="O206" t="n">
-        <v>45932</v>
+        <v>45912</v>
       </c>
       <c r="P206" t="n">
         <v>6614</v>
@@ -16692,16 +16692,16 @@
         <v>17189</v>
       </c>
       <c r="S206" t="n">
-        <v>24529</v>
+        <v>24509</v>
       </c>
       <c r="T206" t="n">
-        <v>13780</v>
+        <v>13774</v>
       </c>
       <c r="U206" t="n">
-        <v>6890</v>
+        <v>6887</v>
       </c>
       <c r="V206" t="n">
-        <v>3860</v>
+        <v>3849</v>
       </c>
       <c r="W206" t="n">
         <v>8.4</v>
@@ -16753,16 +16753,16 @@
         <v>1169</v>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M207" t="n">
         <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>43173</v>
+        <v>43193</v>
       </c>
       <c r="O207" t="n">
-        <v>46727</v>
+        <v>46707</v>
       </c>
       <c r="P207" t="n">
         <v>2948</v>
@@ -16774,16 +16774,16 @@
         <v>17189</v>
       </c>
       <c r="S207" t="n">
-        <v>29190</v>
+        <v>29170</v>
       </c>
       <c r="T207" t="n">
-        <v>14018</v>
+        <v>14012</v>
       </c>
       <c r="U207" t="n">
-        <v>7009</v>
+        <v>7006</v>
       </c>
       <c r="V207" t="n">
-        <v>8163</v>
+        <v>8152</v>
       </c>
       <c r="W207" t="n">
         <v>17.5</v>
@@ -16835,16 +16835,16 @@
         <v>1169</v>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M208" t="n">
         <v>8091</v>
       </c>
       <c r="N208" t="n">
-        <v>51264</v>
+        <v>51284</v>
       </c>
       <c r="O208" t="n">
-        <v>38636</v>
+        <v>38616</v>
       </c>
       <c r="P208" t="n">
         <v>14918</v>
@@ -16856,16 +16856,16 @@
         <v>17189</v>
       </c>
       <c r="S208" t="n">
-        <v>15378</v>
+        <v>15358</v>
       </c>
       <c r="T208" t="n">
-        <v>11591</v>
+        <v>11585</v>
       </c>
       <c r="U208" t="n">
-        <v>5795</v>
+        <v>5792</v>
       </c>
       <c r="V208" t="n">
-        <v>-2008</v>
+        <v>-2019</v>
       </c>
       <c r="W208" t="n">
         <v>-5.2</v>
@@ -16917,16 +16917,16 @@
         <v>1110</v>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M209" t="n">
         <v>7690</v>
       </c>
       <c r="N209" t="n">
-        <v>48910</v>
+        <v>48930</v>
       </c>
       <c r="O209" t="n">
-        <v>36496</v>
+        <v>36476</v>
       </c>
       <c r="P209" t="n">
         <v>4118</v>
@@ -16938,19 +16938,19 @@
         <v>17189</v>
       </c>
       <c r="S209" t="n">
-        <v>19588</v>
+        <v>19568</v>
       </c>
       <c r="T209" t="n">
-        <v>10949</v>
+        <v>10943</v>
       </c>
       <c r="U209" t="n">
-        <v>5474</v>
+        <v>5471</v>
       </c>
       <c r="V209" t="n">
-        <v>3165</v>
+        <v>3154</v>
       </c>
       <c r="W209" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X209" t="inlineStr">
         <is>
@@ -16999,16 +16999,16 @@
         <v>6592</v>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M210" t="n">
         <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>45983</v>
+        <v>46003</v>
       </c>
       <c r="O210" t="n">
-        <v>37917</v>
+        <v>37897</v>
       </c>
       <c r="P210" t="n">
         <v>4564</v>
@@ -17020,16 +17020,16 @@
         <v>17440</v>
       </c>
       <c r="S210" t="n">
-        <v>20863</v>
+        <v>20843</v>
       </c>
       <c r="T210" t="n">
-        <v>11375</v>
+        <v>11369</v>
       </c>
       <c r="U210" t="n">
-        <v>5688</v>
+        <v>5685</v>
       </c>
       <c r="V210" t="n">
-        <v>3800</v>
+        <v>3789</v>
       </c>
       <c r="W210" t="n">
         <v>10</v>
@@ -17081,16 +17081,16 @@
         <v>1078</v>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M211" t="n">
         <v>5803</v>
       </c>
       <c r="N211" t="n">
-        <v>45015</v>
+        <v>45035</v>
       </c>
       <c r="O211" t="n">
-        <v>37885</v>
+        <v>37865</v>
       </c>
       <c r="P211" t="n">
         <v>6198</v>
@@ -17102,19 +17102,19 @@
         <v>14537</v>
       </c>
       <c r="S211" t="n">
-        <v>22150</v>
+        <v>22130</v>
       </c>
       <c r="T211" t="n">
-        <v>11366</v>
+        <v>11360</v>
       </c>
       <c r="U211" t="n">
-        <v>5683</v>
+        <v>5680</v>
       </c>
       <c r="V211" t="n">
-        <v>5102</v>
+        <v>5091</v>
       </c>
       <c r="W211" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="X211" t="inlineStr">
         <is>
@@ -17163,16 +17163,16 @@
         <v>1078</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M212" t="n">
         <v>4145</v>
       </c>
       <c r="N212" t="n">
-        <v>43357</v>
+        <v>43377</v>
       </c>
       <c r="O212" t="n">
-        <v>39543</v>
+        <v>39523</v>
       </c>
       <c r="P212" t="n">
         <v>10516</v>
@@ -17184,16 +17184,16 @@
         <v>0</v>
       </c>
       <c r="S212" t="n">
-        <v>33227</v>
+        <v>33207</v>
       </c>
       <c r="T212" t="n">
-        <v>11863</v>
+        <v>11857</v>
       </c>
       <c r="U212" t="n">
-        <v>5931</v>
+        <v>5928</v>
       </c>
       <c r="V212" t="n">
-        <v>15433</v>
+        <v>15422</v>
       </c>
       <c r="W212" t="n">
         <v>39</v>
@@ -17241,16 +17241,16 @@
         <v>1071</v>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M213" t="n">
         <v>7413</v>
       </c>
       <c r="N213" t="n">
-        <v>47116</v>
+        <v>47136</v>
       </c>
       <c r="O213" t="n">
-        <v>35252</v>
+        <v>35232</v>
       </c>
       <c r="P213" t="n">
         <v>2948</v>
@@ -17262,16 +17262,16 @@
         <v>14537</v>
       </c>
       <c r="S213" t="n">
-        <v>20267</v>
+        <v>20247</v>
       </c>
       <c r="T213" t="n">
-        <v>10576</v>
+        <v>10570</v>
       </c>
       <c r="U213" t="n">
-        <v>5288</v>
+        <v>5285</v>
       </c>
       <c r="V213" t="n">
-        <v>4404</v>
+        <v>4393</v>
       </c>
       <c r="W213" t="n">
         <v>12.5</v>
@@ -17323,16 +17323,16 @@
         <v>1070</v>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M214" t="n">
         <v>19320</v>
       </c>
       <c r="N214" t="n">
-        <v>58094</v>
+        <v>58114</v>
       </c>
       <c r="O214" t="n">
-        <v>24226</v>
+        <v>24206</v>
       </c>
       <c r="P214" t="n">
         <v>11584</v>
@@ -17344,19 +17344,19 @@
         <v>14537</v>
       </c>
       <c r="S214" t="n">
-        <v>2305</v>
+        <v>2285</v>
       </c>
       <c r="T214" t="n">
-        <v>7268</v>
+        <v>7262</v>
       </c>
       <c r="U214" t="n">
-        <v>3634</v>
+        <v>3631</v>
       </c>
       <c r="V214" t="n">
-        <v>-8597</v>
+        <v>-8608</v>
       </c>
       <c r="W214" t="n">
-        <v>-35.5</v>
+        <v>-35.6</v>
       </c>
       <c r="X214" t="inlineStr">
         <is>
@@ -17405,16 +17405,16 @@
         <v>1066</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M215" t="n">
         <v>951</v>
       </c>
       <c r="N215" t="n">
-        <v>40048</v>
+        <v>40068</v>
       </c>
       <c r="O215" t="n">
-        <v>41959</v>
+        <v>41939</v>
       </c>
       <c r="P215" t="n">
         <v>5415</v>
@@ -17426,16 +17426,16 @@
         <v>14537</v>
       </c>
       <c r="S215" t="n">
-        <v>27557</v>
+        <v>27537</v>
       </c>
       <c r="T215" t="n">
-        <v>12588</v>
+        <v>12582</v>
       </c>
       <c r="U215" t="n">
-        <v>6294</v>
+        <v>6291</v>
       </c>
       <c r="V215" t="n">
-        <v>8675</v>
+        <v>8664</v>
       </c>
       <c r="W215" t="n">
         <v>20.7</v>
@@ -17487,16 +17487,16 @@
         <v>1066</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M216" t="n">
         <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>39569</v>
+        <v>39589</v>
       </c>
       <c r="O216" t="n">
-        <v>42438</v>
+        <v>42418</v>
       </c>
       <c r="P216" t="n">
         <v>3099</v>
@@ -17508,16 +17508,16 @@
         <v>14537</v>
       </c>
       <c r="S216" t="n">
-        <v>27601</v>
+        <v>27581</v>
       </c>
       <c r="T216" t="n">
-        <v>12731</v>
+        <v>12725</v>
       </c>
       <c r="U216" t="n">
-        <v>6366</v>
+        <v>6363</v>
       </c>
       <c r="V216" t="n">
-        <v>8504</v>
+        <v>8493</v>
       </c>
       <c r="W216" t="n">
         <v>20</v>
@@ -17569,16 +17569,16 @@
         <v>1066</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M217" t="n">
         <v>951</v>
       </c>
       <c r="N217" t="n">
-        <v>44148</v>
+        <v>44168</v>
       </c>
       <c r="O217" t="n">
-        <v>37859</v>
+        <v>37839</v>
       </c>
       <c r="P217" t="n">
         <v>4463</v>
@@ -17590,16 +17590,16 @@
         <v>14537</v>
       </c>
       <c r="S217" t="n">
-        <v>23059</v>
+        <v>23039</v>
       </c>
       <c r="T217" t="n">
-        <v>11358</v>
+        <v>11352</v>
       </c>
       <c r="U217" t="n">
-        <v>5679</v>
+        <v>5676</v>
       </c>
       <c r="V217" t="n">
-        <v>6022</v>
+        <v>6011</v>
       </c>
       <c r="W217" t="n">
         <v>15.9</v>
@@ -17651,16 +17651,16 @@
         <v>1057</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M218" t="n">
         <v>5018</v>
       </c>
       <c r="N218" t="n">
-        <v>43797</v>
+        <v>43817</v>
       </c>
       <c r="O218" t="n">
-        <v>37538</v>
+        <v>37518</v>
       </c>
       <c r="P218" t="n">
         <v>4947</v>
@@ -17672,16 +17672,16 @@
         <v>14537</v>
       </c>
       <c r="S218" t="n">
-        <v>23054</v>
+        <v>23034</v>
       </c>
       <c r="T218" t="n">
-        <v>11261</v>
+        <v>11255</v>
       </c>
       <c r="U218" t="n">
-        <v>5631</v>
+        <v>5628</v>
       </c>
       <c r="V218" t="n">
-        <v>6162</v>
+        <v>6151</v>
       </c>
       <c r="W218" t="n">
         <v>16.4</v>
@@ -17733,16 +17733,16 @@
         <v>1039</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M219" t="n">
         <v>9134</v>
       </c>
       <c r="N219" t="n">
-        <v>47401</v>
+        <v>47421</v>
       </c>
       <c r="O219" t="n">
-        <v>32499</v>
+        <v>32479</v>
       </c>
       <c r="P219" t="n">
         <v>6882</v>
@@ -17754,16 +17754,16 @@
         <v>12464</v>
       </c>
       <c r="S219" t="n">
-        <v>18053</v>
+        <v>18033</v>
       </c>
       <c r="T219" t="n">
-        <v>9750</v>
+        <v>9744</v>
       </c>
       <c r="U219" t="n">
-        <v>4875</v>
+        <v>4872</v>
       </c>
       <c r="V219" t="n">
-        <v>3428</v>
+        <v>3417</v>
       </c>
       <c r="W219" t="n">
         <v>10.5</v>
@@ -17816,16 +17816,16 @@
         <v>1039</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M220" t="n">
         <v>9134</v>
       </c>
       <c r="N220" t="n">
-        <v>47401</v>
+        <v>47421</v>
       </c>
       <c r="O220" t="n">
-        <v>32499</v>
+        <v>32479</v>
       </c>
       <c r="P220" t="n">
         <v>7175</v>
@@ -17837,19 +17837,19 @@
         <v>12464</v>
       </c>
       <c r="S220" t="n">
-        <v>18059</v>
+        <v>18039</v>
       </c>
       <c r="T220" t="n">
-        <v>9750</v>
+        <v>9744</v>
       </c>
       <c r="U220" t="n">
-        <v>4875</v>
+        <v>4872</v>
       </c>
       <c r="V220" t="n">
-        <v>3434</v>
+        <v>3423</v>
       </c>
       <c r="W220" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="X220" t="inlineStr">
         <is>
@@ -17899,16 +17899,16 @@
         <v>1036</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M221" t="n">
         <v>7175</v>
       </c>
       <c r="N221" t="n">
-        <v>45652</v>
+        <v>45672</v>
       </c>
       <c r="O221" t="n">
-        <v>34069</v>
+        <v>34049</v>
       </c>
       <c r="P221" t="n">
         <v>0</v>
@@ -17920,16 +17920,16 @@
         <v>13664</v>
       </c>
       <c r="S221" t="n">
-        <v>25954</v>
+        <v>25934</v>
       </c>
       <c r="T221" t="n">
-        <v>10221</v>
+        <v>10215</v>
       </c>
       <c r="U221" t="n">
-        <v>5110</v>
+        <v>5107</v>
       </c>
       <c r="V221" t="n">
-        <v>10623</v>
+        <v>10612</v>
       </c>
       <c r="W221" t="n">
         <v>31.2</v>
@@ -17981,16 +17981,16 @@
         <v>4441</v>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M222" t="n">
         <v>10682</v>
       </c>
       <c r="N222" t="n">
-        <v>55992</v>
+        <v>56012</v>
       </c>
       <c r="O222" t="n">
-        <v>23211</v>
+        <v>23191</v>
       </c>
       <c r="P222" t="n">
         <v>5919</v>
@@ -18002,16 +18002,16 @@
         <v>12464</v>
       </c>
       <c r="S222" t="n">
-        <v>9827</v>
+        <v>9807</v>
       </c>
       <c r="T222" t="n">
-        <v>6963</v>
+        <v>6957</v>
       </c>
       <c r="U222" t="n">
-        <v>3482</v>
+        <v>3479</v>
       </c>
       <c r="V222" t="n">
-        <v>-618</v>
+        <v>-629</v>
       </c>
       <c r="W222" t="n">
         <v>-2.7</v>
@@ -18064,16 +18064,16 @@
         <v>4541</v>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M223" t="n">
         <v>17414</v>
       </c>
       <c r="N223" t="n">
-        <v>58784</v>
+        <v>58804</v>
       </c>
       <c r="O223" t="n">
-        <v>19972</v>
+        <v>19952</v>
       </c>
       <c r="P223" t="n">
         <v>7914</v>
@@ -18085,19 +18085,19 @@
         <v>16574</v>
       </c>
       <c r="S223" t="n">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="T223" t="n">
-        <v>5992</v>
+        <v>5986</v>
       </c>
       <c r="U223" t="n">
-        <v>2996</v>
+        <v>2993</v>
       </c>
       <c r="V223" t="n">
-        <v>-8653</v>
+        <v>-8664</v>
       </c>
       <c r="W223" t="n">
-        <v>-43.3</v>
+        <v>-43.4</v>
       </c>
       <c r="X223" t="inlineStr">
         <is>
@@ -18146,16 +18146,16 @@
         <v>1014</v>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>37650</v>
+        <v>37670</v>
       </c>
       <c r="O224" t="n">
-        <v>40372</v>
+        <v>40352</v>
       </c>
       <c r="P224" t="n">
         <v>6040</v>
@@ -18167,16 +18167,16 @@
         <v>13664</v>
       </c>
       <c r="S224" t="n">
-        <v>23368</v>
+        <v>23348</v>
       </c>
       <c r="T224" t="n">
-        <v>12112</v>
+        <v>12106</v>
       </c>
       <c r="U224" t="n">
-        <v>6056</v>
+        <v>6053</v>
       </c>
       <c r="V224" t="n">
-        <v>5201</v>
+        <v>5190</v>
       </c>
       <c r="W224" t="n">
         <v>12.9</v>
@@ -18228,16 +18228,16 @@
         <v>4541</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M225" t="n">
         <v>11570</v>
       </c>
       <c r="N225" t="n">
-        <v>52600</v>
+        <v>52620</v>
       </c>
       <c r="O225" t="n">
-        <v>25422</v>
+        <v>25402</v>
       </c>
       <c r="P225" t="n">
         <v>4386</v>
@@ -18249,19 +18249,19 @@
         <v>13664</v>
       </c>
       <c r="S225" t="n">
-        <v>11971</v>
+        <v>11951</v>
       </c>
       <c r="T225" t="n">
-        <v>7627</v>
+        <v>7621</v>
       </c>
       <c r="U225" t="n">
-        <v>3813</v>
+        <v>3810</v>
       </c>
       <c r="V225" t="n">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="W225" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="X225" t="inlineStr">
         <is>
@@ -18310,16 +18310,16 @@
         <v>1014</v>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M226" t="n">
         <v>11570</v>
       </c>
       <c r="N226" t="n">
-        <v>49073</v>
+        <v>49093</v>
       </c>
       <c r="O226" t="n">
-        <v>28949</v>
+        <v>28929</v>
       </c>
       <c r="P226" t="n">
         <v>3099</v>
@@ -18331,16 +18331,16 @@
         <v>13664</v>
       </c>
       <c r="S226" t="n">
-        <v>15586</v>
+        <v>15566</v>
       </c>
       <c r="T226" t="n">
-        <v>8685</v>
+        <v>8679</v>
       </c>
       <c r="U226" t="n">
-        <v>4342</v>
+        <v>4339</v>
       </c>
       <c r="V226" t="n">
-        <v>2559</v>
+        <v>2548</v>
       </c>
       <c r="W226" t="n">
         <v>8.800000000000001</v>
@@ -18392,16 +18392,16 @@
         <v>1014</v>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M227" t="n">
         <v>11570</v>
       </c>
       <c r="N227" t="n">
-        <v>49073</v>
+        <v>49093</v>
       </c>
       <c r="O227" t="n">
-        <v>28949</v>
+        <v>28929</v>
       </c>
       <c r="P227" t="n">
         <v>3098</v>
@@ -18413,19 +18413,19 @@
         <v>13664</v>
       </c>
       <c r="S227" t="n">
-        <v>14986</v>
+        <v>14966</v>
       </c>
       <c r="T227" t="n">
-        <v>8685</v>
+        <v>8679</v>
       </c>
       <c r="U227" t="n">
-        <v>4342</v>
+        <v>4339</v>
       </c>
       <c r="V227" t="n">
-        <v>1959</v>
+        <v>1948</v>
       </c>
       <c r="W227" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X227" t="inlineStr">
         <is>
@@ -18474,16 +18474,16 @@
         <v>1014</v>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M228" t="n">
         <v>14691</v>
       </c>
       <c r="N228" t="n">
-        <v>52194</v>
+        <v>52214</v>
       </c>
       <c r="O228" t="n">
-        <v>25828</v>
+        <v>25808</v>
       </c>
       <c r="P228" t="n">
         <v>0</v>
@@ -18495,16 +18495,16 @@
         <v>13664</v>
       </c>
       <c r="S228" t="n">
-        <v>15664</v>
+        <v>15644</v>
       </c>
       <c r="T228" t="n">
-        <v>7748</v>
+        <v>7742</v>
       </c>
       <c r="U228" t="n">
-        <v>3874</v>
+        <v>3871</v>
       </c>
       <c r="V228" t="n">
-        <v>4041</v>
+        <v>4030</v>
       </c>
       <c r="W228" t="n">
         <v>15.6</v>
@@ -18556,16 +18556,16 @@
         <v>1014</v>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M229" t="n">
         <v>11570</v>
       </c>
       <c r="N229" t="n">
-        <v>49073</v>
+        <v>49093</v>
       </c>
       <c r="O229" t="n">
-        <v>28949</v>
+        <v>28929</v>
       </c>
       <c r="P229" t="n">
         <v>0</v>
@@ -18577,16 +18577,16 @@
         <v>13664</v>
       </c>
       <c r="S229" t="n">
-        <v>19684</v>
+        <v>19664</v>
       </c>
       <c r="T229" t="n">
-        <v>8685</v>
+        <v>8679</v>
       </c>
       <c r="U229" t="n">
-        <v>4342</v>
+        <v>4339</v>
       </c>
       <c r="V229" t="n">
-        <v>6657</v>
+        <v>6646</v>
       </c>
       <c r="W229" t="n">
         <v>23</v>
@@ -18638,16 +18638,16 @@
         <v>1014</v>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M230" t="n">
         <v>5462</v>
       </c>
       <c r="N230" t="n">
-        <v>43097</v>
+        <v>43117</v>
       </c>
       <c r="O230" t="n">
-        <v>34925</v>
+        <v>34905</v>
       </c>
       <c r="P230" t="n">
         <v>4386</v>
@@ -18659,16 +18659,16 @@
         <v>13664</v>
       </c>
       <c r="S230" t="n">
-        <v>21175</v>
+        <v>21155</v>
       </c>
       <c r="T230" t="n">
-        <v>10478</v>
+        <v>10472</v>
       </c>
       <c r="U230" t="n">
-        <v>5239</v>
+        <v>5236</v>
       </c>
       <c r="V230" t="n">
-        <v>5459</v>
+        <v>5448</v>
       </c>
       <c r="W230" t="n">
         <v>15.6</v>
@@ -18720,16 +18720,16 @@
         <v>1014</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M231" t="n">
         <v>3901</v>
       </c>
       <c r="N231" t="n">
-        <v>41337</v>
+        <v>41357</v>
       </c>
       <c r="O231" t="n">
-        <v>36685</v>
+        <v>36665</v>
       </c>
       <c r="P231" t="n">
         <v>5350</v>
@@ -18741,16 +18741,16 @@
         <v>13664</v>
       </c>
       <c r="S231" t="n">
-        <v>22821</v>
+        <v>22801</v>
       </c>
       <c r="T231" t="n">
-        <v>11006</v>
+        <v>11000</v>
       </c>
       <c r="U231" t="n">
-        <v>5503</v>
+        <v>5500</v>
       </c>
       <c r="V231" t="n">
-        <v>6313</v>
+        <v>6302</v>
       </c>
       <c r="W231" t="n">
         <v>17.2</v>
@@ -18802,16 +18802,16 @@
         <v>1014</v>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M232" t="n">
         <v>11570</v>
       </c>
       <c r="N232" t="n">
-        <v>49073</v>
+        <v>49093</v>
       </c>
       <c r="O232" t="n">
-        <v>28949</v>
+        <v>28929</v>
       </c>
       <c r="P232" t="n">
         <v>5368</v>
@@ -18823,19 +18823,19 @@
         <v>13664</v>
       </c>
       <c r="S232" t="n">
-        <v>15017</v>
+        <v>14997</v>
       </c>
       <c r="T232" t="n">
-        <v>8685</v>
+        <v>8679</v>
       </c>
       <c r="U232" t="n">
-        <v>4342</v>
+        <v>4339</v>
       </c>
       <c r="V232" t="n">
-        <v>1990</v>
+        <v>1979</v>
       </c>
       <c r="W232" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X232" t="inlineStr">
         <is>
@@ -18884,16 +18884,16 @@
         <v>1014</v>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M233" t="n">
         <v>3901</v>
       </c>
       <c r="N233" t="n">
-        <v>41552</v>
+        <v>41572</v>
       </c>
       <c r="O233" t="n">
-        <v>36470</v>
+        <v>36450</v>
       </c>
       <c r="P233" t="n">
         <v>1</v>
@@ -18905,16 +18905,16 @@
         <v>13664</v>
       </c>
       <c r="S233" t="n">
-        <v>27304</v>
+        <v>27284</v>
       </c>
       <c r="T233" t="n">
-        <v>10941</v>
+        <v>10935</v>
       </c>
       <c r="U233" t="n">
-        <v>5470</v>
+        <v>5468</v>
       </c>
       <c r="V233" t="n">
-        <v>10892</v>
+        <v>10882</v>
       </c>
       <c r="W233" t="n">
         <v>29.9</v>
@@ -18966,16 +18966,16 @@
         <v>1014</v>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M234" t="n">
         <v>11570</v>
       </c>
       <c r="N234" t="n">
-        <v>49073</v>
+        <v>49093</v>
       </c>
       <c r="O234" t="n">
-        <v>28949</v>
+        <v>28929</v>
       </c>
       <c r="P234" t="n">
         <v>3099</v>
@@ -18987,19 +18987,19 @@
         <v>13664</v>
       </c>
       <c r="S234" t="n">
-        <v>14985</v>
+        <v>14965</v>
       </c>
       <c r="T234" t="n">
-        <v>8685</v>
+        <v>8679</v>
       </c>
       <c r="U234" t="n">
-        <v>4342</v>
+        <v>4339</v>
       </c>
       <c r="V234" t="n">
-        <v>1958</v>
+        <v>1947</v>
       </c>
       <c r="W234" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X234" t="inlineStr">
         <is>
@@ -19048,16 +19048,16 @@
         <v>1014</v>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M235" t="n">
         <v>7669</v>
       </c>
       <c r="N235" t="n">
-        <v>45172</v>
+        <v>45192</v>
       </c>
       <c r="O235" t="n">
-        <v>32850</v>
+        <v>32830</v>
       </c>
       <c r="P235" t="n">
         <v>7495</v>
@@ -19069,16 +19069,16 @@
         <v>13664</v>
       </c>
       <c r="S235" t="n">
-        <v>20040</v>
+        <v>20020</v>
       </c>
       <c r="T235" t="n">
-        <v>9855</v>
+        <v>9849</v>
       </c>
       <c r="U235" t="n">
-        <v>4928</v>
+        <v>4924</v>
       </c>
       <c r="V235" t="n">
-        <v>5258</v>
+        <v>5246</v>
       </c>
       <c r="W235" t="n">
         <v>16</v>
@@ -19130,16 +19130,16 @@
         <v>1014</v>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M236" t="n">
         <v>11570</v>
       </c>
       <c r="N236" t="n">
-        <v>49073</v>
+        <v>49093</v>
       </c>
       <c r="O236" t="n">
-        <v>28949</v>
+        <v>28929</v>
       </c>
       <c r="P236" t="n">
         <v>3099</v>
@@ -19151,16 +19151,16 @@
         <v>13664</v>
       </c>
       <c r="S236" t="n">
-        <v>14686</v>
+        <v>14666</v>
       </c>
       <c r="T236" t="n">
-        <v>8685</v>
+        <v>8679</v>
       </c>
       <c r="U236" t="n">
-        <v>4342</v>
+        <v>4339</v>
       </c>
       <c r="V236" t="n">
-        <v>1659</v>
+        <v>1648</v>
       </c>
       <c r="W236" t="n">
         <v>5.7</v>
@@ -19212,16 +19212,16 @@
         <v>1014</v>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M237" t="n">
         <v>4569</v>
       </c>
       <c r="N237" t="n">
-        <v>42356</v>
+        <v>42376</v>
       </c>
       <c r="O237" t="n">
-        <v>35666</v>
+        <v>35646</v>
       </c>
       <c r="P237" t="n">
         <v>4136</v>
@@ -19233,16 +19233,16 @@
         <v>13664</v>
       </c>
       <c r="S237" t="n">
-        <v>22166</v>
+        <v>22146</v>
       </c>
       <c r="T237" t="n">
-        <v>10700</v>
+        <v>10694</v>
       </c>
       <c r="U237" t="n">
-        <v>5350</v>
+        <v>5347</v>
       </c>
       <c r="V237" t="n">
-        <v>6116</v>
+        <v>6105</v>
       </c>
       <c r="W237" t="n">
         <v>17.1</v>
@@ -19294,16 +19294,16 @@
         <v>1014</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M238" t="n">
         <v>11575</v>
       </c>
       <c r="N238" t="n">
-        <v>49080</v>
+        <v>49100</v>
       </c>
       <c r="O238" t="n">
-        <v>28942</v>
+        <v>28922</v>
       </c>
       <c r="P238" t="n">
         <v>4136</v>
@@ -19315,16 +19315,16 @@
         <v>13664</v>
       </c>
       <c r="S238" t="n">
-        <v>15641</v>
+        <v>15621</v>
       </c>
       <c r="T238" t="n">
-        <v>8683</v>
+        <v>8677</v>
       </c>
       <c r="U238" t="n">
-        <v>4341</v>
+        <v>4338</v>
       </c>
       <c r="V238" t="n">
-        <v>2617</v>
+        <v>2606</v>
       </c>
       <c r="W238" t="n">
         <v>9</v>
@@ -19376,16 +19376,16 @@
         <v>1014</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M239" t="n">
         <v>667</v>
       </c>
       <c r="N239" t="n">
-        <v>42356</v>
+        <v>42376</v>
       </c>
       <c r="O239" t="n">
-        <v>35666</v>
+        <v>35646</v>
       </c>
       <c r="P239" t="n">
         <v>1000</v>
@@ -19397,19 +19397,19 @@
         <v>13664</v>
       </c>
       <c r="S239" t="n">
-        <v>23701</v>
+        <v>23681</v>
       </c>
       <c r="T239" t="n">
-        <v>10700</v>
+        <v>10694</v>
       </c>
       <c r="U239" t="n">
-        <v>5350</v>
+        <v>5347</v>
       </c>
       <c r="V239" t="n">
-        <v>7651</v>
+        <v>7640</v>
       </c>
       <c r="W239" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="X239" t="inlineStr">
         <is>
@@ -19458,16 +19458,16 @@
         <v>1013</v>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M240" t="n">
         <v>7011</v>
       </c>
       <c r="N240" t="n">
-        <v>43858</v>
+        <v>43878</v>
       </c>
       <c r="O240" t="n">
-        <v>34042</v>
+        <v>34022</v>
       </c>
       <c r="P240" t="n">
         <v>207</v>
@@ -19479,16 +19479,16 @@
         <v>11912</v>
       </c>
       <c r="S240" t="n">
-        <v>26422</v>
+        <v>26402</v>
       </c>
       <c r="T240" t="n">
-        <v>10213</v>
+        <v>10207</v>
       </c>
       <c r="U240" t="n">
-        <v>5106</v>
+        <v>5103</v>
       </c>
       <c r="V240" t="n">
-        <v>11103</v>
+        <v>11092</v>
       </c>
       <c r="W240" t="n">
         <v>32.6</v>
@@ -19540,16 +19540,16 @@
         <v>1013</v>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M241" t="n">
         <v>7011</v>
       </c>
       <c r="N241" t="n">
-        <v>44597</v>
+        <v>44617</v>
       </c>
       <c r="O241" t="n">
-        <v>33303</v>
+        <v>33283</v>
       </c>
       <c r="P241" t="n">
         <v>7749</v>
@@ -19561,16 +19561,16 @@
         <v>11912</v>
       </c>
       <c r="S241" t="n">
-        <v>18642</v>
+        <v>18622</v>
       </c>
       <c r="T241" t="n">
-        <v>9991</v>
+        <v>9985</v>
       </c>
       <c r="U241" t="n">
-        <v>4995</v>
+        <v>4992</v>
       </c>
       <c r="V241" t="n">
-        <v>3656</v>
+        <v>3645</v>
       </c>
       <c r="W241" t="n">
         <v>11</v>
@@ -19622,16 +19622,16 @@
         <v>1013</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M242" t="n">
         <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>37588</v>
+        <v>37608</v>
       </c>
       <c r="O242" t="n">
-        <v>40312</v>
+        <v>40292</v>
       </c>
       <c r="P242" t="n">
         <v>5441</v>
@@ -19643,16 +19643,16 @@
         <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>39870</v>
+        <v>39850</v>
       </c>
       <c r="T242" t="n">
-        <v>12094</v>
+        <v>12088</v>
       </c>
       <c r="U242" t="n">
-        <v>6047</v>
+        <v>6044</v>
       </c>
       <c r="V242" t="n">
-        <v>21730</v>
+        <v>21719</v>
       </c>
       <c r="W242" t="n">
         <v>53.9</v>
@@ -19704,16 +19704,16 @@
         <v>1013</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M243" t="n">
         <v>46696</v>
       </c>
       <c r="N243" t="n">
-        <v>84138</v>
+        <v>84158</v>
       </c>
       <c r="O243" t="n">
-        <v>-6238</v>
+        <v>-6258</v>
       </c>
       <c r="P243" t="n">
         <v>4197</v>
@@ -19725,16 +19725,16 @@
         <v>16349</v>
       </c>
       <c r="S243" t="n">
-        <v>-22484</v>
+        <v>-22504</v>
       </c>
       <c r="T243" t="n">
-        <v>-1871</v>
+        <v>-1877</v>
       </c>
       <c r="U243" t="n">
-        <v>-936</v>
+        <v>-939</v>
       </c>
       <c r="V243" t="n">
-        <v>-19677</v>
+        <v>-19688</v>
       </c>
       <c r="X243" t="inlineStr">
         <is>
@@ -19783,16 +19783,16 @@
         <v>1000</v>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M244" t="n">
         <v>3845</v>
       </c>
       <c r="N244" t="n">
-        <v>44064</v>
+        <v>44084</v>
       </c>
       <c r="O244" t="n">
-        <v>32836</v>
+        <v>32816</v>
       </c>
       <c r="P244" t="n">
         <v>1000</v>
@@ -19804,16 +19804,16 @@
         <v>12651</v>
       </c>
       <c r="S244" t="n">
-        <v>21685</v>
+        <v>21665</v>
       </c>
       <c r="T244" t="n">
-        <v>9851</v>
+        <v>9845</v>
       </c>
       <c r="U244" t="n">
-        <v>4925</v>
+        <v>4922</v>
       </c>
       <c r="V244" t="n">
-        <v>6909</v>
+        <v>6898</v>
       </c>
       <c r="W244" t="n">
         <v>21</v>
@@ -19865,16 +19865,16 @@
         <v>987</v>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M245" t="n">
         <v>5313</v>
       </c>
       <c r="N245" t="n">
-        <v>41925</v>
+        <v>41945</v>
       </c>
       <c r="O245" t="n">
-        <v>33975</v>
+        <v>33955</v>
       </c>
       <c r="P245" t="n">
         <v>0</v>
@@ -19886,16 +19886,16 @@
         <v>11465</v>
       </c>
       <c r="S245" t="n">
-        <v>29160</v>
+        <v>29140</v>
       </c>
       <c r="T245" t="n">
-        <v>10192</v>
+        <v>10186</v>
       </c>
       <c r="U245" t="n">
-        <v>5096</v>
+        <v>5093</v>
       </c>
       <c r="V245" t="n">
-        <v>13871</v>
+        <v>13860</v>
       </c>
       <c r="W245" t="n">
         <v>40.8</v>
@@ -19947,16 +19947,16 @@
         <v>987</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M246" t="n">
         <v>5313</v>
       </c>
       <c r="N246" t="n">
-        <v>41980</v>
+        <v>42000</v>
       </c>
       <c r="O246" t="n">
-        <v>33920</v>
+        <v>33900</v>
       </c>
       <c r="P246" t="n">
         <v>3099</v>
@@ -19968,16 +19968,16 @@
         <v>11465</v>
       </c>
       <c r="S246" t="n">
-        <v>22055</v>
+        <v>22035</v>
       </c>
       <c r="T246" t="n">
-        <v>10176</v>
+        <v>10170</v>
       </c>
       <c r="U246" t="n">
-        <v>5088</v>
+        <v>5085</v>
       </c>
       <c r="V246" t="n">
-        <v>6791</v>
+        <v>6780</v>
       </c>
       <c r="W246" t="n">
         <v>20</v>
@@ -20029,16 +20029,16 @@
         <v>987</v>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M247" t="n">
         <v>10541</v>
       </c>
       <c r="N247" t="n">
-        <v>47094</v>
+        <v>47114</v>
       </c>
       <c r="O247" t="n">
-        <v>28806</v>
+        <v>28786</v>
       </c>
       <c r="P247" t="n">
         <v>5103</v>
@@ -20050,16 +20050,16 @@
         <v>13482</v>
       </c>
       <c r="S247" t="n">
-        <v>13220</v>
+        <v>13200</v>
       </c>
       <c r="T247" t="n">
-        <v>8642</v>
+        <v>8636</v>
       </c>
       <c r="U247" t="n">
-        <v>4321</v>
+        <v>4318</v>
       </c>
       <c r="V247" t="n">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="W247" t="n">
         <v>0.9</v>
@@ -20111,16 +20111,16 @@
         <v>987</v>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M248" t="n">
         <v>3795</v>
       </c>
       <c r="N248" t="n">
-        <v>40420</v>
+        <v>40440</v>
       </c>
       <c r="O248" t="n">
-        <v>35480</v>
+        <v>35460</v>
       </c>
       <c r="P248" t="n">
         <v>1000</v>
@@ -20132,16 +20132,16 @@
         <v>11465</v>
       </c>
       <c r="S248" t="n">
-        <v>25614</v>
+        <v>25594</v>
       </c>
       <c r="T248" t="n">
-        <v>10644</v>
+        <v>10638</v>
       </c>
       <c r="U248" t="n">
-        <v>5322</v>
+        <v>5319</v>
       </c>
       <c r="V248" t="n">
-        <v>9648</v>
+        <v>9637</v>
       </c>
       <c r="W248" t="n">
         <v>27.2</v>
@@ -20189,16 +20189,16 @@
         <v>984</v>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M249" t="n">
         <v>11453</v>
       </c>
       <c r="N249" t="n">
-        <v>47849</v>
+        <v>47869</v>
       </c>
       <c r="O249" t="n">
-        <v>27832</v>
+        <v>27812</v>
       </c>
       <c r="P249" t="n">
         <v>3099</v>
@@ -20210,16 +20210,16 @@
         <v>13664</v>
       </c>
       <c r="S249" t="n">
-        <v>13868</v>
+        <v>13848</v>
       </c>
       <c r="T249" t="n">
-        <v>8350</v>
+        <v>8344</v>
       </c>
       <c r="U249" t="n">
-        <v>4175</v>
+        <v>4172</v>
       </c>
       <c r="V249" t="n">
-        <v>1344</v>
+        <v>1333</v>
       </c>
       <c r="W249" t="n">
         <v>4.8</v>
@@ -20271,16 +20271,16 @@
         <v>978</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M250" t="n">
         <v>4487</v>
       </c>
       <c r="N250" t="n">
-        <v>6022</v>
+        <v>6042</v>
       </c>
       <c r="O250" t="n">
-        <v>69203</v>
+        <v>69183</v>
       </c>
       <c r="P250" t="n">
         <v>1000</v>
@@ -20292,16 +20292,16 @@
         <v>13482</v>
       </c>
       <c r="S250" t="n">
-        <v>57320</v>
+        <v>57300</v>
       </c>
       <c r="T250" t="n">
-        <v>20761</v>
+        <v>20755</v>
       </c>
       <c r="U250" t="n">
-        <v>10380</v>
+        <v>10377</v>
       </c>
       <c r="V250" t="n">
-        <v>26179</v>
+        <v>26168</v>
       </c>
       <c r="W250" t="n">
         <v>37.8</v>
@@ -20353,16 +20353,16 @@
         <v>1723</v>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M251" t="n">
         <v>5139</v>
       </c>
       <c r="N251" t="n">
-        <v>41790</v>
+        <v>41810</v>
       </c>
       <c r="O251" t="n">
-        <v>33110</v>
+        <v>33090</v>
       </c>
       <c r="P251" t="n">
         <v>3549</v>
@@ -20374,16 +20374,16 @@
         <v>12464</v>
       </c>
       <c r="S251" t="n">
-        <v>19397</v>
+        <v>19377</v>
       </c>
       <c r="T251" t="n">
-        <v>9933</v>
+        <v>9927</v>
       </c>
       <c r="U251" t="n">
-        <v>4966</v>
+        <v>4964</v>
       </c>
       <c r="V251" t="n">
-        <v>4498</v>
+        <v>4486</v>
       </c>
       <c r="W251" t="n">
         <v>13.6</v>
@@ -20436,16 +20436,16 @@
         <v>974</v>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M252" t="n">
         <v>727</v>
       </c>
       <c r="N252" t="n">
-        <v>36712</v>
+        <v>36732</v>
       </c>
       <c r="O252" t="n">
-        <v>38188</v>
+        <v>38168</v>
       </c>
       <c r="P252" t="n">
         <v>2948</v>
@@ -20457,16 +20457,16 @@
         <v>13482</v>
       </c>
       <c r="S252" t="n">
-        <v>24457</v>
+        <v>24437</v>
       </c>
       <c r="T252" t="n">
-        <v>11456</v>
+        <v>11450</v>
       </c>
       <c r="U252" t="n">
-        <v>5728</v>
+        <v>5725</v>
       </c>
       <c r="V252" t="n">
-        <v>7272</v>
+        <v>7261</v>
       </c>
       <c r="W252" t="n">
         <v>19</v>
@@ -20597,16 +20597,16 @@
         <v>974</v>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M254" t="n">
         <v>10162</v>
       </c>
       <c r="N254" t="n">
-        <v>46312</v>
+        <v>46332</v>
       </c>
       <c r="O254" t="n">
-        <v>28588</v>
+        <v>28568</v>
       </c>
       <c r="P254" t="n">
         <v>5179</v>
@@ -20618,16 +20618,16 @@
         <v>12464</v>
       </c>
       <c r="S254" t="n">
-        <v>16795</v>
+        <v>16775</v>
       </c>
       <c r="T254" t="n">
-        <v>8576</v>
+        <v>8570</v>
       </c>
       <c r="U254" t="n">
-        <v>4288</v>
+        <v>4285</v>
       </c>
       <c r="V254" t="n">
-        <v>3930</v>
+        <v>3919</v>
       </c>
       <c r="W254" t="n">
         <v>13.7</v>
@@ -20679,16 +20679,16 @@
         <v>974</v>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M255" t="n">
         <v>10491</v>
       </c>
       <c r="N255" t="n">
-        <v>46571</v>
+        <v>46591</v>
       </c>
       <c r="O255" t="n">
-        <v>28329</v>
+        <v>28309</v>
       </c>
       <c r="P255" t="n">
         <v>2004</v>
@@ -20700,16 +20700,16 @@
         <v>13482</v>
       </c>
       <c r="S255" t="n">
-        <v>15642</v>
+        <v>15622</v>
       </c>
       <c r="T255" t="n">
-        <v>8499</v>
+        <v>8493</v>
       </c>
       <c r="U255" t="n">
-        <v>4249</v>
+        <v>4246</v>
       </c>
       <c r="V255" t="n">
-        <v>2894</v>
+        <v>2883</v>
       </c>
       <c r="W255" t="n">
         <v>10.2</v>
@@ -20761,16 +20761,16 @@
         <v>974</v>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M256" t="n">
         <v>727</v>
       </c>
       <c r="N256" t="n">
-        <v>36712</v>
+        <v>36732</v>
       </c>
       <c r="O256" t="n">
-        <v>38188</v>
+        <v>38168</v>
       </c>
       <c r="P256" t="n">
         <v>5270</v>
@@ -20782,16 +20782,16 @@
         <v>13482</v>
       </c>
       <c r="S256" t="n">
-        <v>24436</v>
+        <v>24416</v>
       </c>
       <c r="T256" t="n">
-        <v>11456</v>
+        <v>11450</v>
       </c>
       <c r="U256" t="n">
-        <v>5728</v>
+        <v>5725</v>
       </c>
       <c r="V256" t="n">
-        <v>7251</v>
+        <v>7240</v>
       </c>
       <c r="W256" t="n">
         <v>19</v>
@@ -20843,16 +20843,16 @@
         <v>974</v>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M257" t="n">
         <v>5243</v>
       </c>
       <c r="N257" t="n">
-        <v>40598</v>
+        <v>40618</v>
       </c>
       <c r="O257" t="n">
-        <v>34302</v>
+        <v>34282</v>
       </c>
       <c r="P257" t="n">
         <v>3074</v>
@@ -20864,19 +20864,19 @@
         <v>13482</v>
       </c>
       <c r="S257" t="n">
-        <v>20946</v>
+        <v>20926</v>
       </c>
       <c r="T257" t="n">
-        <v>10291</v>
+        <v>10285</v>
       </c>
       <c r="U257" t="n">
-        <v>5145</v>
+        <v>5142</v>
       </c>
       <c r="V257" t="n">
-        <v>5510</v>
+        <v>5499</v>
       </c>
       <c r="W257" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="X257" t="inlineStr">
         <is>
@@ -20925,16 +20925,16 @@
         <v>1721</v>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M258" t="n">
         <v>6735</v>
       </c>
       <c r="N258" t="n">
-        <v>43096</v>
+        <v>43116</v>
       </c>
       <c r="O258" t="n">
-        <v>31738</v>
+        <v>31718</v>
       </c>
       <c r="P258" t="n">
         <v>3978</v>
@@ -20946,16 +20946,16 @@
         <v>13482</v>
       </c>
       <c r="S258" t="n">
-        <v>17878</v>
+        <v>17858</v>
       </c>
       <c r="T258" t="n">
-        <v>9521</v>
+        <v>9515</v>
       </c>
       <c r="U258" t="n">
-        <v>4761</v>
+        <v>4758</v>
       </c>
       <c r="V258" t="n">
-        <v>3596</v>
+        <v>3585</v>
       </c>
       <c r="W258" t="n">
         <v>11.3</v>
@@ -21007,16 +21007,16 @@
         <v>5134</v>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M259" t="n">
         <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>40052</v>
+        <v>40072</v>
       </c>
       <c r="O259" t="n">
-        <v>34782</v>
+        <v>34762</v>
       </c>
       <c r="P259" t="n">
         <v>3099</v>
@@ -21028,16 +21028,16 @@
         <v>13482</v>
       </c>
       <c r="S259" t="n">
-        <v>20900</v>
+        <v>20880</v>
       </c>
       <c r="T259" t="n">
-        <v>10435</v>
+        <v>10429</v>
       </c>
       <c r="U259" t="n">
-        <v>5217</v>
+        <v>5214</v>
       </c>
       <c r="V259" t="n">
-        <v>5248</v>
+        <v>5237</v>
       </c>
       <c r="W259" t="n">
         <v>15.1</v>
@@ -21089,16 +21089,16 @@
         <v>973</v>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M260" t="n">
         <v>8013</v>
       </c>
       <c r="N260" t="n">
-        <v>43848</v>
+        <v>43868</v>
       </c>
       <c r="O260" t="n">
-        <v>30986</v>
+        <v>30966</v>
       </c>
       <c r="P260" t="n">
         <v>0</v>
@@ -21110,16 +21110,16 @@
         <v>13482</v>
       </c>
       <c r="S260" t="n">
-        <v>20103</v>
+        <v>20083</v>
       </c>
       <c r="T260" t="n">
-        <v>9296</v>
+        <v>9290</v>
       </c>
       <c r="U260" t="n">
-        <v>4648</v>
+        <v>4645</v>
       </c>
       <c r="V260" t="n">
-        <v>6159</v>
+        <v>6148</v>
       </c>
       <c r="W260" t="n">
         <v>19.9</v>
@@ -21171,16 +21171,16 @@
         <v>973</v>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M261" t="n">
         <v>3757</v>
       </c>
       <c r="N261" t="n">
-        <v>39760</v>
+        <v>39780</v>
       </c>
       <c r="O261" t="n">
-        <v>35074</v>
+        <v>35054</v>
       </c>
       <c r="P261" t="n">
         <v>4589</v>
@@ -21192,16 +21192,16 @@
         <v>13482</v>
       </c>
       <c r="S261" t="n">
-        <v>22002</v>
+        <v>21982</v>
       </c>
       <c r="T261" t="n">
-        <v>10522</v>
+        <v>10516</v>
       </c>
       <c r="U261" t="n">
-        <v>5261</v>
+        <v>5258</v>
       </c>
       <c r="V261" t="n">
-        <v>6219</v>
+        <v>6208</v>
       </c>
       <c r="W261" t="n">
         <v>17.7</v>
@@ -21253,16 +21253,16 @@
         <v>973</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M262" t="n">
         <v>4271</v>
       </c>
       <c r="N262" t="n">
-        <v>43848</v>
+        <v>43868</v>
       </c>
       <c r="O262" t="n">
-        <v>30986</v>
+        <v>30966</v>
       </c>
       <c r="P262" t="n">
         <v>4801</v>
@@ -21274,16 +21274,16 @@
         <v>13482</v>
       </c>
       <c r="S262" t="n">
-        <v>18002</v>
+        <v>17982</v>
       </c>
       <c r="T262" t="n">
-        <v>9296</v>
+        <v>9290</v>
       </c>
       <c r="U262" t="n">
-        <v>4648</v>
+        <v>4645</v>
       </c>
       <c r="V262" t="n">
-        <v>4058</v>
+        <v>4047</v>
       </c>
       <c r="W262" t="n">
         <v>13.1</v>
@@ -21335,16 +21335,16 @@
         <v>966</v>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M263" t="n">
         <v>6690</v>
       </c>
       <c r="N263" t="n">
-        <v>42565</v>
+        <v>42585</v>
       </c>
       <c r="O263" t="n">
-        <v>31767</v>
+        <v>31747</v>
       </c>
       <c r="P263" t="n">
         <v>2948</v>
@@ -21356,19 +21356,19 @@
         <v>13410</v>
       </c>
       <c r="S263" t="n">
-        <v>18509</v>
+        <v>18489</v>
       </c>
       <c r="T263" t="n">
-        <v>9530</v>
+        <v>9524</v>
       </c>
       <c r="U263" t="n">
-        <v>4765</v>
+        <v>4762</v>
       </c>
       <c r="V263" t="n">
-        <v>4214</v>
+        <v>4203</v>
       </c>
       <c r="W263" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="X263" t="inlineStr">
         <is>
@@ -21417,16 +21417,16 @@
         <v>965</v>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M264" t="n">
         <v>11820</v>
       </c>
       <c r="N264" t="n">
-        <v>47409</v>
+        <v>47429</v>
       </c>
       <c r="O264" t="n">
-        <v>26829</v>
+        <v>26809</v>
       </c>
       <c r="P264" t="n">
         <v>4670</v>
@@ -21438,16 +21438,16 @@
         <v>12464</v>
       </c>
       <c r="S264" t="n">
-        <v>13694</v>
+        <v>13674</v>
       </c>
       <c r="T264" t="n">
-        <v>8049</v>
+        <v>8043</v>
       </c>
       <c r="U264" t="n">
-        <v>4024</v>
+        <v>4021</v>
       </c>
       <c r="V264" t="n">
-        <v>1621</v>
+        <v>1610</v>
       </c>
       <c r="W264" t="n">
         <v>6</v>
@@ -21500,16 +21500,16 @@
         <v>961</v>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M265" t="n">
         <v>6131</v>
       </c>
       <c r="N265" t="n">
-        <v>41657</v>
+        <v>41677</v>
       </c>
       <c r="O265" t="n">
-        <v>32243</v>
+        <v>32223</v>
       </c>
       <c r="P265" t="n">
         <v>0</v>
@@ -21521,16 +21521,16 @@
         <v>11912</v>
       </c>
       <c r="S265" t="n">
-        <v>23130</v>
+        <v>23110</v>
       </c>
       <c r="T265" t="n">
-        <v>9673</v>
+        <v>9667</v>
       </c>
       <c r="U265" t="n">
-        <v>4836</v>
+        <v>4833</v>
       </c>
       <c r="V265" t="n">
-        <v>8621</v>
+        <v>8610</v>
       </c>
       <c r="W265" t="n">
         <v>26.7</v>
@@ -21582,16 +21582,16 @@
         <v>935</v>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M266" t="n">
         <v>3595</v>
       </c>
       <c r="N266" t="n">
-        <v>38292</v>
+        <v>38312</v>
       </c>
       <c r="O266" t="n">
-        <v>33608</v>
+        <v>33588</v>
       </c>
       <c r="P266" t="n">
         <v>6472</v>
@@ -21603,16 +21603,16 @@
         <v>11225</v>
       </c>
       <c r="S266" t="n">
-        <v>21110</v>
+        <v>21090</v>
       </c>
       <c r="T266" t="n">
-        <v>10082</v>
+        <v>10076</v>
       </c>
       <c r="U266" t="n">
-        <v>5041</v>
+        <v>5038</v>
       </c>
       <c r="V266" t="n">
-        <v>5986</v>
+        <v>5975</v>
       </c>
       <c r="W266" t="n">
         <v>17.8</v>
@@ -21664,16 +21664,16 @@
         <v>935</v>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M267" t="n">
         <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>38270</v>
+        <v>38290</v>
       </c>
       <c r="O267" t="n">
-        <v>33630</v>
+        <v>33610</v>
       </c>
       <c r="P267" t="n">
         <v>0</v>
@@ -21685,16 +21685,16 @@
         <v>11225</v>
       </c>
       <c r="S267" t="n">
-        <v>27555</v>
+        <v>27535</v>
       </c>
       <c r="T267" t="n">
-        <v>10089</v>
+        <v>10083</v>
       </c>
       <c r="U267" t="n">
-        <v>5044</v>
+        <v>5042</v>
       </c>
       <c r="V267" t="n">
-        <v>12422</v>
+        <v>12410</v>
       </c>
       <c r="W267" t="n">
         <v>36.9</v>
@@ -21742,16 +21742,16 @@
         <v>925</v>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M268" t="n">
         <v>10120</v>
       </c>
       <c r="N268" t="n">
-        <v>44251</v>
+        <v>44271</v>
       </c>
       <c r="O268" t="n">
-        <v>26906</v>
+        <v>26886</v>
       </c>
       <c r="P268" t="n">
         <v>7175</v>
@@ -21763,16 +21763,16 @@
         <v>12464</v>
       </c>
       <c r="S268" t="n">
-        <v>11167</v>
+        <v>11147</v>
       </c>
       <c r="T268" t="n">
-        <v>8072</v>
+        <v>8066</v>
       </c>
       <c r="U268" t="n">
-        <v>4036</v>
+        <v>4033</v>
       </c>
       <c r="V268" t="n">
-        <v>-941</v>
+        <v>-952</v>
       </c>
       <c r="W268" t="n">
         <v>-3.5</v>
@@ -21825,16 +21825,16 @@
         <v>4676</v>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M269" t="n">
         <v>15</v>
       </c>
       <c r="N269" t="n">
-        <v>38000</v>
+        <v>38020</v>
       </c>
       <c r="O269" t="n">
-        <v>33093</v>
+        <v>33073</v>
       </c>
       <c r="P269" t="n">
         <v>2948</v>
@@ -21846,16 +21846,16 @@
         <v>13482</v>
       </c>
       <c r="S269" t="n">
-        <v>19162</v>
+        <v>19142</v>
       </c>
       <c r="T269" t="n">
-        <v>9928</v>
+        <v>9922</v>
       </c>
       <c r="U269" t="n">
-        <v>4964</v>
+        <v>4961</v>
       </c>
       <c r="V269" t="n">
-        <v>4270</v>
+        <v>4259</v>
       </c>
       <c r="W269" t="n">
         <v>12.9</v>
@@ -21907,16 +21907,16 @@
         <v>922</v>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M270" t="n">
         <v>4963</v>
       </c>
       <c r="N270" t="n">
-        <v>39202</v>
+        <v>39222</v>
       </c>
       <c r="O270" t="n">
-        <v>31698</v>
+        <v>31678</v>
       </c>
       <c r="P270" t="n">
         <v>10180</v>
@@ -21928,19 +21928,19 @@
         <v>12490</v>
       </c>
       <c r="S270" t="n">
-        <v>19327</v>
+        <v>19307</v>
       </c>
       <c r="T270" t="n">
-        <v>9509</v>
+        <v>9503</v>
       </c>
       <c r="U270" t="n">
-        <v>4755</v>
+        <v>4752</v>
       </c>
       <c r="V270" t="n">
-        <v>5063</v>
+        <v>5052</v>
       </c>
       <c r="W270" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="X270" t="inlineStr">
         <is>
@@ -21989,16 +21989,16 @@
         <v>4724</v>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M271" t="n">
         <v>7830</v>
       </c>
       <c r="N271" t="n">
-        <v>44445</v>
+        <v>44465</v>
       </c>
       <c r="O271" t="n">
-        <v>23455</v>
+        <v>23435</v>
       </c>
       <c r="P271" t="n">
         <v>3932</v>
@@ -22010,19 +22010,19 @@
         <v>11225</v>
       </c>
       <c r="S271" t="n">
-        <v>12498</v>
+        <v>12478</v>
       </c>
       <c r="T271" t="n">
-        <v>7036</v>
+        <v>7030</v>
       </c>
       <c r="U271" t="n">
-        <v>3518</v>
+        <v>3515</v>
       </c>
       <c r="V271" t="n">
-        <v>1943</v>
+        <v>1932</v>
       </c>
       <c r="W271" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X271" t="inlineStr">
         <is>
@@ -22071,16 +22071,16 @@
         <v>870</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M272" t="n">
         <v>6021</v>
       </c>
       <c r="N272" t="n">
-        <v>41187</v>
+        <v>41207</v>
       </c>
       <c r="O272" t="n">
-        <v>25713</v>
+        <v>25693</v>
       </c>
       <c r="P272" t="n">
         <v>1629</v>
@@ -22092,19 +22092,19 @@
         <v>11909</v>
       </c>
       <c r="S272" t="n">
-        <v>14775</v>
+        <v>14755</v>
       </c>
       <c r="T272" t="n">
-        <v>7714</v>
+        <v>7708</v>
       </c>
       <c r="U272" t="n">
-        <v>3857</v>
+        <v>3854</v>
       </c>
       <c r="V272" t="n">
-        <v>3204</v>
+        <v>3193</v>
       </c>
       <c r="W272" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="X272" t="inlineStr">
         <is>
@@ -22153,16 +22153,16 @@
         <v>1401</v>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M273" t="n">
         <v>4263</v>
       </c>
       <c r="N273" t="n">
-        <v>33932</v>
+        <v>33952</v>
       </c>
       <c r="O273" t="n">
-        <v>26968</v>
+        <v>26948</v>
       </c>
       <c r="P273" t="n">
         <v>4170</v>
@@ -22174,16 +22174,16 @@
         <v>10373</v>
       </c>
       <c r="S273" t="n">
-        <v>16725</v>
+        <v>16705</v>
       </c>
       <c r="T273" t="n">
-        <v>8090</v>
+        <v>8084</v>
       </c>
       <c r="U273" t="n">
-        <v>4045</v>
+        <v>4042</v>
       </c>
       <c r="V273" t="n">
-        <v>4589</v>
+        <v>4578</v>
       </c>
       <c r="W273" t="n">
         <v>17</v>
@@ -22235,16 +22235,16 @@
         <v>792</v>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M274" t="n">
         <v>10666</v>
       </c>
       <c r="N274" t="n">
-        <v>39861</v>
+        <v>39881</v>
       </c>
       <c r="O274" t="n">
-        <v>21039</v>
+        <v>21019</v>
       </c>
       <c r="P274" t="n">
         <v>5627</v>
@@ -22256,16 +22256,16 @@
         <v>10373</v>
       </c>
       <c r="S274" t="n">
-        <v>9239</v>
+        <v>9219</v>
       </c>
       <c r="T274" t="n">
-        <v>6312</v>
+        <v>6306</v>
       </c>
       <c r="U274" t="n">
-        <v>3156</v>
+        <v>3153</v>
       </c>
       <c r="V274" t="n">
-        <v>-229</v>
+        <v>-240</v>
       </c>
       <c r="W274" t="n">
         <v>-1.1</v>
@@ -22317,16 +22317,16 @@
         <v>792</v>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M275" t="n">
         <v>5481</v>
       </c>
       <c r="N275" t="n">
-        <v>34837</v>
+        <v>34857</v>
       </c>
       <c r="O275" t="n">
-        <v>26063</v>
+        <v>26043</v>
       </c>
       <c r="P275" t="n">
         <v>3978</v>
@@ -22338,19 +22338,19 @@
         <v>10373</v>
       </c>
       <c r="S275" t="n">
-        <v>15212</v>
+        <v>15192</v>
       </c>
       <c r="T275" t="n">
-        <v>7819</v>
+        <v>7813</v>
       </c>
       <c r="U275" t="n">
-        <v>3909</v>
+        <v>3906</v>
       </c>
       <c r="V275" t="n">
-        <v>3484</v>
+        <v>3473</v>
       </c>
       <c r="W275" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="X275" t="inlineStr">
         <is>
@@ -22399,16 +22399,16 @@
         <v>3869</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M276" t="n">
         <v>59515</v>
       </c>
       <c r="N276" t="n">
-        <v>89638</v>
+        <v>89658</v>
       </c>
       <c r="O276" t="n">
-        <v>-32738</v>
+        <v>-32758</v>
       </c>
       <c r="P276" t="n">
         <v>3139</v>
@@ -22420,16 +22420,16 @@
         <v>9760</v>
       </c>
       <c r="S276" t="n">
-        <v>-41638</v>
+        <v>-41658</v>
       </c>
       <c r="T276" t="n">
-        <v>-9821</v>
+        <v>-9827</v>
       </c>
       <c r="U276" t="n">
-        <v>-4911</v>
+        <v>-4914</v>
       </c>
       <c r="V276" t="n">
-        <v>-26906</v>
+        <v>-26917</v>
       </c>
       <c r="X276" t="inlineStr">
         <is>
@@ -22478,16 +22478,16 @@
         <v>728</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M277" t="n">
         <v>3987</v>
       </c>
       <c r="N277" t="n">
-        <v>30913</v>
+        <v>30933</v>
       </c>
       <c r="O277" t="n">
-        <v>25067</v>
+        <v>25047</v>
       </c>
       <c r="P277" t="n">
         <v>2948</v>
@@ -22499,19 +22499,19 @@
         <v>9760</v>
       </c>
       <c r="S277" t="n">
-        <v>15059</v>
+        <v>15039</v>
       </c>
       <c r="T277" t="n">
-        <v>7520</v>
+        <v>7514</v>
       </c>
       <c r="U277" t="n">
-        <v>3760</v>
+        <v>3757</v>
       </c>
       <c r="V277" t="n">
-        <v>3779</v>
+        <v>3768</v>
       </c>
       <c r="W277" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="X277" t="inlineStr">
         <is>
@@ -22560,16 +22560,16 @@
         <v>728</v>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M278" t="n">
         <v>9025</v>
       </c>
       <c r="N278" t="n">
-        <v>35951</v>
+        <v>35971</v>
       </c>
       <c r="O278" t="n">
-        <v>20029</v>
+        <v>20009</v>
       </c>
       <c r="P278" t="n">
         <v>3849</v>
@@ -22581,16 +22581,16 @@
         <v>9760</v>
       </c>
       <c r="S278" t="n">
-        <v>9820</v>
+        <v>9800</v>
       </c>
       <c r="T278" t="n">
-        <v>6009</v>
+        <v>6003</v>
       </c>
       <c r="U278" t="n">
-        <v>3004</v>
+        <v>3001</v>
       </c>
       <c r="V278" t="n">
-        <v>807</v>
+        <v>796</v>
       </c>
       <c r="W278" t="n">
         <v>4</v>
@@ -22642,16 +22642,16 @@
         <v>727</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M279" t="n">
         <v>11434</v>
       </c>
       <c r="N279" t="n">
-        <v>38264</v>
+        <v>38284</v>
       </c>
       <c r="O279" t="n">
-        <v>17636</v>
+        <v>17616</v>
       </c>
       <c r="P279" t="n">
         <v>4794</v>
@@ -22663,19 +22663,19 @@
         <v>10373</v>
       </c>
       <c r="S279" t="n">
-        <v>4968</v>
+        <v>4948</v>
       </c>
       <c r="T279" t="n">
-        <v>5291</v>
+        <v>5285</v>
       </c>
       <c r="U279" t="n">
-        <v>2645</v>
+        <v>2642</v>
       </c>
       <c r="V279" t="n">
-        <v>-2968</v>
+        <v>-2979</v>
       </c>
       <c r="W279" t="n">
-        <v>-16.8</v>
+        <v>-16.9</v>
       </c>
       <c r="X279" t="inlineStr">
         <is>
@@ -22724,16 +22724,16 @@
         <v>727</v>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M280" t="n">
         <v>9197</v>
       </c>
       <c r="N280" t="n">
-        <v>36026</v>
+        <v>36046</v>
       </c>
       <c r="O280" t="n">
-        <v>19874</v>
+        <v>19854</v>
       </c>
       <c r="P280" t="n">
         <v>1694</v>
@@ -22745,19 +22745,19 @@
         <v>10373</v>
       </c>
       <c r="S280" t="n">
-        <v>10307</v>
+        <v>10287</v>
       </c>
       <c r="T280" t="n">
-        <v>5962</v>
+        <v>5956</v>
       </c>
       <c r="U280" t="n">
-        <v>2981</v>
+        <v>2978</v>
       </c>
       <c r="V280" t="n">
-        <v>1364</v>
+        <v>1353</v>
       </c>
       <c r="W280" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X280" t="inlineStr">
         <is>
@@ -22806,16 +22806,16 @@
         <v>690</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M281" t="n">
         <v>2655</v>
       </c>
       <c r="N281" t="n">
-        <v>28027</v>
+        <v>28047</v>
       </c>
       <c r="O281" t="n">
-        <v>25078</v>
+        <v>25058</v>
       </c>
       <c r="P281" t="n">
         <v>3099</v>
@@ -22827,16 +22827,16 @@
         <v>10373</v>
       </c>
       <c r="S281" t="n">
-        <v>14405</v>
+        <v>14385</v>
       </c>
       <c r="T281" t="n">
-        <v>7523</v>
+        <v>7517</v>
       </c>
       <c r="U281" t="n">
-        <v>3762</v>
+        <v>3759</v>
       </c>
       <c r="V281" t="n">
-        <v>3120</v>
+        <v>3109</v>
       </c>
       <c r="W281" t="n">
         <v>12.4</v>
@@ -22888,16 +22888,16 @@
         <v>675</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M282" t="n">
         <v>56988</v>
       </c>
       <c r="N282" t="n">
-        <v>81617</v>
+        <v>81637</v>
       </c>
       <c r="O282" t="n">
-        <v>-29717</v>
+        <v>-29737</v>
       </c>
       <c r="P282" t="n">
         <v>3099</v>
@@ -22909,16 +22909,16 @@
         <v>9760</v>
       </c>
       <c r="S282" t="n">
-        <v>-39877</v>
+        <v>-39897</v>
       </c>
       <c r="T282" t="n">
-        <v>-8915</v>
+        <v>-8921</v>
       </c>
       <c r="U282" t="n">
-        <v>-4458</v>
+        <v>-4461</v>
       </c>
       <c r="V282" t="n">
-        <v>-26504</v>
+        <v>-26515</v>
       </c>
       <c r="X282" t="inlineStr">
         <is>
@@ -22967,16 +22967,16 @@
         <v>675</v>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M283" t="n">
         <v>27733</v>
       </c>
       <c r="N283" t="n">
-        <v>52679</v>
+        <v>52699</v>
       </c>
       <c r="O283" t="n">
-        <v>-779</v>
+        <v>-799</v>
       </c>
       <c r="P283" t="n">
         <v>3099</v>
@@ -22988,16 +22988,16 @@
         <v>9760</v>
       </c>
       <c r="S283" t="n">
-        <v>-11138</v>
+        <v>-11158</v>
       </c>
       <c r="T283" t="n">
-        <v>-234</v>
+        <v>-240</v>
       </c>
       <c r="U283" t="n">
-        <v>-117</v>
+        <v>-120</v>
       </c>
       <c r="V283" t="n">
-        <v>-10787</v>
+        <v>-10798</v>
       </c>
       <c r="X283" t="inlineStr">
         <is>
@@ -23046,16 +23046,16 @@
         <v>675</v>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M284" t="n">
         <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>25045</v>
+        <v>25065</v>
       </c>
       <c r="O284" t="n">
-        <v>26855</v>
+        <v>26835</v>
       </c>
       <c r="P284" t="n">
         <v>6419</v>
@@ -23067,16 +23067,16 @@
         <v>9760</v>
       </c>
       <c r="S284" t="n">
-        <v>15875</v>
+        <v>15855</v>
       </c>
       <c r="T284" t="n">
-        <v>8056</v>
+        <v>8050</v>
       </c>
       <c r="U284" t="n">
-        <v>4028</v>
+        <v>4025</v>
       </c>
       <c r="V284" t="n">
-        <v>3790</v>
+        <v>3779</v>
       </c>
       <c r="W284" t="n">
         <v>14.1</v>
@@ -23128,16 +23128,16 @@
         <v>666</v>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M285" t="n">
         <v>6549</v>
       </c>
       <c r="N285" t="n">
-        <v>31229</v>
+        <v>31249</v>
       </c>
       <c r="O285" t="n">
-        <v>20002</v>
+        <v>19982</v>
       </c>
       <c r="P285" t="n">
         <v>3099</v>
@@ -23149,16 +23149,16 @@
         <v>9760</v>
       </c>
       <c r="S285" t="n">
-        <v>9443</v>
+        <v>9423</v>
       </c>
       <c r="T285" t="n">
-        <v>6001</v>
+        <v>5995</v>
       </c>
       <c r="U285" t="n">
-        <v>3000</v>
+        <v>2997</v>
       </c>
       <c r="V285" t="n">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="W285" t="n">
         <v>2.2</v>
@@ -23210,16 +23210,16 @@
         <v>519</v>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M286" t="n">
         <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>21200</v>
+        <v>21220</v>
       </c>
       <c r="O286" t="n">
-        <v>18700</v>
+        <v>18680</v>
       </c>
       <c r="P286" t="n">
         <v>1689</v>
@@ -23231,19 +23231,19 @@
         <v>0</v>
       </c>
       <c r="S286" t="n">
-        <v>22711</v>
+        <v>22691</v>
       </c>
       <c r="T286" t="n">
-        <v>5610</v>
+        <v>5604</v>
       </c>
       <c r="U286" t="n">
-        <v>2805</v>
+        <v>2802</v>
       </c>
       <c r="V286" t="n">
-        <v>14296</v>
+        <v>14285</v>
       </c>
       <c r="W286" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="X286" t="inlineStr">
         <is>
@@ -23292,16 +23292,16 @@
         <v>421</v>
       </c>
       <c r="L287" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M287" t="n">
         <v>1619</v>
       </c>
       <c r="N287" t="n">
-        <v>18646</v>
+        <v>18638</v>
       </c>
       <c r="O287" t="n">
-        <v>13731</v>
+        <v>13739</v>
       </c>
       <c r="P287" t="n">
         <v>0</v>
@@ -23313,16 +23313,16 @@
         <v>4411</v>
       </c>
       <c r="S287" t="n">
-        <v>9320</v>
+        <v>9328</v>
       </c>
       <c r="T287" t="n">
-        <v>4119</v>
+        <v>4122</v>
       </c>
       <c r="U287" t="n">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="V287" t="n">
-        <v>3141</v>
+        <v>3145</v>
       </c>
       <c r="W287" t="n">
         <v>22.9</v>
@@ -23370,16 +23370,16 @@
         <v>421</v>
       </c>
       <c r="L288" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M288" t="n">
         <v>1619</v>
       </c>
       <c r="N288" t="n">
-        <v>18718</v>
+        <v>18709</v>
       </c>
       <c r="O288" t="n">
-        <v>13659</v>
+        <v>13668</v>
       </c>
       <c r="P288" t="n">
         <v>0</v>
@@ -23391,16 +23391,16 @@
         <v>4411</v>
       </c>
       <c r="S288" t="n">
-        <v>9248</v>
+        <v>9257</v>
       </c>
       <c r="T288" t="n">
-        <v>4098</v>
+        <v>4100</v>
       </c>
       <c r="U288" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="V288" t="n">
-        <v>3101</v>
+        <v>3106</v>
       </c>
       <c r="W288" t="n">
         <v>22.7</v>
@@ -23448,16 +23448,16 @@
         <v>421</v>
       </c>
       <c r="L289" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M289" t="n">
         <v>0</v>
       </c>
       <c r="N289" t="n">
-        <v>16680</v>
+        <v>16670</v>
       </c>
       <c r="O289" t="n">
-        <v>15697</v>
+        <v>15707</v>
       </c>
       <c r="P289" t="n">
         <v>0</v>
@@ -23469,16 +23469,16 @@
         <v>4411</v>
       </c>
       <c r="S289" t="n">
-        <v>11286</v>
+        <v>11296</v>
       </c>
       <c r="T289" t="n">
-        <v>4709</v>
+        <v>4712</v>
       </c>
       <c r="U289" t="n">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="V289" t="n">
-        <v>4222</v>
+        <v>4228</v>
       </c>
       <c r="W289" t="n">
         <v>26.9</v>
@@ -23526,16 +23526,16 @@
         <v>410</v>
       </c>
       <c r="L290" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
         <v>5682</v>
       </c>
       <c r="N290" t="n">
-        <v>23209</v>
+        <v>23195</v>
       </c>
       <c r="O290" t="n">
-        <v>8357</v>
+        <v>8371</v>
       </c>
       <c r="P290" t="n">
         <v>0</v>
@@ -23547,19 +23547,19 @@
         <v>4411</v>
       </c>
       <c r="S290" t="n">
-        <v>3946</v>
+        <v>3960</v>
       </c>
       <c r="T290" t="n">
-        <v>2507</v>
+        <v>2511</v>
       </c>
       <c r="U290" t="n">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="V290" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="W290" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="X290" t="inlineStr"/>
     </row>
@@ -23682,16 +23682,16 @@
         <v>410</v>
       </c>
       <c r="L292" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M292" t="n">
         <v>0</v>
       </c>
       <c r="N292" t="n">
-        <v>16849</v>
+        <v>16840</v>
       </c>
       <c r="O292" t="n">
-        <v>14717</v>
+        <v>14726</v>
       </c>
       <c r="P292" t="n">
         <v>0</v>
@@ -23703,16 +23703,16 @@
         <v>4411</v>
       </c>
       <c r="S292" t="n">
-        <v>10306</v>
+        <v>10315</v>
       </c>
       <c r="T292" t="n">
-        <v>4415</v>
+        <v>4418</v>
       </c>
       <c r="U292" t="n">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="V292" t="n">
-        <v>3683</v>
+        <v>3688</v>
       </c>
       <c r="W292" t="n">
         <v>25</v>
@@ -23760,16 +23760,16 @@
         <v>410</v>
       </c>
       <c r="L293" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M293" t="n">
         <v>1578</v>
       </c>
       <c r="N293" t="n">
-        <v>17840</v>
+        <v>17833</v>
       </c>
       <c r="O293" t="n">
-        <v>13726</v>
+        <v>13733</v>
       </c>
       <c r="P293" t="n">
         <v>0</v>
@@ -23781,16 +23781,16 @@
         <v>4411</v>
       </c>
       <c r="S293" t="n">
-        <v>9315</v>
+        <v>9322</v>
       </c>
       <c r="T293" t="n">
-        <v>4118</v>
+        <v>4120</v>
       </c>
       <c r="U293" t="n">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="V293" t="n">
-        <v>3138</v>
+        <v>3142</v>
       </c>
       <c r="W293" t="n">
         <v>22.9</v>
@@ -23838,16 +23838,16 @@
         <v>119</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M294" t="n">
         <v>3428</v>
       </c>
       <c r="N294" t="n">
-        <v>7796</v>
+        <v>7816</v>
       </c>
       <c r="O294" t="n">
-        <v>1394</v>
+        <v>1374</v>
       </c>
       <c r="P294" t="n">
         <v>0</v>
@@ -23859,19 +23859,19 @@
         <v>11759</v>
       </c>
       <c r="S294" t="n">
-        <v>-6165</v>
+        <v>-6185</v>
       </c>
       <c r="T294" t="n">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="U294" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="V294" t="n">
-        <v>-6792</v>
+        <v>-6803</v>
       </c>
       <c r="W294" t="n">
-        <v>-487.3</v>
+        <v>-495.1</v>
       </c>
       <c r="X294" t="inlineStr"/>
     </row>
@@ -23916,16 +23916,16 @@
         <v>119</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M295" t="n">
         <v>8994</v>
       </c>
       <c r="N295" t="n">
-        <v>13705</v>
+        <v>13725</v>
       </c>
       <c r="O295" t="n">
-        <v>-4516</v>
+        <v>-4536</v>
       </c>
       <c r="P295" t="n">
         <v>0</v>
@@ -23937,16 +23937,16 @@
         <v>11759</v>
       </c>
       <c r="S295" t="n">
-        <v>-14175</v>
+        <v>-14195</v>
       </c>
       <c r="T295" t="n">
-        <v>-1355</v>
+        <v>-1361</v>
       </c>
       <c r="U295" t="n">
-        <v>-677</v>
+        <v>-680</v>
       </c>
       <c r="V295" t="n">
-        <v>-12143</v>
+        <v>-12154</v>
       </c>
       <c r="X295" t="inlineStr"/>
     </row>
@@ -23991,16 +23991,16 @@
         <v>79</v>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M296" t="n">
         <v>6448</v>
       </c>
       <c r="N296" t="n">
-        <v>10184</v>
+        <v>10204</v>
       </c>
       <c r="O296" t="n">
-        <v>-4090</v>
+        <v>-4110</v>
       </c>
       <c r="P296" t="n">
         <v>0</v>
@@ -24012,16 +24012,16 @@
         <v>16933</v>
       </c>
       <c r="S296" t="n">
-        <v>-18923</v>
+        <v>-18943</v>
       </c>
       <c r="T296" t="n">
-        <v>-1227</v>
+        <v>-1233</v>
       </c>
       <c r="U296" t="n">
-        <v>-614</v>
+        <v>-616</v>
       </c>
       <c r="V296" t="n">
-        <v>-17082</v>
+        <v>-17094</v>
       </c>
       <c r="X296" t="inlineStr">
         <is>
@@ -24070,16 +24070,16 @@
         <v>60</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M297" t="n">
         <v>18442</v>
       </c>
       <c r="N297" t="n">
-        <v>20776</v>
+        <v>20796</v>
       </c>
       <c r="O297" t="n">
-        <v>-16180</v>
+        <v>-16200</v>
       </c>
       <c r="P297" t="n">
         <v>0</v>
@@ -24091,16 +24091,16 @@
         <v>11759</v>
       </c>
       <c r="S297" t="n">
-        <v>-25739</v>
+        <v>-25759</v>
       </c>
       <c r="T297" t="n">
-        <v>-4854</v>
+        <v>-4860</v>
       </c>
       <c r="U297" t="n">
-        <v>-2427</v>
+        <v>-2430</v>
       </c>
       <c r="V297" t="n">
-        <v>-18458</v>
+        <v>-18469</v>
       </c>
       <c r="X297" t="inlineStr"/>
     </row>
@@ -24145,16 +24145,16 @@
         <v>974</v>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M298" t="n">
         <v>8884</v>
       </c>
       <c r="N298" t="n">
-        <v>10332</v>
+        <v>10352</v>
       </c>
       <c r="O298" t="n">
-        <v>-10332</v>
+        <v>-10352</v>
       </c>
       <c r="P298" t="n">
         <v>3761</v>
@@ -24166,16 +24166,16 @@
         <v>12464</v>
       </c>
       <c r="S298" t="n">
-        <v>-26557</v>
+        <v>-26577</v>
       </c>
       <c r="T298" t="n">
-        <v>-3100</v>
+        <v>-3106</v>
       </c>
       <c r="U298" t="n">
-        <v>-1550</v>
+        <v>-1553</v>
       </c>
       <c r="V298" t="n">
-        <v>-21908</v>
+        <v>-21919</v>
       </c>
       <c r="X298" t="inlineStr">
         <is>
@@ -24723,16 +24723,16 @@
         <v>402</v>
       </c>
       <c r="L306" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M306" t="n">
         <v>1545</v>
       </c>
       <c r="N306" t="n">
-        <v>17670</v>
+        <v>17661</v>
       </c>
       <c r="O306" t="n">
-        <v>13230</v>
+        <v>13239</v>
       </c>
       <c r="P306" t="n">
         <v>0</v>
@@ -24744,16 +24744,16 @@
         <v>3744</v>
       </c>
       <c r="S306" t="n">
-        <v>9486</v>
+        <v>9495</v>
       </c>
       <c r="T306" t="n">
-        <v>3969</v>
+        <v>3972</v>
       </c>
       <c r="U306" t="n">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="V306" t="n">
-        <v>3532</v>
+        <v>3537</v>
       </c>
       <c r="W306" t="n">
         <v>26.7</v>
@@ -24801,16 +24801,16 @@
         <v>402</v>
       </c>
       <c r="L307" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M307" t="n">
         <v>1545</v>
       </c>
       <c r="N307" t="n">
-        <v>18182</v>
+        <v>18174</v>
       </c>
       <c r="O307" t="n">
-        <v>12718</v>
+        <v>12726</v>
       </c>
       <c r="P307" t="n">
         <v>0</v>
@@ -24822,16 +24822,16 @@
         <v>3744</v>
       </c>
       <c r="S307" t="n">
-        <v>8974</v>
+        <v>8982</v>
       </c>
       <c r="T307" t="n">
-        <v>3815</v>
+        <v>3818</v>
       </c>
       <c r="U307" t="n">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="V307" t="n">
-        <v>3251</v>
+        <v>3255</v>
       </c>
       <c r="W307" t="n">
         <v>25.6</v>
@@ -25425,16 +25425,16 @@
         <v>358</v>
       </c>
       <c r="L315" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M315" t="n">
         <v>0</v>
       </c>
       <c r="N315" t="n">
-        <v>15567</v>
+        <v>15558</v>
       </c>
       <c r="O315" t="n">
-        <v>11941</v>
+        <v>11950</v>
       </c>
       <c r="P315" t="n">
         <v>0</v>
@@ -25446,16 +25446,16 @@
         <v>3230</v>
       </c>
       <c r="S315" t="n">
-        <v>8711</v>
+        <v>8720</v>
       </c>
       <c r="T315" t="n">
-        <v>3582</v>
+        <v>3585</v>
       </c>
       <c r="U315" t="n">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="V315" t="n">
-        <v>3338</v>
+        <v>3342</v>
       </c>
       <c r="W315" t="n">
         <v>28</v>
@@ -25503,16 +25503,16 @@
         <v>358</v>
       </c>
       <c r="L316" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M316" t="n">
         <v>1375</v>
       </c>
       <c r="N316" t="n">
-        <v>16710</v>
+        <v>16702</v>
       </c>
       <c r="O316" t="n">
-        <v>10798</v>
+        <v>10806</v>
       </c>
       <c r="P316" t="n">
         <v>0</v>
@@ -25524,16 +25524,16 @@
         <v>3230</v>
       </c>
       <c r="S316" t="n">
-        <v>7568</v>
+        <v>7576</v>
       </c>
       <c r="T316" t="n">
-        <v>3239</v>
+        <v>3242</v>
       </c>
       <c r="U316" t="n">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="V316" t="n">
-        <v>2709</v>
+        <v>2713</v>
       </c>
       <c r="W316" t="n">
         <v>25.1</v>
@@ -25581,16 +25581,16 @@
         <v>288</v>
       </c>
       <c r="L317" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M317" t="n">
         <v>1997</v>
       </c>
       <c r="N317" t="n">
-        <v>14750</v>
+        <v>14740</v>
       </c>
       <c r="O317" t="n">
-        <v>7437</v>
+        <v>7447</v>
       </c>
       <c r="P317" t="n">
         <v>0</v>
@@ -25602,16 +25602,16 @@
         <v>3230</v>
       </c>
       <c r="S317" t="n">
-        <v>4207</v>
+        <v>4217</v>
       </c>
       <c r="T317" t="n">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="U317" t="n">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="V317" t="n">
-        <v>860</v>
+        <v>866</v>
       </c>
       <c r="W317" t="n">
         <v>11.6</v>
@@ -25738,16 +25738,16 @@
         <v>402</v>
       </c>
       <c r="L319" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M319" t="n">
         <v>0</v>
       </c>
       <c r="N319" t="n">
-        <v>1843</v>
+        <v>1822</v>
       </c>
       <c r="O319" t="n">
-        <v>-1843</v>
+        <v>-1822</v>
       </c>
       <c r="P319" t="n">
         <v>0</v>
@@ -25759,16 +25759,16 @@
         <v>3744</v>
       </c>
       <c r="S319" t="n">
-        <v>-5587</v>
+        <v>-5566</v>
       </c>
       <c r="T319" t="n">
-        <v>-553</v>
+        <v>-547</v>
       </c>
       <c r="U319" t="n">
-        <v>-276</v>
+        <v>-273</v>
       </c>
       <c r="V319" t="n">
-        <v>-4758</v>
+        <v>-4746</v>
       </c>
       <c r="X319" t="inlineStr"/>
     </row>
@@ -25805,16 +25805,16 @@
         <v>477480</v>
       </c>
       <c r="L320" s="3" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M320" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>477543</v>
+        <v>477480</v>
       </c>
       <c r="O320" s="3" t="n">
-        <v>-477543</v>
+        <v>-477480</v>
       </c>
       <c r="P320" s="3" t="n">
         <v>0</v>
@@ -25826,16 +25826,16 @@
         <v>0</v>
       </c>
       <c r="S320" s="3" t="n">
-        <v>-477543</v>
+        <v>-477480</v>
       </c>
       <c r="T320" s="3" t="n">
-        <v>-143263</v>
+        <v>-143244</v>
       </c>
       <c r="U320" s="3" t="n">
-        <v>-71631</v>
+        <v>-71622</v>
       </c>
       <c r="V320" s="3" t="n">
-        <v>-262649</v>
+        <v>-262614</v>
       </c>
       <c r="W320" s="3" t="n"/>
       <c r="X320" s="3" t="inlineStr"/>
@@ -25873,16 +25873,16 @@
         <v>822520</v>
       </c>
       <c r="L321" s="4" t="n">
-        <v>20904</v>
+        <v>35639</v>
       </c>
       <c r="M321" s="4" t="n">
         <v>2105807</v>
       </c>
       <c r="N321" s="4" t="n">
-        <v>12862625</v>
+        <v>12877360</v>
       </c>
       <c r="O321" s="4" t="n">
-        <v>8151848</v>
+        <v>8137113</v>
       </c>
       <c r="P321" s="4" t="n">
         <v>646086</v>
@@ -25894,19 +25894,19 @@
         <v>3318949</v>
       </c>
       <c r="S321" s="4" t="n">
-        <v>4832311</v>
+        <v>4817576</v>
       </c>
       <c r="T321" s="4" t="n">
-        <v>2445554</v>
+        <v>2441134</v>
       </c>
       <c r="U321" s="4" t="n">
-        <v>1222777</v>
+        <v>1220567</v>
       </c>
       <c r="V321" s="4" t="n">
-        <v>1163979</v>
+        <v>1155875</v>
       </c>
       <c r="W321" s="4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="X321" s="4" t="inlineStr"/>
     </row>
